--- a/data/64_Submissions_Source.xlsx
+++ b/data/64_Submissions_Source.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Submissions" sheetId="1" r:id="R47ba7da63c184d11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Submissions" sheetId="1" r:id="Rb051e56e78eb485e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -510,45 +510,45 @@
       <x:c r="J2" t="str">
         <x:v>School of Creative Arts</x:v>
       </x:c>
-      <x:c r="K2" t="str"/>
-      <x:c r="L2" t="str"/>
-      <x:c r="M2" t="str"/>
-      <x:c r="N2" t="str"/>
-      <x:c r="O2" t="str"/>
-      <x:c r="P2" t="str"/>
-      <x:c r="Q2" t="str"/>
-      <x:c r="R2" t="str"/>
-      <x:c r="S2" t="str"/>
-      <x:c r="T2" t="str"/>
-      <x:c r="U2" t="str"/>
-      <x:c r="V2" t="str"/>
-      <x:c r="W2" t="str"/>
-      <x:c r="X2" t="str"/>
-      <x:c r="Y2" t="str"/>
-      <x:c r="Z2" t="str"/>
-      <x:c r="AA2" t="str"/>
-      <x:c r="AB2" t="str"/>
-      <x:c r="AC2" t="str"/>
-      <x:c r="AD2" t="str"/>
-      <x:c r="AE2" t="str"/>
-      <x:c r="AF2" t="str"/>
-      <x:c r="AG2" t="str"/>
-      <x:c r="AH2" t="str"/>
-      <x:c r="AI2" t="str"/>
-      <x:c r="AJ2" t="str"/>
-      <x:c r="AK2" t="str"/>
-      <x:c r="AL2" t="str"/>
-      <x:c r="AM2" t="str"/>
-      <x:c r="AN2" t="str"/>
-      <x:c r="AO2" t="str"/>
-      <x:c r="AP2" t="str"/>
-      <x:c r="AQ2" t="str"/>
-      <x:c r="AR2" t="str"/>
-      <x:c r="AS2" t="str"/>
-      <x:c r="AT2" t="str"/>
-      <x:c r="AU2" t="str"/>
-      <x:c r="AV2" t="str"/>
-      <x:c r="AW2" t="str"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
+      <x:c r="M2"/>
+      <x:c r="N2"/>
+      <x:c r="O2"/>
+      <x:c r="P2"/>
+      <x:c r="Q2"/>
+      <x:c r="R2"/>
+      <x:c r="S2"/>
+      <x:c r="T2"/>
+      <x:c r="U2"/>
+      <x:c r="V2"/>
+      <x:c r="W2"/>
+      <x:c r="X2"/>
+      <x:c r="Y2"/>
+      <x:c r="Z2"/>
+      <x:c r="AA2"/>
+      <x:c r="AB2"/>
+      <x:c r="AC2"/>
+      <x:c r="AD2"/>
+      <x:c r="AE2"/>
+      <x:c r="AF2"/>
+      <x:c r="AG2"/>
+      <x:c r="AH2"/>
+      <x:c r="AI2"/>
+      <x:c r="AJ2"/>
+      <x:c r="AK2"/>
+      <x:c r="AL2"/>
+      <x:c r="AM2"/>
+      <x:c r="AN2"/>
+      <x:c r="AO2"/>
+      <x:c r="AP2"/>
+      <x:c r="AQ2"/>
+      <x:c r="AR2"/>
+      <x:c r="AS2"/>
+      <x:c r="AT2"/>
+      <x:c r="AU2"/>
+      <x:c r="AV2"/>
+      <x:c r="AW2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -595,10 +595,10 @@
 Reflection:
 The inaugural session served as an important first step toward building a stronger and more sustainable relationship between SOCA, its alumni, and current students. The feedback and interactions will help the School shape future alumni engagement initiatives according to the needs and interests of both alumni and students.</x:v>
       </x:c>
-      <x:c r="O3" t="str"/>
-      <x:c r="P3" t="str"/>
-      <x:c r="Q3" t="str"/>
-      <x:c r="R3" t="str"/>
+      <x:c r="O3"/>
+      <x:c r="P3"/>
+      <x:c r="Q3"/>
+      <x:c r="R3"/>
       <x:c r="S3" t="str">
         <x:v>Act Local, Think Global: SOCA SDG Awareness Drive (SDG 13 – Climate Action)
 The purpose of the awareness drive is to engage students with the local community through creative communication and raise awareness about climate change and individual responsibility for environmental protection. The initiative will provide SOCA students with an opportunity to apply their academic and creative skills to a real-world social and environmental issue.
@@ -641,33 +641,33 @@
 Community and participant social media sharing
 Post-event highlights and impact report</x:v>
       </x:c>
-      <x:c r="W3" t="str"/>
-      <x:c r="X3" t="str"/>
-      <x:c r="Y3" t="str"/>
-      <x:c r="Z3" t="str"/>
-      <x:c r="AA3" t="str"/>
-      <x:c r="AB3" t="str"/>
-      <x:c r="AC3" t="str"/>
-      <x:c r="AD3" t="str"/>
-      <x:c r="AE3" t="str"/>
-      <x:c r="AF3" t="str"/>
-      <x:c r="AG3" t="str"/>
-      <x:c r="AH3" t="str"/>
-      <x:c r="AI3" t="str"/>
-      <x:c r="AJ3" t="str"/>
-      <x:c r="AK3" t="str"/>
-      <x:c r="AL3" t="str"/>
-      <x:c r="AM3" t="str"/>
-      <x:c r="AN3" t="str"/>
-      <x:c r="AO3" t="str"/>
-      <x:c r="AP3" t="str"/>
-      <x:c r="AQ3" t="str"/>
-      <x:c r="AR3" t="str"/>
-      <x:c r="AS3" t="str"/>
-      <x:c r="AT3" t="str"/>
-      <x:c r="AU3" t="str"/>
-      <x:c r="AV3" t="str"/>
-      <x:c r="AW3" t="str"/>
+      <x:c r="W3"/>
+      <x:c r="X3"/>
+      <x:c r="Y3"/>
+      <x:c r="Z3"/>
+      <x:c r="AA3"/>
+      <x:c r="AB3"/>
+      <x:c r="AC3"/>
+      <x:c r="AD3"/>
+      <x:c r="AE3"/>
+      <x:c r="AF3"/>
+      <x:c r="AG3"/>
+      <x:c r="AH3"/>
+      <x:c r="AI3"/>
+      <x:c r="AJ3"/>
+      <x:c r="AK3"/>
+      <x:c r="AL3"/>
+      <x:c r="AM3"/>
+      <x:c r="AN3"/>
+      <x:c r="AO3"/>
+      <x:c r="AP3"/>
+      <x:c r="AQ3"/>
+      <x:c r="AR3"/>
+      <x:c r="AS3"/>
+      <x:c r="AT3"/>
+      <x:c r="AU3"/>
+      <x:c r="AV3"/>
+      <x:c r="AW3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
@@ -700,7 +700,7 @@
       <x:c r="J4" t="str">
         <x:v>University Institute of Medical Lab Technology</x:v>
       </x:c>
-      <x:c r="K4" t="str"/>
+      <x:c r="K4"/>
       <x:c r="L4" t="str">
         <x:v>Partner Institution: MoU with ELC Biogen, Country: Pakistan, MOU Type: Industry, Status: Under Process</x:v>
       </x:c>
@@ -713,20 +713,20 @@
       <x:c r="O4" t="str">
         <x:v>New Proposals Initiated: MOU for academic research between university of Lahore and Different institutes, External Collaborators: Punjab Uiversity, Current Status: Drafting</x:v>
       </x:c>
-      <x:c r="P4" t="str"/>
+      <x:c r="P4"/>
       <x:c r="Q4" t="str">
         <x:v>Tentative Date: 2026-10-21, Planned Activity / Event: Breast cancer Awareness Seminar, Objective / Expected Outcome: Awareness on breast cancer</x:v>
       </x:c>
-      <x:c r="R4" t="str"/>
+      <x:c r="R4"/>
       <x:c r="S4" t="str">
         <x:v>Breast cancer Awareness Seminar
 -Hands-On Workshop on CBC Analyzer: Principles, Operation and Interpretation
 -Combating Antimicrobial Resistance: Challenges and Solutions
 - Awareness seminar on HIV in collaboration with Punjab Aids Control Program</x:v>
       </x:c>
-      <x:c r="T4" t="str"/>
-      <x:c r="U4" t="str"/>
-      <x:c r="V4" t="str"/>
+      <x:c r="T4"/>
+      <x:c r="U4"/>
+      <x:c r="V4"/>
       <x:c r="W4" t="str">
         <x:v>2026-09-21</x:v>
       </x:c>
@@ -736,30 +736,30 @@
       <x:c r="Y4" t="str">
         <x:v>Lecturer</x:v>
       </x:c>
-      <x:c r="Z4" t="str"/>
-      <x:c r="AA4" t="str"/>
-      <x:c r="AB4" t="str"/>
-      <x:c r="AC4" t="str"/>
-      <x:c r="AD4" t="str"/>
-      <x:c r="AE4" t="str"/>
-      <x:c r="AF4" t="str"/>
-      <x:c r="AG4" t="str"/>
-      <x:c r="AH4" t="str"/>
-      <x:c r="AI4" t="str"/>
-      <x:c r="AJ4" t="str"/>
-      <x:c r="AK4" t="str"/>
-      <x:c r="AL4" t="str"/>
-      <x:c r="AM4" t="str"/>
-      <x:c r="AN4" t="str"/>
-      <x:c r="AO4" t="str"/>
-      <x:c r="AP4" t="str"/>
-      <x:c r="AQ4" t="str"/>
-      <x:c r="AR4" t="str"/>
-      <x:c r="AS4" t="str"/>
-      <x:c r="AT4" t="str"/>
-      <x:c r="AU4" t="str"/>
-      <x:c r="AV4" t="str"/>
-      <x:c r="AW4" t="str"/>
+      <x:c r="Z4"/>
+      <x:c r="AA4"/>
+      <x:c r="AB4"/>
+      <x:c r="AC4"/>
+      <x:c r="AD4"/>
+      <x:c r="AE4"/>
+      <x:c r="AF4"/>
+      <x:c r="AG4"/>
+      <x:c r="AH4"/>
+      <x:c r="AI4"/>
+      <x:c r="AJ4"/>
+      <x:c r="AK4"/>
+      <x:c r="AL4"/>
+      <x:c r="AM4"/>
+      <x:c r="AN4"/>
+      <x:c r="AO4"/>
+      <x:c r="AP4"/>
+      <x:c r="AQ4"/>
+      <x:c r="AR4"/>
+      <x:c r="AS4"/>
+      <x:c r="AT4"/>
+      <x:c r="AU4"/>
+      <x:c r="AV4"/>
+      <x:c r="AW4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
@@ -798,16 +798,16 @@
       <x:c r="L5" t="str">
         <x:v>Partner Institution: The Golden Ring Economic Forum, Country: Pakistan, MOU Type: Industry, Key Activities: Research Collaboration, Status: Completed, Evidence: files::6abf4e0dca9ef_GREF.pdf | Partner Institution: Consortium for Asia Pacific &amp; Eurasian Studies (CAPES), Country: Pakistan, MOU Type: Academic, Key Activities: Research Collaboration, Fellowship Hosting, Status: Completed, Evidence: files::6abf4e22c66dc_CAPES.pdf</x:v>
       </x:c>
-      <x:c r="M5" t="str"/>
-      <x:c r="N5" t="str"/>
-      <x:c r="O5" t="str"/>
-      <x:c r="P5" t="str"/>
-      <x:c r="Q5" t="str"/>
-      <x:c r="R5" t="str"/>
-      <x:c r="S5" t="str"/>
-      <x:c r="T5" t="str"/>
-      <x:c r="U5" t="str"/>
-      <x:c r="V5" t="str"/>
+      <x:c r="M5"/>
+      <x:c r="N5"/>
+      <x:c r="O5"/>
+      <x:c r="P5"/>
+      <x:c r="Q5"/>
+      <x:c r="R5"/>
+      <x:c r="S5"/>
+      <x:c r="T5"/>
+      <x:c r="U5"/>
+      <x:c r="V5"/>
       <x:c r="W5" t="str">
         <x:v>2026-08-31</x:v>
       </x:c>
@@ -820,29 +820,29 @@
       <x:c r="Z5" t="str">
         <x:v>2026-10-02</x:v>
       </x:c>
-      <x:c r="AA5" t="str"/>
-      <x:c r="AB5" t="str"/>
-      <x:c r="AC5" t="str"/>
-      <x:c r="AD5" t="str"/>
-      <x:c r="AE5" t="str"/>
-      <x:c r="AF5" t="str"/>
-      <x:c r="AG5" t="str"/>
-      <x:c r="AH5" t="str"/>
-      <x:c r="AI5" t="str"/>
-      <x:c r="AJ5" t="str"/>
-      <x:c r="AK5" t="str"/>
-      <x:c r="AL5" t="str"/>
-      <x:c r="AM5" t="str"/>
-      <x:c r="AN5" t="str"/>
-      <x:c r="AO5" t="str"/>
-      <x:c r="AP5" t="str"/>
-      <x:c r="AQ5" t="str"/>
-      <x:c r="AR5" t="str"/>
-      <x:c r="AS5" t="str"/>
-      <x:c r="AT5" t="str"/>
-      <x:c r="AU5" t="str"/>
-      <x:c r="AV5" t="str"/>
-      <x:c r="AW5" t="str"/>
+      <x:c r="AA5"/>
+      <x:c r="AB5"/>
+      <x:c r="AC5"/>
+      <x:c r="AD5"/>
+      <x:c r="AE5"/>
+      <x:c r="AF5"/>
+      <x:c r="AG5"/>
+      <x:c r="AH5"/>
+      <x:c r="AI5"/>
+      <x:c r="AJ5"/>
+      <x:c r="AK5"/>
+      <x:c r="AL5"/>
+      <x:c r="AM5"/>
+      <x:c r="AN5"/>
+      <x:c r="AO5"/>
+      <x:c r="AP5"/>
+      <x:c r="AQ5"/>
+      <x:c r="AR5"/>
+      <x:c r="AS5"/>
+      <x:c r="AT5"/>
+      <x:c r="AU5"/>
+      <x:c r="AV5"/>
+      <x:c r="AW5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
@@ -881,16 +881,16 @@
       <x:c r="L6" t="str">
         <x:v>Partner Institution: The Golden Ring Economic Forum, Country: Pakistan, MOU Type: Industry, Key Activities: Research Collaboration, Status: Completed, Evidence: files::6abf4e0dca9ef_GREF.pdf | Partner Institution: Consortium for Asia Pacific &amp; Eurasian Studies (CAPES), Country: Pakistan, MOU Type: Academic, Key Activities: Research Collaboration, Fellowship Hosting, Status: Completed, Evidence: files::6abf4e22c66dc_CAPES.pdf</x:v>
       </x:c>
-      <x:c r="M6" t="str"/>
-      <x:c r="N6" t="str"/>
-      <x:c r="O6" t="str"/>
-      <x:c r="P6" t="str"/>
-      <x:c r="Q6" t="str"/>
-      <x:c r="R6" t="str"/>
-      <x:c r="S6" t="str"/>
-      <x:c r="T6" t="str"/>
-      <x:c r="U6" t="str"/>
-      <x:c r="V6" t="str"/>
+      <x:c r="M6"/>
+      <x:c r="N6"/>
+      <x:c r="O6"/>
+      <x:c r="P6"/>
+      <x:c r="Q6"/>
+      <x:c r="R6"/>
+      <x:c r="S6"/>
+      <x:c r="T6"/>
+      <x:c r="U6"/>
+      <x:c r="V6"/>
       <x:c r="W6" t="str">
         <x:v>2026-08-31</x:v>
       </x:c>
@@ -903,29 +903,29 @@
       <x:c r="Z6" t="str">
         <x:v>2026-10-02</x:v>
       </x:c>
-      <x:c r="AA6" t="str"/>
-      <x:c r="AB6" t="str"/>
-      <x:c r="AC6" t="str"/>
-      <x:c r="AD6" t="str"/>
-      <x:c r="AE6" t="str"/>
-      <x:c r="AF6" t="str"/>
-      <x:c r="AG6" t="str"/>
-      <x:c r="AH6" t="str"/>
-      <x:c r="AI6" t="str"/>
-      <x:c r="AJ6" t="str"/>
-      <x:c r="AK6" t="str"/>
-      <x:c r="AL6" t="str"/>
-      <x:c r="AM6" t="str"/>
-      <x:c r="AN6" t="str"/>
-      <x:c r="AO6" t="str"/>
-      <x:c r="AP6" t="str"/>
-      <x:c r="AQ6" t="str"/>
-      <x:c r="AR6" t="str"/>
-      <x:c r="AS6" t="str"/>
-      <x:c r="AT6" t="str"/>
-      <x:c r="AU6" t="str"/>
-      <x:c r="AV6" t="str"/>
-      <x:c r="AW6" t="str"/>
+      <x:c r="AA6"/>
+      <x:c r="AB6"/>
+      <x:c r="AC6"/>
+      <x:c r="AD6"/>
+      <x:c r="AE6"/>
+      <x:c r="AF6"/>
+      <x:c r="AG6"/>
+      <x:c r="AH6"/>
+      <x:c r="AI6"/>
+      <x:c r="AJ6"/>
+      <x:c r="AK6"/>
+      <x:c r="AL6"/>
+      <x:c r="AM6"/>
+      <x:c r="AN6"/>
+      <x:c r="AO6"/>
+      <x:c r="AP6"/>
+      <x:c r="AQ6"/>
+      <x:c r="AR6"/>
+      <x:c r="AS6"/>
+      <x:c r="AT6"/>
+      <x:c r="AU6"/>
+      <x:c r="AV6"/>
+      <x:c r="AW6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
@@ -964,16 +964,16 @@
       <x:c r="L7" t="str">
         <x:v>Partner Institution: The Golden Ring Economic Forum, Country: Pakistan, MOU Type: Industry, Key Activities: Research Collaboration, Status: Completed, Evidence: files::6abf4e0dca9ef_GREF.pdf | Partner Institution: Consortium for Asia Pacific &amp; Eurasian Studies (CAPES), Country: Pakistan, MOU Type: Academic, Key Activities: Research Collaboration, Fellowship Hosting, Status: Completed, Evidence: files::6abf4e22c66dc_CAPES.pdf</x:v>
       </x:c>
-      <x:c r="M7" t="str"/>
-      <x:c r="N7" t="str"/>
-      <x:c r="O7" t="str"/>
-      <x:c r="P7" t="str"/>
-      <x:c r="Q7" t="str"/>
-      <x:c r="R7" t="str"/>
-      <x:c r="S7" t="str"/>
-      <x:c r="T7" t="str"/>
-      <x:c r="U7" t="str"/>
-      <x:c r="V7" t="str"/>
+      <x:c r="M7"/>
+      <x:c r="N7"/>
+      <x:c r="O7"/>
+      <x:c r="P7"/>
+      <x:c r="Q7"/>
+      <x:c r="R7"/>
+      <x:c r="S7"/>
+      <x:c r="T7"/>
+      <x:c r="U7"/>
+      <x:c r="V7"/>
       <x:c r="W7" t="str">
         <x:v>2026-08-31</x:v>
       </x:c>
@@ -986,29 +986,29 @@
       <x:c r="Z7" t="str">
         <x:v>2026-10-02</x:v>
       </x:c>
-      <x:c r="AA7" t="str"/>
-      <x:c r="AB7" t="str"/>
-      <x:c r="AC7" t="str"/>
-      <x:c r="AD7" t="str"/>
-      <x:c r="AE7" t="str"/>
-      <x:c r="AF7" t="str"/>
-      <x:c r="AG7" t="str"/>
-      <x:c r="AH7" t="str"/>
-      <x:c r="AI7" t="str"/>
-      <x:c r="AJ7" t="str"/>
-      <x:c r="AK7" t="str"/>
-      <x:c r="AL7" t="str"/>
-      <x:c r="AM7" t="str"/>
-      <x:c r="AN7" t="str"/>
-      <x:c r="AO7" t="str"/>
-      <x:c r="AP7" t="str"/>
-      <x:c r="AQ7" t="str"/>
-      <x:c r="AR7" t="str"/>
-      <x:c r="AS7" t="str"/>
-      <x:c r="AT7" t="str"/>
-      <x:c r="AU7" t="str"/>
-      <x:c r="AV7" t="str"/>
-      <x:c r="AW7" t="str"/>
+      <x:c r="AA7"/>
+      <x:c r="AB7"/>
+      <x:c r="AC7"/>
+      <x:c r="AD7"/>
+      <x:c r="AE7"/>
+      <x:c r="AF7"/>
+      <x:c r="AG7"/>
+      <x:c r="AH7"/>
+      <x:c r="AI7"/>
+      <x:c r="AJ7"/>
+      <x:c r="AK7"/>
+      <x:c r="AL7"/>
+      <x:c r="AM7"/>
+      <x:c r="AN7"/>
+      <x:c r="AO7"/>
+      <x:c r="AP7"/>
+      <x:c r="AQ7"/>
+      <x:c r="AR7"/>
+      <x:c r="AS7"/>
+      <x:c r="AT7"/>
+      <x:c r="AU7"/>
+      <x:c r="AV7"/>
+      <x:c r="AW7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
@@ -1044,19 +1044,19 @@
       <x:c r="K8" t="str">
         <x:v>Activity Type: IP, How Many: 240, Name Of Organization Planned with: About sixty six companies for the placement of industrial Training  Internship, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-10-02 | Activity Type: Industrial Visit, How Many: 3, Name Of Organization Planned with: Codecoy, Planned: Yes, Scheduled: No, Datev Planned on: 2026-10-13, Remarks/Result: Yes | Activity Type: Seminar / Conference / Workshop, How Many: 2, Name Of Organization Planned with: XYZ, Planned: Yes, Datev Planned on: 2026-10-31, Remarks/Result: Yes | Activity Type: IAB Meeting / Industry Consultation, How Many: 1, Name Of Organization Planned with: Yousaf Engg Air Comfort Creative Tech Grit  Private Ltd Mediland, Planned: Yes, Scheduled: No, Datev Planned on: 2026-11-30, Remarks/Result: yes | </x:v>
       </x:c>
-      <x:c r="L8" t="str"/>
+      <x:c r="L8"/>
       <x:c r="M8" t="str">
         <x:v>Company: about 66 companies, Sector: Mechanical, Civil, Electrical, Biomedical &amp; Information Engineering Technologies, Number Of students: 240, Duration: 4 months, Type: Intership, Mode: Physical</x:v>
       </x:c>
-      <x:c r="N8" t="str"/>
-      <x:c r="O8" t="str"/>
-      <x:c r="P8" t="str"/>
-      <x:c r="Q8" t="str"/>
-      <x:c r="R8" t="str"/>
-      <x:c r="S8" t="str"/>
-      <x:c r="T8" t="str"/>
-      <x:c r="U8" t="str"/>
-      <x:c r="V8" t="str"/>
+      <x:c r="N8"/>
+      <x:c r="O8"/>
+      <x:c r="P8"/>
+      <x:c r="Q8"/>
+      <x:c r="R8"/>
+      <x:c r="S8"/>
+      <x:c r="T8"/>
+      <x:c r="U8"/>
+      <x:c r="V8"/>
       <x:c r="W8" t="str">
         <x:v>2026-10-02</x:v>
       </x:c>
@@ -1069,29 +1069,29 @@
       <x:c r="Z8" t="str">
         <x:v>2026-10-02</x:v>
       </x:c>
-      <x:c r="AA8" t="str"/>
-      <x:c r="AB8" t="str"/>
-      <x:c r="AC8" t="str"/>
-      <x:c r="AD8" t="str"/>
-      <x:c r="AE8" t="str"/>
-      <x:c r="AF8" t="str"/>
-      <x:c r="AG8" t="str"/>
-      <x:c r="AH8" t="str"/>
-      <x:c r="AI8" t="str"/>
-      <x:c r="AJ8" t="str"/>
-      <x:c r="AK8" t="str"/>
-      <x:c r="AL8" t="str"/>
-      <x:c r="AM8" t="str"/>
-      <x:c r="AN8" t="str"/>
-      <x:c r="AO8" t="str"/>
-      <x:c r="AP8" t="str"/>
-      <x:c r="AQ8" t="str"/>
-      <x:c r="AR8" t="str"/>
-      <x:c r="AS8" t="str"/>
-      <x:c r="AT8" t="str"/>
-      <x:c r="AU8" t="str"/>
-      <x:c r="AV8" t="str"/>
-      <x:c r="AW8" t="str"/>
+      <x:c r="AA8"/>
+      <x:c r="AB8"/>
+      <x:c r="AC8"/>
+      <x:c r="AD8"/>
+      <x:c r="AE8"/>
+      <x:c r="AF8"/>
+      <x:c r="AG8"/>
+      <x:c r="AH8"/>
+      <x:c r="AI8"/>
+      <x:c r="AJ8"/>
+      <x:c r="AK8"/>
+      <x:c r="AL8"/>
+      <x:c r="AM8"/>
+      <x:c r="AN8"/>
+      <x:c r="AO8"/>
+      <x:c r="AP8"/>
+      <x:c r="AQ8"/>
+      <x:c r="AR8"/>
+      <x:c r="AS8"/>
+      <x:c r="AT8"/>
+      <x:c r="AU8"/>
+      <x:c r="AV8"/>
+      <x:c r="AW8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
@@ -1127,50 +1127,50 @@
       <x:c r="K9" t="str">
         <x:v>Datev Planned on: 2026-09-24, How Many: 1, Activity Type: Seminar / Conference / Workshop, Name Of Organization Planned with: Institute of Architects of Pakistan IAP, Remarks/Result: A day of ideas, conversations, and new possibilities around AI and the future of architecture in Pakistan.  From thought-provoking discussions to meaningful exchanges, “AI &amp; The Future of Architecture in Pakistan” brought together architects, educators, students, and design thinkers to explore how technology is reshaping the way we imagine and create our built environment., Planned: Yes, Scheduled: Yes</x:v>
       </x:c>
-      <x:c r="L9" t="str"/>
-      <x:c r="M9" t="str"/>
-      <x:c r="N9" t="str"/>
-      <x:c r="O9" t="str"/>
-      <x:c r="P9" t="str"/>
-      <x:c r="Q9" t="str"/>
+      <x:c r="L9"/>
+      <x:c r="M9"/>
+      <x:c r="N9"/>
+      <x:c r="O9"/>
+      <x:c r="P9"/>
+      <x:c r="Q9"/>
       <x:c r="R9" t="str">
         <x:v>Evidence Attached: files::6abdf5ba43240_WhatsApp_Image_2026-10-01_at_10.54.27.jpeg</x:v>
       </x:c>
-      <x:c r="S9" t="str"/>
-      <x:c r="T9" t="str"/>
-      <x:c r="U9" t="str"/>
-      <x:c r="V9" t="str"/>
+      <x:c r="S9"/>
+      <x:c r="T9"/>
+      <x:c r="U9"/>
+      <x:c r="V9"/>
       <x:c r="W9" t="str">
         <x:v>2026-10-24</x:v>
       </x:c>
       <x:c r="X9" t="str">
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="Y9" t="str"/>
-      <x:c r="Z9" t="str"/>
-      <x:c r="AA9" t="str"/>
-      <x:c r="AB9" t="str"/>
-      <x:c r="AC9" t="str"/>
-      <x:c r="AD9" t="str"/>
-      <x:c r="AE9" t="str"/>
-      <x:c r="AF9" t="str"/>
-      <x:c r="AG9" t="str"/>
-      <x:c r="AH9" t="str"/>
-      <x:c r="AI9" t="str"/>
-      <x:c r="AJ9" t="str"/>
-      <x:c r="AK9" t="str"/>
-      <x:c r="AL9" t="str"/>
-      <x:c r="AM9" t="str"/>
-      <x:c r="AN9" t="str"/>
-      <x:c r="AO9" t="str"/>
-      <x:c r="AP9" t="str"/>
-      <x:c r="AQ9" t="str"/>
-      <x:c r="AR9" t="str"/>
-      <x:c r="AS9" t="str"/>
-      <x:c r="AT9" t="str"/>
-      <x:c r="AU9" t="str"/>
-      <x:c r="AV9" t="str"/>
-      <x:c r="AW9" t="str"/>
+      <x:c r="Y9"/>
+      <x:c r="Z9"/>
+      <x:c r="AA9"/>
+      <x:c r="AB9"/>
+      <x:c r="AC9"/>
+      <x:c r="AD9"/>
+      <x:c r="AE9"/>
+      <x:c r="AF9"/>
+      <x:c r="AG9"/>
+      <x:c r="AH9"/>
+      <x:c r="AI9"/>
+      <x:c r="AJ9"/>
+      <x:c r="AK9"/>
+      <x:c r="AL9"/>
+      <x:c r="AM9"/>
+      <x:c r="AN9"/>
+      <x:c r="AO9"/>
+      <x:c r="AP9"/>
+      <x:c r="AQ9"/>
+      <x:c r="AR9"/>
+      <x:c r="AS9"/>
+      <x:c r="AT9"/>
+      <x:c r="AU9"/>
+      <x:c r="AV9"/>
+      <x:c r="AW9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
@@ -1203,7 +1203,7 @@
       <x:c r="J10" t="str">
         <x:v>Department of Islamic Studies</x:v>
       </x:c>
-      <x:c r="K10" t="str"/>
+      <x:c r="K10"/>
       <x:c r="L10" t="str">
         <x:v>Partner Institution: Ehsan TV, Country: Pakistan, MOU Type: Academic, Key Activities: Islamic Content, Students training, Status: Completed, Evidence: files::6abcea4746c11_MOU_with_Al-Ehsan_TV.pdf | Partner Institution: Bait ul Noor, Country: Pakistan, MOU Type: Academic, Key Activities: Research and outreach, Status: Under Process</x:v>
       </x:c>
@@ -1225,7 +1225,7 @@
 Expected Outcome: Students will gain deeper subject knowledge, develop critical thinking, and broaden their academic and intellectual perspectives. | Planned Activity / Event: Departmental Annual Tour, Tentative Date: 2026-12-05, Objective / Expected Outcome: Objective: To provide students with an opportunity for educational exposure, social interaction, and recreational learning in an informal environment.
 Expected Outcome: Students will develop stronger interpersonal skills, teamwork, and a sense of collaboration while gaining meaningful educational and recreational experiences.</x:v>
       </x:c>
-      <x:c r="R10" t="str"/>
+      <x:c r="R10"/>
       <x:c r="S10" t="str">
         <x:v>o	Media talks and public lectures by HOD and faculty.</x:v>
       </x:c>
@@ -1265,24 +1265,24 @@
       <x:c r="AE10" t="str">
         <x:v>o	Future International MoUs and Webinars</x:v>
       </x:c>
-      <x:c r="AF10" t="str"/>
-      <x:c r="AG10" t="str"/>
-      <x:c r="AH10" t="str"/>
-      <x:c r="AI10" t="str"/>
-      <x:c r="AJ10" t="str"/>
-      <x:c r="AK10" t="str"/>
-      <x:c r="AL10" t="str"/>
-      <x:c r="AM10" t="str"/>
-      <x:c r="AN10" t="str"/>
-      <x:c r="AO10" t="str"/>
-      <x:c r="AP10" t="str"/>
-      <x:c r="AQ10" t="str"/>
-      <x:c r="AR10" t="str"/>
-      <x:c r="AS10" t="str"/>
-      <x:c r="AT10" t="str"/>
-      <x:c r="AU10" t="str"/>
-      <x:c r="AV10" t="str"/>
-      <x:c r="AW10" t="str"/>
+      <x:c r="AF10"/>
+      <x:c r="AG10"/>
+      <x:c r="AH10"/>
+      <x:c r="AI10"/>
+      <x:c r="AJ10"/>
+      <x:c r="AK10"/>
+      <x:c r="AL10"/>
+      <x:c r="AM10"/>
+      <x:c r="AN10"/>
+      <x:c r="AO10"/>
+      <x:c r="AP10"/>
+      <x:c r="AQ10"/>
+      <x:c r="AR10"/>
+      <x:c r="AS10"/>
+      <x:c r="AT10"/>
+      <x:c r="AU10"/>
+      <x:c r="AV10"/>
+      <x:c r="AW10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
@@ -1315,7 +1315,7 @@
       <x:c r="J11" t="str">
         <x:v>Department of Islamic Studies</x:v>
       </x:c>
-      <x:c r="K11" t="str"/>
+      <x:c r="K11"/>
       <x:c r="L11" t="str">
         <x:v>Partner Institution: Ehsan TV, Country: Pakistan, MOU Type: Academic, Key Activities: Islamic Content, Students training, Status: Completed, Evidence: files::6abcea4746c11_MOU_with_Al-Ehsan_TV.pdf | Partner Institution: Bait ul Noor, Country: Pakistan, MOU Type: Academic, Key Activities: Research and outreach, Status: Under Process</x:v>
       </x:c>
@@ -1337,7 +1337,7 @@
 Expected Outcome: Students will gain deeper subject knowledge, develop critical thinking, and broaden their academic and intellectual perspectives. | Planned Activity / Event: Departmental Annual Tour, Tentative Date: 2026-12-05, Objective / Expected Outcome: Objective: To provide students with an opportunity for educational exposure, social interaction, and recreational learning in an informal environment.
 Expected Outcome: Students will develop stronger interpersonal skills, teamwork, and a sense of collaboration while gaining meaningful educational and recreational experiences.</x:v>
       </x:c>
-      <x:c r="R11" t="str"/>
+      <x:c r="R11"/>
       <x:c r="S11" t="str">
         <x:v>o	Media talks and public lectures by HOD and faculty.</x:v>
       </x:c>
@@ -1377,24 +1377,24 @@
       <x:c r="AE11" t="str">
         <x:v>o	Future International MoUs and Webinars</x:v>
       </x:c>
-      <x:c r="AF11" t="str"/>
-      <x:c r="AG11" t="str"/>
-      <x:c r="AH11" t="str"/>
-      <x:c r="AI11" t="str"/>
-      <x:c r="AJ11" t="str"/>
-      <x:c r="AK11" t="str"/>
-      <x:c r="AL11" t="str"/>
-      <x:c r="AM11" t="str"/>
-      <x:c r="AN11" t="str"/>
-      <x:c r="AO11" t="str"/>
-      <x:c r="AP11" t="str"/>
-      <x:c r="AQ11" t="str"/>
-      <x:c r="AR11" t="str"/>
-      <x:c r="AS11" t="str"/>
-      <x:c r="AT11" t="str"/>
-      <x:c r="AU11" t="str"/>
-      <x:c r="AV11" t="str"/>
-      <x:c r="AW11" t="str"/>
+      <x:c r="AF11"/>
+      <x:c r="AG11"/>
+      <x:c r="AH11"/>
+      <x:c r="AI11"/>
+      <x:c r="AJ11"/>
+      <x:c r="AK11"/>
+      <x:c r="AL11"/>
+      <x:c r="AM11"/>
+      <x:c r="AN11"/>
+      <x:c r="AO11"/>
+      <x:c r="AP11"/>
+      <x:c r="AQ11"/>
+      <x:c r="AR11"/>
+      <x:c r="AS11"/>
+      <x:c r="AT11"/>
+      <x:c r="AU11"/>
+      <x:c r="AV11"/>
+      <x:c r="AW11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
@@ -1427,7 +1427,7 @@
       <x:c r="J12" t="str">
         <x:v>Department of Islamic Studies</x:v>
       </x:c>
-      <x:c r="K12" t="str"/>
+      <x:c r="K12"/>
       <x:c r="L12" t="str">
         <x:v>Partner Institution: Ehsan TV, Country: Pakistan, MOU Type: Academic, Key Activities: Islamic Content, Students training, Status: Completed, Evidence: files::6abcea4746c11_MOU_with_Al-Ehsan_TV.pdf | Partner Institution: Bait ul Noor, Country: Pakistan, MOU Type: Academic, Key Activities: Research and outreach, Status: Under Process</x:v>
       </x:c>
@@ -1449,7 +1449,7 @@
 Expected Outcome: Students will gain deeper subject knowledge, develop critical thinking, and broaden their academic and intellectual perspectives. | Planned Activity / Event: Departmental Annual Tour, Tentative Date: 2026-12-05, Objective / Expected Outcome: Objective: To provide students with an opportunity for educational exposure, social interaction, and recreational learning in an informal environment.
 Expected Outcome: Students will develop stronger interpersonal skills, teamwork, and a sense of collaboration while gaining meaningful educational and recreational experiences.</x:v>
       </x:c>
-      <x:c r="R12" t="str"/>
+      <x:c r="R12"/>
       <x:c r="S12" t="str">
         <x:v>o	Media talks and public lectures by HOD and faculty.</x:v>
       </x:c>
@@ -1489,24 +1489,24 @@
       <x:c r="AE12" t="str">
         <x:v>o	Future International MoUs and Webinars</x:v>
       </x:c>
-      <x:c r="AF12" t="str"/>
-      <x:c r="AG12" t="str"/>
-      <x:c r="AH12" t="str"/>
-      <x:c r="AI12" t="str"/>
-      <x:c r="AJ12" t="str"/>
-      <x:c r="AK12" t="str"/>
-      <x:c r="AL12" t="str"/>
-      <x:c r="AM12" t="str"/>
-      <x:c r="AN12" t="str"/>
-      <x:c r="AO12" t="str"/>
-      <x:c r="AP12" t="str"/>
-      <x:c r="AQ12" t="str"/>
-      <x:c r="AR12" t="str"/>
-      <x:c r="AS12" t="str"/>
-      <x:c r="AT12" t="str"/>
-      <x:c r="AU12" t="str"/>
-      <x:c r="AV12" t="str"/>
-      <x:c r="AW12" t="str"/>
+      <x:c r="AF12"/>
+      <x:c r="AG12"/>
+      <x:c r="AH12"/>
+      <x:c r="AI12"/>
+      <x:c r="AJ12"/>
+      <x:c r="AK12"/>
+      <x:c r="AL12"/>
+      <x:c r="AM12"/>
+      <x:c r="AN12"/>
+      <x:c r="AO12"/>
+      <x:c r="AP12"/>
+      <x:c r="AQ12"/>
+      <x:c r="AR12"/>
+      <x:c r="AS12"/>
+      <x:c r="AT12"/>
+      <x:c r="AU12"/>
+      <x:c r="AV12"/>
+      <x:c r="AW12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
@@ -1542,7 +1542,7 @@
       <x:c r="K13" t="str">
         <x:v>Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Title Parliament in Action, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Title Data  Management Analysis Pivoting and Visualization using Excel and Google sheets, Planned: Yes, Scheduled: Yes | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: Workshop on QGIS for data visualization through heat maps, Planned: Yes, Scheduled: Yes | Activity Type: IV, How Many: 1, Name Of Organization Planned with: Industrial Visit Millat Tractors, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Islamic Economic System  Modern Day Challenges, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Rational Consumer Bahaviour and Climate change, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Prospects of Pakistan Economy, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Environmental Challenges and Role of Youth, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Industrial Development, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture How to Think Design and Execute Research in Emerging Economies, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Understanding Time Series From RealWorld Data to Economic Forecasting, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Understanding Time Series From RealWorld Data to Economic Forecasting, Planned: Yes, Scheduled: Yes</x:v>
       </x:c>
-      <x:c r="L13" t="str"/>
+      <x:c r="L13"/>
       <x:c r="M13" t="str">
         <x:v>Company: the</x:v>
       </x:c>
@@ -1552,8 +1552,8 @@
       <x:c r="O13" t="str">
         <x:v>New Proposals Initiated: Ongoing research projects will be shared while compiling the final report.</x:v>
       </x:c>
-      <x:c r="P13" t="str"/>
-      <x:c r="Q13" t="str"/>
+      <x:c r="P13"/>
+      <x:c r="Q13"/>
       <x:c r="R13" t="str">
         <x:v>Remarks/Folder Reference/URLs: will be shared later while compiling the final file.</x:v>
       </x:c>
@@ -1563,8 +1563,8 @@
       <x:c r="T13" t="str">
         <x:v>The boys of intermediate standard at the Crescent College, Lahore</x:v>
       </x:c>
-      <x:c r="U13" t="str"/>
-      <x:c r="V13" t="str"/>
+      <x:c r="U13"/>
+      <x:c r="V13"/>
       <x:c r="W13" t="str">
         <x:v>2026-07-30</x:v>
       </x:c>
@@ -1577,31 +1577,31 @@
       <x:c r="Z13" t="str">
         <x:v>2026-09-21</x:v>
       </x:c>
-      <x:c r="AA13" t="str"/>
+      <x:c r="AA13"/>
       <x:c r="AB13" t="str">
         <x:v>The Department of Economics has plans for internationalisation through international conferences and seminars.</x:v>
       </x:c>
-      <x:c r="AC13" t="str"/>
-      <x:c r="AD13" t="str"/>
-      <x:c r="AE13" t="str"/>
-      <x:c r="AF13" t="str"/>
-      <x:c r="AG13" t="str"/>
-      <x:c r="AH13" t="str"/>
-      <x:c r="AI13" t="str"/>
-      <x:c r="AJ13" t="str"/>
-      <x:c r="AK13" t="str"/>
-      <x:c r="AL13" t="str"/>
-      <x:c r="AM13" t="str"/>
-      <x:c r="AN13" t="str"/>
-      <x:c r="AO13" t="str"/>
-      <x:c r="AP13" t="str"/>
-      <x:c r="AQ13" t="str"/>
-      <x:c r="AR13" t="str"/>
-      <x:c r="AS13" t="str"/>
-      <x:c r="AT13" t="str"/>
-      <x:c r="AU13" t="str"/>
-      <x:c r="AV13" t="str"/>
-      <x:c r="AW13" t="str"/>
+      <x:c r="AC13"/>
+      <x:c r="AD13"/>
+      <x:c r="AE13"/>
+      <x:c r="AF13"/>
+      <x:c r="AG13"/>
+      <x:c r="AH13"/>
+      <x:c r="AI13"/>
+      <x:c r="AJ13"/>
+      <x:c r="AK13"/>
+      <x:c r="AL13"/>
+      <x:c r="AM13"/>
+      <x:c r="AN13"/>
+      <x:c r="AO13"/>
+      <x:c r="AP13"/>
+      <x:c r="AQ13"/>
+      <x:c r="AR13"/>
+      <x:c r="AS13"/>
+      <x:c r="AT13"/>
+      <x:c r="AU13"/>
+      <x:c r="AV13"/>
+      <x:c r="AW13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
@@ -1637,7 +1637,7 @@
       <x:c r="K14" t="str">
         <x:v>Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Title Parliament in Action, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Title Data  Management Analysis Pivoting and Visualization using Excel and Google sheets, Planned: Yes, Scheduled: Yes | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: Workshop on QGIS for data visualization through heat maps, Planned: Yes, Scheduled: Yes | Activity Type: IV, How Many: 1, Name Of Organization Planned with: Industrial Visit Millat Tractors, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Islamic Economic System  Modern Day Challenges, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Rational Consumer Bahaviour and Climate change, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Prospects of Pakistan Economy, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Environmental Challenges and Role of Youth, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Industrial Development, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture How to Think Design and Execute Research in Emerging Economies, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Understanding Time Series From RealWorld Data to Economic Forecasting, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Understanding Time Series From RealWorld Data to Economic Forecasting, Planned: Yes, Scheduled: Yes</x:v>
       </x:c>
-      <x:c r="L14" t="str"/>
+      <x:c r="L14"/>
       <x:c r="M14" t="str">
         <x:v>Company: the</x:v>
       </x:c>
@@ -1647,8 +1647,8 @@
       <x:c r="O14" t="str">
         <x:v>New Proposals Initiated: Ongoing research projects will be shared while compiling the final report.</x:v>
       </x:c>
-      <x:c r="P14" t="str"/>
-      <x:c r="Q14" t="str"/>
+      <x:c r="P14"/>
+      <x:c r="Q14"/>
       <x:c r="R14" t="str">
         <x:v>Remarks/Folder Reference/URLs: will be shared later while compiling the final file.</x:v>
       </x:c>
@@ -1658,8 +1658,8 @@
       <x:c r="T14" t="str">
         <x:v>The boys of intermediate standard at the Crescent College, Lahore</x:v>
       </x:c>
-      <x:c r="U14" t="str"/>
-      <x:c r="V14" t="str"/>
+      <x:c r="U14"/>
+      <x:c r="V14"/>
       <x:c r="W14" t="str">
         <x:v>2026-07-30</x:v>
       </x:c>
@@ -1672,31 +1672,31 @@
       <x:c r="Z14" t="str">
         <x:v>2026-09-21</x:v>
       </x:c>
-      <x:c r="AA14" t="str"/>
+      <x:c r="AA14"/>
       <x:c r="AB14" t="str">
         <x:v>The Department of Economics has plans for internationalisation through international conferences and seminars.</x:v>
       </x:c>
-      <x:c r="AC14" t="str"/>
-      <x:c r="AD14" t="str"/>
-      <x:c r="AE14" t="str"/>
-      <x:c r="AF14" t="str"/>
-      <x:c r="AG14" t="str"/>
-      <x:c r="AH14" t="str"/>
-      <x:c r="AI14" t="str"/>
-      <x:c r="AJ14" t="str"/>
-      <x:c r="AK14" t="str"/>
-      <x:c r="AL14" t="str"/>
-      <x:c r="AM14" t="str"/>
-      <x:c r="AN14" t="str"/>
-      <x:c r="AO14" t="str"/>
-      <x:c r="AP14" t="str"/>
-      <x:c r="AQ14" t="str"/>
-      <x:c r="AR14" t="str"/>
-      <x:c r="AS14" t="str"/>
-      <x:c r="AT14" t="str"/>
-      <x:c r="AU14" t="str"/>
-      <x:c r="AV14" t="str"/>
-      <x:c r="AW14" t="str"/>
+      <x:c r="AC14"/>
+      <x:c r="AD14"/>
+      <x:c r="AE14"/>
+      <x:c r="AF14"/>
+      <x:c r="AG14"/>
+      <x:c r="AH14"/>
+      <x:c r="AI14"/>
+      <x:c r="AJ14"/>
+      <x:c r="AK14"/>
+      <x:c r="AL14"/>
+      <x:c r="AM14"/>
+      <x:c r="AN14"/>
+      <x:c r="AO14"/>
+      <x:c r="AP14"/>
+      <x:c r="AQ14"/>
+      <x:c r="AR14"/>
+      <x:c r="AS14"/>
+      <x:c r="AT14"/>
+      <x:c r="AU14"/>
+      <x:c r="AV14"/>
+      <x:c r="AW14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
@@ -1732,7 +1732,7 @@
       <x:c r="K15" t="str">
         <x:v>Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Title Parliament in Action, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Title Data  Management Analysis Pivoting and Visualization using Excel and Google sheets, Planned: Yes, Scheduled: Yes | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: Workshop on QGIS for data visualization through heat maps, Planned: Yes, Scheduled: Yes | Activity Type: IV, How Many: 1, Name Of Organization Planned with: Industrial Visit Millat Tractors, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Islamic Economic System  Modern Day Challenges, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Rational Consumer Bahaviour and Climate change, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Prospects of Pakistan Economy, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Environmental Challenges and Role of Youth, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Industrial Development, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture How to Think Design and Execute Research in Emerging Economies, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Understanding Time Series From RealWorld Data to Economic Forecasting, Planned: Yes, Scheduled: Yes | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Guest Lecture Understanding Time Series From RealWorld Data to Economic Forecasting, Planned: Yes, Scheduled: Yes</x:v>
       </x:c>
-      <x:c r="L15" t="str"/>
+      <x:c r="L15"/>
       <x:c r="M15" t="str">
         <x:v>Company: the</x:v>
       </x:c>
@@ -1742,8 +1742,8 @@
       <x:c r="O15" t="str">
         <x:v>New Proposals Initiated: Ongoing research projects will be shared while compiling the final report.</x:v>
       </x:c>
-      <x:c r="P15" t="str"/>
-      <x:c r="Q15" t="str"/>
+      <x:c r="P15"/>
+      <x:c r="Q15"/>
       <x:c r="R15" t="str">
         <x:v>Remarks/Folder Reference/URLs: will be shared later while compiling the final file.</x:v>
       </x:c>
@@ -1753,8 +1753,8 @@
       <x:c r="T15" t="str">
         <x:v>The boys of intermediate standard at the Crescent College, Lahore</x:v>
       </x:c>
-      <x:c r="U15" t="str"/>
-      <x:c r="V15" t="str"/>
+      <x:c r="U15"/>
+      <x:c r="V15"/>
       <x:c r="W15" t="str">
         <x:v>2026-07-30</x:v>
       </x:c>
@@ -1767,31 +1767,31 @@
       <x:c r="Z15" t="str">
         <x:v>2026-09-21</x:v>
       </x:c>
-      <x:c r="AA15" t="str"/>
+      <x:c r="AA15"/>
       <x:c r="AB15" t="str">
         <x:v>The Department of Economics has plans for internationalisation through international conferences and seminars.</x:v>
       </x:c>
-      <x:c r="AC15" t="str"/>
-      <x:c r="AD15" t="str"/>
-      <x:c r="AE15" t="str"/>
-      <x:c r="AF15" t="str"/>
-      <x:c r="AG15" t="str"/>
-      <x:c r="AH15" t="str"/>
-      <x:c r="AI15" t="str"/>
-      <x:c r="AJ15" t="str"/>
-      <x:c r="AK15" t="str"/>
-      <x:c r="AL15" t="str"/>
-      <x:c r="AM15" t="str"/>
-      <x:c r="AN15" t="str"/>
-      <x:c r="AO15" t="str"/>
-      <x:c r="AP15" t="str"/>
-      <x:c r="AQ15" t="str"/>
-      <x:c r="AR15" t="str"/>
-      <x:c r="AS15" t="str"/>
-      <x:c r="AT15" t="str"/>
-      <x:c r="AU15" t="str"/>
-      <x:c r="AV15" t="str"/>
-      <x:c r="AW15" t="str"/>
+      <x:c r="AC15"/>
+      <x:c r="AD15"/>
+      <x:c r="AE15"/>
+      <x:c r="AF15"/>
+      <x:c r="AG15"/>
+      <x:c r="AH15"/>
+      <x:c r="AI15"/>
+      <x:c r="AJ15"/>
+      <x:c r="AK15"/>
+      <x:c r="AL15"/>
+      <x:c r="AM15"/>
+      <x:c r="AN15"/>
+      <x:c r="AO15"/>
+      <x:c r="AP15"/>
+      <x:c r="AQ15"/>
+      <x:c r="AR15"/>
+      <x:c r="AS15"/>
+      <x:c r="AT15"/>
+      <x:c r="AU15"/>
+      <x:c r="AV15"/>
+      <x:c r="AW15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
@@ -1824,47 +1824,47 @@
       <x:c r="J16" t="str">
         <x:v>Department of Technology</x:v>
       </x:c>
-      <x:c r="K16" t="str"/>
+      <x:c r="K16"/>
       <x:c r="L16" t="str">
         <x:v>Partner Institution: Codecoy Technologies, Country: Pakistan, MOU Type: Academic, Key Activities: MoU with Information Engineering Technology, Status: Under Process</x:v>
       </x:c>
-      <x:c r="M16" t="str"/>
-      <x:c r="N16" t="str"/>
-      <x:c r="O16" t="str"/>
-      <x:c r="P16" t="str"/>
-      <x:c r="Q16" t="str"/>
-      <x:c r="R16" t="str"/>
-      <x:c r="S16" t="str"/>
-      <x:c r="T16" t="str"/>
-      <x:c r="U16" t="str"/>
-      <x:c r="V16" t="str"/>
-      <x:c r="W16" t="str"/>
-      <x:c r="X16" t="str"/>
-      <x:c r="Y16" t="str"/>
-      <x:c r="Z16" t="str"/>
-      <x:c r="AA16" t="str"/>
-      <x:c r="AB16" t="str"/>
-      <x:c r="AC16" t="str"/>
-      <x:c r="AD16" t="str"/>
-      <x:c r="AE16" t="str"/>
-      <x:c r="AF16" t="str"/>
-      <x:c r="AG16" t="str"/>
-      <x:c r="AH16" t="str"/>
-      <x:c r="AI16" t="str"/>
-      <x:c r="AJ16" t="str"/>
-      <x:c r="AK16" t="str"/>
-      <x:c r="AL16" t="str"/>
-      <x:c r="AM16" t="str"/>
-      <x:c r="AN16" t="str"/>
-      <x:c r="AO16" t="str"/>
-      <x:c r="AP16" t="str"/>
-      <x:c r="AQ16" t="str"/>
-      <x:c r="AR16" t="str"/>
-      <x:c r="AS16" t="str"/>
-      <x:c r="AT16" t="str"/>
-      <x:c r="AU16" t="str"/>
-      <x:c r="AV16" t="str"/>
-      <x:c r="AW16" t="str"/>
+      <x:c r="M16"/>
+      <x:c r="N16"/>
+      <x:c r="O16"/>
+      <x:c r="P16"/>
+      <x:c r="Q16"/>
+      <x:c r="R16"/>
+      <x:c r="S16"/>
+      <x:c r="T16"/>
+      <x:c r="U16"/>
+      <x:c r="V16"/>
+      <x:c r="W16"/>
+      <x:c r="X16"/>
+      <x:c r="Y16"/>
+      <x:c r="Z16"/>
+      <x:c r="AA16"/>
+      <x:c r="AB16"/>
+      <x:c r="AC16"/>
+      <x:c r="AD16"/>
+      <x:c r="AE16"/>
+      <x:c r="AF16"/>
+      <x:c r="AG16"/>
+      <x:c r="AH16"/>
+      <x:c r="AI16"/>
+      <x:c r="AJ16"/>
+      <x:c r="AK16"/>
+      <x:c r="AL16"/>
+      <x:c r="AM16"/>
+      <x:c r="AN16"/>
+      <x:c r="AO16"/>
+      <x:c r="AP16"/>
+      <x:c r="AQ16"/>
+      <x:c r="AR16"/>
+      <x:c r="AS16"/>
+      <x:c r="AT16"/>
+      <x:c r="AU16"/>
+      <x:c r="AV16"/>
+      <x:c r="AW16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
@@ -1897,47 +1897,47 @@
       <x:c r="J17" t="str">
         <x:v>Department of Technology</x:v>
       </x:c>
-      <x:c r="K17" t="str"/>
+      <x:c r="K17"/>
       <x:c r="L17" t="str">
         <x:v>Partner Institution: Codecoy Technologies, Country: Pakistan, MOU Type: Academic, Key Activities: MoU with Information Engineering Technology, Status: Under Process</x:v>
       </x:c>
-      <x:c r="M17" t="str"/>
-      <x:c r="N17" t="str"/>
-      <x:c r="O17" t="str"/>
-      <x:c r="P17" t="str"/>
-      <x:c r="Q17" t="str"/>
-      <x:c r="R17" t="str"/>
-      <x:c r="S17" t="str"/>
-      <x:c r="T17" t="str"/>
-      <x:c r="U17" t="str"/>
-      <x:c r="V17" t="str"/>
-      <x:c r="W17" t="str"/>
-      <x:c r="X17" t="str"/>
-      <x:c r="Y17" t="str"/>
-      <x:c r="Z17" t="str"/>
-      <x:c r="AA17" t="str"/>
-      <x:c r="AB17" t="str"/>
-      <x:c r="AC17" t="str"/>
-      <x:c r="AD17" t="str"/>
-      <x:c r="AE17" t="str"/>
-      <x:c r="AF17" t="str"/>
-      <x:c r="AG17" t="str"/>
-      <x:c r="AH17" t="str"/>
-      <x:c r="AI17" t="str"/>
-      <x:c r="AJ17" t="str"/>
-      <x:c r="AK17" t="str"/>
-      <x:c r="AL17" t="str"/>
-      <x:c r="AM17" t="str"/>
-      <x:c r="AN17" t="str"/>
-      <x:c r="AO17" t="str"/>
-      <x:c r="AP17" t="str"/>
-      <x:c r="AQ17" t="str"/>
-      <x:c r="AR17" t="str"/>
-      <x:c r="AS17" t="str"/>
-      <x:c r="AT17" t="str"/>
-      <x:c r="AU17" t="str"/>
-      <x:c r="AV17" t="str"/>
-      <x:c r="AW17" t="str"/>
+      <x:c r="M17"/>
+      <x:c r="N17"/>
+      <x:c r="O17"/>
+      <x:c r="P17"/>
+      <x:c r="Q17"/>
+      <x:c r="R17"/>
+      <x:c r="S17"/>
+      <x:c r="T17"/>
+      <x:c r="U17"/>
+      <x:c r="V17"/>
+      <x:c r="W17"/>
+      <x:c r="X17"/>
+      <x:c r="Y17"/>
+      <x:c r="Z17"/>
+      <x:c r="AA17"/>
+      <x:c r="AB17"/>
+      <x:c r="AC17"/>
+      <x:c r="AD17"/>
+      <x:c r="AE17"/>
+      <x:c r="AF17"/>
+      <x:c r="AG17"/>
+      <x:c r="AH17"/>
+      <x:c r="AI17"/>
+      <x:c r="AJ17"/>
+      <x:c r="AK17"/>
+      <x:c r="AL17"/>
+      <x:c r="AM17"/>
+      <x:c r="AN17"/>
+      <x:c r="AO17"/>
+      <x:c r="AP17"/>
+      <x:c r="AQ17"/>
+      <x:c r="AR17"/>
+      <x:c r="AS17"/>
+      <x:c r="AT17"/>
+      <x:c r="AU17"/>
+      <x:c r="AV17"/>
+      <x:c r="AW17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
@@ -1973,48 +1973,48 @@
       <x:c r="K18" t="str">
         <x:v>Activity Type: Others, How Many: 1, Name Of Organization Planned with: A visit to Haveli Nau Nihal Singh, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-09-16</x:v>
       </x:c>
-      <x:c r="L18" t="str"/>
-      <x:c r="M18" t="str"/>
-      <x:c r="N18" t="str"/>
-      <x:c r="O18" t="str"/>
-      <x:c r="P18" t="str"/>
-      <x:c r="Q18" t="str"/>
+      <x:c r="L18"/>
+      <x:c r="M18"/>
+      <x:c r="N18"/>
+      <x:c r="O18"/>
+      <x:c r="P18"/>
+      <x:c r="Q18"/>
       <x:c r="R18" t="str">
         <x:v>Item: Other, Evidence Attached: files::6aab71af6cfef_image__8_.png, Remarks/Folder Reference/URLs: https://www.instagram.com/uol.soa.official/</x:v>
       </x:c>
-      <x:c r="S18" t="str"/>
-      <x:c r="T18" t="str"/>
-      <x:c r="U18" t="str"/>
-      <x:c r="V18" t="str"/>
+      <x:c r="S18"/>
+      <x:c r="T18"/>
+      <x:c r="U18"/>
+      <x:c r="V18"/>
       <x:c r="W18" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
-      <x:c r="X18" t="str"/>
-      <x:c r="Y18" t="str"/>
-      <x:c r="Z18" t="str"/>
-      <x:c r="AA18" t="str"/>
-      <x:c r="AB18" t="str"/>
-      <x:c r="AC18" t="str"/>
-      <x:c r="AD18" t="str"/>
-      <x:c r="AE18" t="str"/>
-      <x:c r="AF18" t="str"/>
-      <x:c r="AG18" t="str"/>
-      <x:c r="AH18" t="str"/>
-      <x:c r="AI18" t="str"/>
-      <x:c r="AJ18" t="str"/>
-      <x:c r="AK18" t="str"/>
-      <x:c r="AL18" t="str"/>
-      <x:c r="AM18" t="str"/>
-      <x:c r="AN18" t="str"/>
-      <x:c r="AO18" t="str"/>
-      <x:c r="AP18" t="str"/>
-      <x:c r="AQ18" t="str"/>
-      <x:c r="AR18" t="str"/>
-      <x:c r="AS18" t="str"/>
-      <x:c r="AT18" t="str"/>
-      <x:c r="AU18" t="str"/>
-      <x:c r="AV18" t="str"/>
-      <x:c r="AW18" t="str"/>
+      <x:c r="X18"/>
+      <x:c r="Y18"/>
+      <x:c r="Z18"/>
+      <x:c r="AA18"/>
+      <x:c r="AB18"/>
+      <x:c r="AC18"/>
+      <x:c r="AD18"/>
+      <x:c r="AE18"/>
+      <x:c r="AF18"/>
+      <x:c r="AG18"/>
+      <x:c r="AH18"/>
+      <x:c r="AI18"/>
+      <x:c r="AJ18"/>
+      <x:c r="AK18"/>
+      <x:c r="AL18"/>
+      <x:c r="AM18"/>
+      <x:c r="AN18"/>
+      <x:c r="AO18"/>
+      <x:c r="AP18"/>
+      <x:c r="AQ18"/>
+      <x:c r="AR18"/>
+      <x:c r="AS18"/>
+      <x:c r="AT18"/>
+      <x:c r="AU18"/>
+      <x:c r="AV18"/>
+      <x:c r="AW18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
@@ -2050,46 +2050,46 @@
       <x:c r="K19" t="str">
         <x:v>Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Ar Syed Rameez Haider, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-09-15, Remarks/Result: A sessin exploring wood and brick beyond their constructional use—their material qualities, character, craft, and potential to shape architectural experience. | </x:v>
       </x:c>
-      <x:c r="L19" t="str"/>
-      <x:c r="M19" t="str"/>
-      <x:c r="N19" t="str"/>
-      <x:c r="O19" t="str"/>
-      <x:c r="P19" t="str"/>
-      <x:c r="Q19" t="str"/>
+      <x:c r="L19"/>
+      <x:c r="M19"/>
+      <x:c r="N19"/>
+      <x:c r="O19"/>
+      <x:c r="P19"/>
+      <x:c r="Q19"/>
       <x:c r="R19" t="str">
         <x:v>Item: Guest Visit/Meeting Reports, Evidence Attached: files::6aab700cefc6a_WhatsApp_Image_2026-09-17_at_09.43.35.jpeg, Remarks/Folder Reference/URLs: Ar Syed Rameez Haider</x:v>
       </x:c>
-      <x:c r="S19" t="str"/>
-      <x:c r="T19" t="str"/>
-      <x:c r="U19" t="str"/>
-      <x:c r="V19" t="str"/>
-      <x:c r="W19" t="str"/>
-      <x:c r="X19" t="str"/>
-      <x:c r="Y19" t="str"/>
-      <x:c r="Z19" t="str"/>
-      <x:c r="AA19" t="str"/>
-      <x:c r="AB19" t="str"/>
-      <x:c r="AC19" t="str"/>
-      <x:c r="AD19" t="str"/>
-      <x:c r="AE19" t="str"/>
-      <x:c r="AF19" t="str"/>
-      <x:c r="AG19" t="str"/>
-      <x:c r="AH19" t="str"/>
-      <x:c r="AI19" t="str"/>
-      <x:c r="AJ19" t="str"/>
-      <x:c r="AK19" t="str"/>
-      <x:c r="AL19" t="str"/>
-      <x:c r="AM19" t="str"/>
-      <x:c r="AN19" t="str"/>
-      <x:c r="AO19" t="str"/>
-      <x:c r="AP19" t="str"/>
-      <x:c r="AQ19" t="str"/>
-      <x:c r="AR19" t="str"/>
-      <x:c r="AS19" t="str"/>
-      <x:c r="AT19" t="str"/>
-      <x:c r="AU19" t="str"/>
-      <x:c r="AV19" t="str"/>
-      <x:c r="AW19" t="str"/>
+      <x:c r="S19"/>
+      <x:c r="T19"/>
+      <x:c r="U19"/>
+      <x:c r="V19"/>
+      <x:c r="W19"/>
+      <x:c r="X19"/>
+      <x:c r="Y19"/>
+      <x:c r="Z19"/>
+      <x:c r="AA19"/>
+      <x:c r="AB19"/>
+      <x:c r="AC19"/>
+      <x:c r="AD19"/>
+      <x:c r="AE19"/>
+      <x:c r="AF19"/>
+      <x:c r="AG19"/>
+      <x:c r="AH19"/>
+      <x:c r="AI19"/>
+      <x:c r="AJ19"/>
+      <x:c r="AK19"/>
+      <x:c r="AL19"/>
+      <x:c r="AM19"/>
+      <x:c r="AN19"/>
+      <x:c r="AO19"/>
+      <x:c r="AP19"/>
+      <x:c r="AQ19"/>
+      <x:c r="AR19"/>
+      <x:c r="AS19"/>
+      <x:c r="AT19"/>
+      <x:c r="AU19"/>
+      <x:c r="AV19"/>
+      <x:c r="AW19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
@@ -2125,46 +2125,46 @@
       <x:c r="K20" t="str">
         <x:v>Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Ar Syed Rameez Haider, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-09-15, Remarks/Result: A sessin exploring wood and brick beyond their constructional use—their material qualities, character, craft, and potential to shape architectural experience. | </x:v>
       </x:c>
-      <x:c r="L20" t="str"/>
-      <x:c r="M20" t="str"/>
-      <x:c r="N20" t="str"/>
-      <x:c r="O20" t="str"/>
-      <x:c r="P20" t="str"/>
-      <x:c r="Q20" t="str"/>
+      <x:c r="L20"/>
+      <x:c r="M20"/>
+      <x:c r="N20"/>
+      <x:c r="O20"/>
+      <x:c r="P20"/>
+      <x:c r="Q20"/>
       <x:c r="R20" t="str">
         <x:v>Item: Guest Visit/Meeting Reports, Evidence Attached: files::6aab700cefc6a_WhatsApp_Image_2026-09-17_at_09.43.35.jpeg, Remarks/Folder Reference/URLs: Ar Syed Rameez Haider</x:v>
       </x:c>
-      <x:c r="S20" t="str"/>
-      <x:c r="T20" t="str"/>
-      <x:c r="U20" t="str"/>
-      <x:c r="V20" t="str"/>
-      <x:c r="W20" t="str"/>
-      <x:c r="X20" t="str"/>
-      <x:c r="Y20" t="str"/>
-      <x:c r="Z20" t="str"/>
-      <x:c r="AA20" t="str"/>
-      <x:c r="AB20" t="str"/>
-      <x:c r="AC20" t="str"/>
-      <x:c r="AD20" t="str"/>
-      <x:c r="AE20" t="str"/>
-      <x:c r="AF20" t="str"/>
-      <x:c r="AG20" t="str"/>
-      <x:c r="AH20" t="str"/>
-      <x:c r="AI20" t="str"/>
-      <x:c r="AJ20" t="str"/>
-      <x:c r="AK20" t="str"/>
-      <x:c r="AL20" t="str"/>
-      <x:c r="AM20" t="str"/>
-      <x:c r="AN20" t="str"/>
-      <x:c r="AO20" t="str"/>
-      <x:c r="AP20" t="str"/>
-      <x:c r="AQ20" t="str"/>
-      <x:c r="AR20" t="str"/>
-      <x:c r="AS20" t="str"/>
-      <x:c r="AT20" t="str"/>
-      <x:c r="AU20" t="str"/>
-      <x:c r="AV20" t="str"/>
-      <x:c r="AW20" t="str"/>
+      <x:c r="S20"/>
+      <x:c r="T20"/>
+      <x:c r="U20"/>
+      <x:c r="V20"/>
+      <x:c r="W20"/>
+      <x:c r="X20"/>
+      <x:c r="Y20"/>
+      <x:c r="Z20"/>
+      <x:c r="AA20"/>
+      <x:c r="AB20"/>
+      <x:c r="AC20"/>
+      <x:c r="AD20"/>
+      <x:c r="AE20"/>
+      <x:c r="AF20"/>
+      <x:c r="AG20"/>
+      <x:c r="AH20"/>
+      <x:c r="AI20"/>
+      <x:c r="AJ20"/>
+      <x:c r="AK20"/>
+      <x:c r="AL20"/>
+      <x:c r="AM20"/>
+      <x:c r="AN20"/>
+      <x:c r="AO20"/>
+      <x:c r="AP20"/>
+      <x:c r="AQ20"/>
+      <x:c r="AR20"/>
+      <x:c r="AS20"/>
+      <x:c r="AT20"/>
+      <x:c r="AU20"/>
+      <x:c r="AV20"/>
+      <x:c r="AW20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
@@ -2266,30 +2266,30 @@
         <x:v>German Leprosy and Tuberculosis relief Association  HQ Wuerzburg Germany 
 Marie adelaide Leprosy center Karachi Pkaistan</x:v>
       </x:c>
-      <x:c r="AD21" t="str"/>
-      <x:c r="AE21" t="str"/>
+      <x:c r="AD21"/>
+      <x:c r="AE21"/>
       <x:c r="AF21" t="str">
         <x:v>0: files::6aa924b990834_WhatsApp_Image_2026-09-15_at_3.52.12_PM__1_.jpeg, 1: files::6aa924b99083b_WhatsApp_Image_2026-09-15_at_3.52.12_PM.jpeg, 2: files::6aa924d21771b_WhatsApp_Image_2026-09-15_at_3.52.12_PM__2_.jpeg | 0: files::6aa924b990834_WhatsApp_Image_2026-09-15_at_3.52.12_PM__1_.jpeg, 1: files::6aa924b99083b_WhatsApp_Image_2026-09-15_at_3.52.12_PM.jpeg, 2: files::6aa924d21771b_WhatsApp_Image_2026-09-15_at_3.52.12_PM__2_.jpeg | 0: f, 1: i, 2: l, 3: e, 4: s, 5: :, 6: :, 7: 6, 8: a, 9: a, 10: 9, 11: 2, 12: 4, 13: b, 14: 9, 15: 9, 16: 0, 17: 8, 18: 3, 19: 4, 20: _, 21: W, 22: h, 23: a, 24: t, 25: s, 26: A, 27: p, 28: p, 29: _, 30: I, 31: m, 32: a, 33: g, 34: e, 35: _, 36: 2, 37: 0, 38: 2, 39: 6, 40: -, 41: 0, 42: 9, 43: -, 44: 1, 45: 5, 46: _, 47: a, 48: t, 49: _, 50: 3, 51: ., 52: 5, 53: 2, 54: ., 55: 1, 56: 2, 57: _, 58: P, 59: M, 60: _, 61: _, 62: 1, 63: _, 64: ., 65: j, 66: p, 67: e, 68: g | 0: f, 1: i, 2: l, 3: e, 4: s, 5: :, 6: :, 7: 6, 8: a, 9: a, 10: 9, 11: 2, 12: 4, 13: b, 14: 9, 15: 9, 16: 0, 17: 8, 18: 3, 19: b, 20: _, 21: W, 22: h, 23: a, 24: t, 25: s, 26: A, 27: p, 28: p, 29: _, 30: I, 31: m, 32: a, 33: g, 34: e, 35: _, 36: 2, 37: 0, 38: 2, 39: 6, 40: -, 41: 0, 42: 9, 43: -, 44: 1, 45: 5, 46: _, 47: a, 48: t, 49: _, 50: 3, 51: ., 52: 5, 53: 2, 54: ., 55: 1, 56: 2, 57: _, 58: P, 59: M, 60: ., 61: j, 62: p, 63: e, 64: g | 0: f, 1: i, 2: l, 3: e, 4: s, 5: :, 6: :, 7: 6, 8: a, 9: a, 10: 9, 11: 2, 12: 4, 13: d, 14: 2, 15: 1, 16: 7, 17: 7, 18: 1, 19: b, 20: _, 21: W, 22: h, 23: a, 24: t, 25: s, 26: A, 27: p, 28: p, 29: _, 30: I, 31: m, 32: a, 33: g, 34: e, 35: _, 36: 2, 37: 0, 38: 2, 39: 6, 40: -, 41: 0, 42: 9, 43: -, 44: 1, 45: 5, 46: _, 47: a, 48: t, 49: _, 50: 3, 51: ., 52: 5, 53: 2, 54: ., 55: 1, 56: 2, 57: _, 58: P, 59: M, 60: _, 61: _, 62: 2, 63: _, 64: ., 65: j, 66: p, 67: e, 68: g | 0: files::6aa924b990834_WhatsApp_Image_2026-09-15_at_3.52.12_PM__1_.jpeg, 1: files::6aa924b99083b_WhatsApp_Image_2026-09-15_at_3.52.12_PM.jpeg, 2: files::6aa924d21771b_WhatsApp_Image_2026-09-15_at_3.52.12_PM__2_.jpeg | 0: files::6aa924b990834_WhatsApp_Image_2026-09-15_at_3.52.12_PM__1_.jpeg, 1: files::6aa924b99083b_WhatsApp_Image_2026-09-15_at_3.52.12_PM.jpeg, 2: files::6aa924d21771b_WhatsApp_Image_2026-09-15_at_3.52.12_PM__2_.jpeg | 0: files::6aa924b990834_WhatsApp_Image_2026-09-15_at_3.52.12_PM__1_.jpeg, 1: files::6aa924b99083b_WhatsApp_Image_2026-09-15_at_3.52.12_PM.jpeg, 2: files::6aa924d21771b_WhatsApp_Image_2026-09-15_at_3.52.12_PM__2_.jpeg | 0: files::6aa924b990834_WhatsApp_Image_2026-09-15_at_3.52.12_PM__1_.jpeg, 1: files::6aa924b99083b_WhatsApp_Image_2026-09-15_at_3.52.12_PM.jpeg, 2: files::6aa924d21771b_WhatsApp_Image_2026-09-15_at_3.52.12_PM__2_.jpeg | 0: files::6aa924b990834_WhatsApp_Image_2026-09-15_at_3.52.12_PM__1_.jpeg, 1: files::6aa924b99083b_WhatsApp_Image_2026-09-15_at_3.52.12_PM.jpeg, 2: files::6aa924d21771b_WhatsApp_Image_2026-09-15_at_3.52.12_PM__2_.jpeg | 0: files::6aa924b990834_WhatsApp_Image_2026-09-15_at_3.52.12_PM__1_.jpeg, 1: files::6aa924b99083b_WhatsApp_Image_2026-09-15_at_3.52.12_PM.jpeg, 2: files::6aa924d21771b_WhatsApp_Image_2026-09-15_at_3.52.12_PM__2_.jpeg | 0: files::6aa924b990834_WhatsApp_Image_2026-09-15_at_3.52.12_PM__1_.jpeg, 1: files::6aa924b99083b_WhatsApp_Image_2026-09-15_at_3.52.12_PM.jpeg, 2: files::6aa924d21771b_WhatsApp_Image_2026-09-15_at_3.52.12_PM__2_.jpeg | 0: files::6aa924b990834_WhatsApp_Image_2026-09-15_at_3.52.12_PM__1_.jpeg, 1: files::6aa924b99083b_WhatsApp_Image_2026-09-15_at_3.52.12_PM.jpeg, 2: files::6aa924d21771b_WhatsApp_Image_2026-09-15_at_3.52.12_PM__2_.jpeg | 0: files::6aa924b990834_WhatsApp_Image_2026-09-15_at_3.52.12_PM__1_.jpeg, 1: files::6aa924b99083b_WhatsApp_Image_2026-09-15_at_3.52.12_PM.jpeg, 2: files::6aa924d21771b_WhatsApp_Image_2026-09-15_at_3.52.12_PM__2_.jpeg | 0: files::6aa924b990834_WhatsApp_Image_2026-09-15_at_3.52.12_PM__1_.jpeg, 1: files::6aa924b99083b_WhatsApp_Image_2026-09-15_at_3.52.12_PM.jpeg, 2: files::6aa924d21771b_WhatsApp_Image_2026-09-15_at_3.52.12_PM__2_.jpeg</x:v>
       </x:c>
       <x:c r="AG21" t="str">
         <x:v>0: files::6aaa1eb94c603_WhatsApp_Image_2026-09-15_at_4.54.59_PM__1_.jpeg, 1: files::6aaa1eb93b76e_WhatsApp_Image_2026-09-15_at_4.54.59_PM.jpeg | 0: files::6aaa1eb94c603_WhatsApp_Image_2026-09-15_at_4.54.59_PM__1_.jpeg, 1: files::6aaa1eb93b76e_WhatsApp_Image_2026-09-15_at_4.54.59_PM.jpeg | 0: f, 1: i, 2: l, 3: e, 4: s, 5: :, 6: :, 7: 6, 8: a, 9: a, 10: a, 11: 1, 12: e, 13: b, 14: 9, 15: 4, 16: c, 17: 6, 18: 0, 19: 3, 20: _, 21: W, 22: h, 23: a, 24: t, 25: s, 26: A, 27: p, 28: p, 29: _, 30: I, 31: m, 32: a, 33: g, 34: e, 35: _, 36: 2, 37: 0, 38: 2, 39: 6, 40: -, 41: 0, 42: 9, 43: -, 44: 1, 45: 5, 46: _, 47: a, 48: t, 49: _, 50: 4, 51: ., 52: 5, 53: 4, 54: ., 55: 5, 56: 9, 57: _, 58: P, 59: M, 60: _, 61: _, 62: 1, 63: _, 64: ., 65: j, 66: p, 67: e, 68: g | 0: f, 1: i, 2: l, 3: e, 4: s, 5: :, 6: :, 7: 6, 8: a, 9: a, 10: a, 11: 1, 12: e, 13: b, 14: 9, 15: 3, 16: b, 17: 7, 18: 6, 19: e, 20: _, 21: W, 22: h, 23: a, 24: t, 25: s, 26: A, 27: p, 28: p, 29: _, 30: I, 31: m, 32: a, 33: g, 34: e, 35: _, 36: 2, 37: 0, 38: 2, 39: 6, 40: -, 41: 0, 42: 9, 43: -, 44: 1, 45: 5, 46: _, 47: a, 48: t, 49: _, 50: 4, 51: ., 52: 5, 53: 4, 54: ., 55: 5, 56: 9, 57: _, 58: P, 59: M, 60: ., 61: j, 62: p, 63: e, 64: g</x:v>
       </x:c>
-      <x:c r="AH21" t="str"/>
-      <x:c r="AI21" t="str"/>
-      <x:c r="AJ21" t="str"/>
-      <x:c r="AK21" t="str"/>
-      <x:c r="AL21" t="str"/>
-      <x:c r="AM21" t="str"/>
-      <x:c r="AN21" t="str"/>
-      <x:c r="AO21" t="str"/>
-      <x:c r="AP21" t="str"/>
-      <x:c r="AQ21" t="str"/>
-      <x:c r="AR21" t="str"/>
-      <x:c r="AS21" t="str"/>
-      <x:c r="AT21" t="str"/>
-      <x:c r="AU21" t="str"/>
-      <x:c r="AV21" t="str"/>
-      <x:c r="AW21" t="str"/>
+      <x:c r="AH21"/>
+      <x:c r="AI21"/>
+      <x:c r="AJ21"/>
+      <x:c r="AK21"/>
+      <x:c r="AL21"/>
+      <x:c r="AM21"/>
+      <x:c r="AN21"/>
+      <x:c r="AO21"/>
+      <x:c r="AP21"/>
+      <x:c r="AQ21"/>
+      <x:c r="AR21"/>
+      <x:c r="AS21"/>
+      <x:c r="AT21"/>
+      <x:c r="AU21"/>
+      <x:c r="AV21"/>
+      <x:c r="AW21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
@@ -2325,46 +2325,46 @@
       <x:c r="K22" t="str">
         <x:v>Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Ar. Zeenia Hussain, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-09-10, Remarks/Result: insightful guest lecture on “Different Aspects of Brick Construction in Residential Units,” as part of our 3rd year studio project | Activity Type: GLIT, How Many: 16, Name Of Organization Planned with: Ahmed Mukhtar, CEO, Al Imam Enterprises, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-08-31, Remarks/Result: Ahmed Mukhtar will be conducting insightful and professional lectures for 4th year Urban Design throughout the semester, drawing from his vast professional experience in the field.</x:v>
       </x:c>
-      <x:c r="L22" t="str"/>
-      <x:c r="M22" t="str"/>
-      <x:c r="N22" t="str"/>
-      <x:c r="O22" t="str"/>
-      <x:c r="P22" t="str"/>
-      <x:c r="Q22" t="str"/>
+      <x:c r="L22"/>
+      <x:c r="M22"/>
+      <x:c r="N22"/>
+      <x:c r="O22"/>
+      <x:c r="P22"/>
+      <x:c r="Q22"/>
       <x:c r="R22" t="str">
         <x:v>Item: Event Flyers/Reports, Evidence Attached: files::6aa3cb2c0d107_WhatsApp_Image_2026-09-11_at_14.33.57.jpeg, Remarks/Folder Reference/URLs: insightful guest lecture on “Different Aspects of Brick Construction in Residential Units,” as part of our 3rd year studio project</x:v>
       </x:c>
-      <x:c r="S22" t="str"/>
-      <x:c r="T22" t="str"/>
-      <x:c r="U22" t="str"/>
-      <x:c r="V22" t="str"/>
-      <x:c r="W22" t="str"/>
-      <x:c r="X22" t="str"/>
-      <x:c r="Y22" t="str"/>
-      <x:c r="Z22" t="str"/>
-      <x:c r="AA22" t="str"/>
-      <x:c r="AB22" t="str"/>
-      <x:c r="AC22" t="str"/>
-      <x:c r="AD22" t="str"/>
-      <x:c r="AE22" t="str"/>
-      <x:c r="AF22" t="str"/>
-      <x:c r="AG22" t="str"/>
-      <x:c r="AH22" t="str"/>
-      <x:c r="AI22" t="str"/>
-      <x:c r="AJ22" t="str"/>
-      <x:c r="AK22" t="str"/>
-      <x:c r="AL22" t="str"/>
-      <x:c r="AM22" t="str"/>
-      <x:c r="AN22" t="str"/>
-      <x:c r="AO22" t="str"/>
-      <x:c r="AP22" t="str"/>
-      <x:c r="AQ22" t="str"/>
-      <x:c r="AR22" t="str"/>
-      <x:c r="AS22" t="str"/>
-      <x:c r="AT22" t="str"/>
-      <x:c r="AU22" t="str"/>
-      <x:c r="AV22" t="str"/>
-      <x:c r="AW22" t="str"/>
+      <x:c r="S22"/>
+      <x:c r="T22"/>
+      <x:c r="U22"/>
+      <x:c r="V22"/>
+      <x:c r="W22"/>
+      <x:c r="X22"/>
+      <x:c r="Y22"/>
+      <x:c r="Z22"/>
+      <x:c r="AA22"/>
+      <x:c r="AB22"/>
+      <x:c r="AC22"/>
+      <x:c r="AD22"/>
+      <x:c r="AE22"/>
+      <x:c r="AF22"/>
+      <x:c r="AG22"/>
+      <x:c r="AH22"/>
+      <x:c r="AI22"/>
+      <x:c r="AJ22"/>
+      <x:c r="AK22"/>
+      <x:c r="AL22"/>
+      <x:c r="AM22"/>
+      <x:c r="AN22"/>
+      <x:c r="AO22"/>
+      <x:c r="AP22"/>
+      <x:c r="AQ22"/>
+      <x:c r="AR22"/>
+      <x:c r="AS22"/>
+      <x:c r="AT22"/>
+      <x:c r="AU22"/>
+      <x:c r="AV22"/>
+      <x:c r="AW22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
@@ -2397,49 +2397,49 @@
       <x:c r="J23" t="str">
         <x:v>Department of Technology</x:v>
       </x:c>
-      <x:c r="K23" t="str"/>
+      <x:c r="K23"/>
       <x:c r="L23" t="str">
         <x:v>Partner Institution: Fast Cables, Country: Pakistan, MOU Type: Academic, Key Activities: In process, Status: Under Process</x:v>
       </x:c>
       <x:c r="M23" t="str">
         <x:v>Company: About 70 Companies, Sector: Mechanical, Civil, Architecture, Biomedical &amp; IET, Number Of students: 200, Duration: 4 Months, Type: Planned, Mode: Physical</x:v>
       </x:c>
-      <x:c r="N23" t="str"/>
-      <x:c r="O23" t="str"/>
-      <x:c r="P23" t="str"/>
-      <x:c r="Q23" t="str"/>
-      <x:c r="R23" t="str"/>
-      <x:c r="S23" t="str"/>
-      <x:c r="T23" t="str"/>
-      <x:c r="U23" t="str"/>
-      <x:c r="V23" t="str"/>
-      <x:c r="W23" t="str"/>
-      <x:c r="X23" t="str"/>
-      <x:c r="Y23" t="str"/>
-      <x:c r="Z23" t="str"/>
-      <x:c r="AA23" t="str"/>
-      <x:c r="AB23" t="str"/>
-      <x:c r="AC23" t="str"/>
-      <x:c r="AD23" t="str"/>
-      <x:c r="AE23" t="str"/>
-      <x:c r="AF23" t="str"/>
-      <x:c r="AG23" t="str"/>
-      <x:c r="AH23" t="str"/>
-      <x:c r="AI23" t="str"/>
-      <x:c r="AJ23" t="str"/>
-      <x:c r="AK23" t="str"/>
-      <x:c r="AL23" t="str"/>
-      <x:c r="AM23" t="str"/>
-      <x:c r="AN23" t="str"/>
-      <x:c r="AO23" t="str"/>
-      <x:c r="AP23" t="str"/>
-      <x:c r="AQ23" t="str"/>
-      <x:c r="AR23" t="str"/>
-      <x:c r="AS23" t="str"/>
-      <x:c r="AT23" t="str"/>
-      <x:c r="AU23" t="str"/>
-      <x:c r="AV23" t="str"/>
-      <x:c r="AW23" t="str"/>
+      <x:c r="N23"/>
+      <x:c r="O23"/>
+      <x:c r="P23"/>
+      <x:c r="Q23"/>
+      <x:c r="R23"/>
+      <x:c r="S23"/>
+      <x:c r="T23"/>
+      <x:c r="U23"/>
+      <x:c r="V23"/>
+      <x:c r="W23"/>
+      <x:c r="X23"/>
+      <x:c r="Y23"/>
+      <x:c r="Z23"/>
+      <x:c r="AA23"/>
+      <x:c r="AB23"/>
+      <x:c r="AC23"/>
+      <x:c r="AD23"/>
+      <x:c r="AE23"/>
+      <x:c r="AF23"/>
+      <x:c r="AG23"/>
+      <x:c r="AH23"/>
+      <x:c r="AI23"/>
+      <x:c r="AJ23"/>
+      <x:c r="AK23"/>
+      <x:c r="AL23"/>
+      <x:c r="AM23"/>
+      <x:c r="AN23"/>
+      <x:c r="AO23"/>
+      <x:c r="AP23"/>
+      <x:c r="AQ23"/>
+      <x:c r="AR23"/>
+      <x:c r="AS23"/>
+      <x:c r="AT23"/>
+      <x:c r="AU23"/>
+      <x:c r="AV23"/>
+      <x:c r="AW23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
@@ -2481,7 +2481,7 @@
       <x:c r="M24" t="str">
         <x:v>Company: Pakistan Health and Population Welfare Department, Sector: Government, Number Of students: 3, Duration: 6 weeks, Type: Intership, Mode: Physical</x:v>
       </x:c>
-      <x:c r="N24" t="str"/>
+      <x:c r="N24"/>
       <x:c r="O24" t="str">
         <x:v>New Proposals Initiated: 2, External Collaborators: University of Chongqing, Focus Areas / Themes: Health and Social Issues, Current Status: Drafting</x:v>
       </x:c>
@@ -2533,24 +2533,24 @@
       <x:c r="AE24" t="str">
         <x:v>Visit to Women Development Department with students.</x:v>
       </x:c>
-      <x:c r="AF24" t="str"/>
-      <x:c r="AG24" t="str"/>
-      <x:c r="AH24" t="str"/>
-      <x:c r="AI24" t="str"/>
-      <x:c r="AJ24" t="str"/>
-      <x:c r="AK24" t="str"/>
-      <x:c r="AL24" t="str"/>
-      <x:c r="AM24" t="str"/>
-      <x:c r="AN24" t="str"/>
-      <x:c r="AO24" t="str"/>
-      <x:c r="AP24" t="str"/>
-      <x:c r="AQ24" t="str"/>
-      <x:c r="AR24" t="str"/>
-      <x:c r="AS24" t="str"/>
-      <x:c r="AT24" t="str"/>
-      <x:c r="AU24" t="str"/>
-      <x:c r="AV24" t="str"/>
-      <x:c r="AW24" t="str"/>
+      <x:c r="AF24"/>
+      <x:c r="AG24"/>
+      <x:c r="AH24"/>
+      <x:c r="AI24"/>
+      <x:c r="AJ24"/>
+      <x:c r="AK24"/>
+      <x:c r="AL24"/>
+      <x:c r="AM24"/>
+      <x:c r="AN24"/>
+      <x:c r="AO24"/>
+      <x:c r="AP24"/>
+      <x:c r="AQ24"/>
+      <x:c r="AR24"/>
+      <x:c r="AS24"/>
+      <x:c r="AT24"/>
+      <x:c r="AU24"/>
+      <x:c r="AV24"/>
+      <x:c r="AW24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
@@ -2586,21 +2586,21 @@
       <x:c r="K25" t="str">
         <x:v>Activity Type: IP, How Many: 190, Name Of Organization Planned with: UOTH and Social Security Hospital Multan Road, Lahore, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-02-23, Remarks/Result: Internship completed | Activity Type: IV, How Many: 50, Name Of Organization Planned with: Pak-Korea Nutrition Center (PKNC), Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-04-29, Remarks/Result: Training and Visit completed</x:v>
       </x:c>
-      <x:c r="L25" t="str"/>
+      <x:c r="L25"/>
       <x:c r="M25" t="str">
         <x:v>Company: UOTH and Social Security Hospital Multan Road, Lahore, Sector: Hospital, Number Of students: 190, Duration: 3 months, Type: Intership, Mode: Physical, Evidence: files::6aa03b7157e52_Email_clinical.jpeg,files::6aa03b894277e_Social_Security_Multan_Road_roster_final.pdf,files::6aa03b896028d_UOLTH_Roaster_Final.pdf | Company: Pak-Korea Nutrition Center (PKNC), Sector: Research Institute, Number Of students: 50, Duration: 2 days, Type: Planned, Mode: Physical, Evidence: files::6aa03c0b946c5_Cerificate_PKNC.jpeg,files::6aa03c408c460_WhatsApp_Image_2026-09-08_at_2.57.13_PM__1_.jpeg,files::6aa03c4271da7_WhatsApp_Image_2026-09-08_at_2.57.13_PM.jpeg,files::6aa03c424d4e8_WhatsApp_Image_2026-09-08_at_2.57.14_PM__1_.jpeg,files::6aa03c41e5cb0_WhatsApp_Image_2026-09-08_at_2.57.14_PM.jpeg</x:v>
       </x:c>
-      <x:c r="N25" t="str"/>
-      <x:c r="O25" t="str"/>
-      <x:c r="P25" t="str"/>
-      <x:c r="Q25" t="str"/>
+      <x:c r="N25"/>
+      <x:c r="O25"/>
+      <x:c r="P25"/>
+      <x:c r="Q25"/>
       <x:c r="R25" t="str">
         <x:v>Item: Photo Evidence</x:v>
       </x:c>
-      <x:c r="S25" t="str"/>
-      <x:c r="T25" t="str"/>
-      <x:c r="U25" t="str"/>
-      <x:c r="V25" t="str"/>
+      <x:c r="S25"/>
+      <x:c r="T25"/>
+      <x:c r="U25"/>
+      <x:c r="V25"/>
       <x:c r="W25" t="str">
         <x:v>2026-09-04</x:v>
       </x:c>
@@ -2616,28 +2616,28 @@
       <x:c r="AA25" t="str">
         <x:v>+923216427809</x:v>
       </x:c>
-      <x:c r="AB25" t="str"/>
-      <x:c r="AC25" t="str"/>
-      <x:c r="AD25" t="str"/>
-      <x:c r="AE25" t="str"/>
-      <x:c r="AF25" t="str"/>
-      <x:c r="AG25" t="str"/>
-      <x:c r="AH25" t="str"/>
-      <x:c r="AI25" t="str"/>
-      <x:c r="AJ25" t="str"/>
-      <x:c r="AK25" t="str"/>
-      <x:c r="AL25" t="str"/>
-      <x:c r="AM25" t="str"/>
-      <x:c r="AN25" t="str"/>
-      <x:c r="AO25" t="str"/>
-      <x:c r="AP25" t="str"/>
-      <x:c r="AQ25" t="str"/>
-      <x:c r="AR25" t="str"/>
-      <x:c r="AS25" t="str"/>
-      <x:c r="AT25" t="str"/>
-      <x:c r="AU25" t="str"/>
-      <x:c r="AV25" t="str"/>
-      <x:c r="AW25" t="str"/>
+      <x:c r="AB25"/>
+      <x:c r="AC25"/>
+      <x:c r="AD25"/>
+      <x:c r="AE25"/>
+      <x:c r="AF25"/>
+      <x:c r="AG25"/>
+      <x:c r="AH25"/>
+      <x:c r="AI25"/>
+      <x:c r="AJ25"/>
+      <x:c r="AK25"/>
+      <x:c r="AL25"/>
+      <x:c r="AM25"/>
+      <x:c r="AN25"/>
+      <x:c r="AO25"/>
+      <x:c r="AP25"/>
+      <x:c r="AQ25"/>
+      <x:c r="AR25"/>
+      <x:c r="AS25"/>
+      <x:c r="AT25"/>
+      <x:c r="AU25"/>
+      <x:c r="AV25"/>
+      <x:c r="AW25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
@@ -2679,11 +2679,11 @@
       <x:c r="M26" t="str">
         <x:v>Company: Media / TV, Number Of students: 35, Sector: media, Duration: 6, Type: Intership, Mode: Physical, Evidence: files::6a8c518a7111e_School_of_Creative_Arts__Graduate_Productive_Employment__July_____December_2025.xlsx,files::6a8c5188d8fe2_School_of_Creative_Arts__Graduate_Productive_Employment_January_____June_2026.xlsx</x:v>
       </x:c>
-      <x:c r="N26" t="str"/>
-      <x:c r="O26" t="str"/>
-      <x:c r="P26" t="str"/>
-      <x:c r="Q26" t="str"/>
-      <x:c r="R26" t="str"/>
+      <x:c r="N26"/>
+      <x:c r="O26"/>
+      <x:c r="P26"/>
+      <x:c r="Q26"/>
+      <x:c r="R26"/>
       <x:c r="S26" t="str">
         <x:v>SOCA SDG Awareness and Sustainability Activities
 The School of Creative Arts (SOCA) actively participated in promoting the United Nations Sustainable Development Goals (SDGs) through a series of awareness and engagement activities focused on environmental sustainability, quality education, gender equality, and responsible citizenship.
@@ -2718,30 +2718,30 @@
       <x:c r="AA26" t="str">
         <x:v>00923444076539</x:v>
       </x:c>
-      <x:c r="AB26" t="str"/>
-      <x:c r="AC26" t="str"/>
-      <x:c r="AD26" t="str"/>
-      <x:c r="AE26" t="str"/>
+      <x:c r="AB26"/>
+      <x:c r="AC26"/>
+      <x:c r="AD26"/>
+      <x:c r="AE26"/>
       <x:c r="AF26" t="str">
         <x:v>0: files::6a82e8be675bf_WhatsApp_Image_2026-08-17_at_2.32.45_PM.jpeg, 1: files::6a82e8be6f048_WhatsApp_Image_2026-08-17_at_2.32.47_PM.jpeg, 2: files::6a82e8be6cb39_WhatsApp_Image_2026-08-17_at_PM.jpeg | 0: files::6a82e8be675bf_WhatsApp_Image_2026-08-17_at_2.32.45_PM.jpeg, 1: files::6a82e8be6f048_WhatsApp_Image_2026-08-17_at_2.32.47_PM.jpeg, 2: files::6a82e8be6cb39_WhatsApp_Image_2026-08-17_at_PM.jpeg | 0: f, 1: i, 2: l, 3: e, 4: s, 5: :, 6: :, 7: 6, 8: a, 9: 8, 10: 2, 11: e, 12: 8, 13: b, 14: e, 15: 6, 16: 7, 17: 5, 18: b, 19: f, 20: _, 21: W, 22: h, 23: a, 24: t, 25: s, 26: A, 27: p, 28: p, 29: _, 30: I, 31: m, 32: a, 33: g, 34: e, 35: _, 36: 2, 37: 0, 38: 2, 39: 6, 40: -, 41: 0, 42: 8, 43: -, 44: 1, 45: 7, 46: _, 47: a, 48: t, 49: _, 50: 2, 51: ., 52: 3, 53: 2, 54: ., 55: 4, 56: 5, 57: _, 58: P, 59: M, 60: ., 61: j, 62: p, 63: e, 64: g | 0: f, 1: i, 2: l, 3: e, 4: s, 5: :, 6: :, 7: 6, 8: a, 9: 8, 10: 2, 11: e, 12: 8, 13: b, 14: e, 15: 6, 16: f, 17: 0, 18: 4, 19: 8, 20: _, 21: W, 22: h, 23: a, 24: t, 25: s, 26: A, 27: p, 28: p, 29: _, 30: I, 31: m, 32: a, 33: g, 34: e, 35: _, 36: 2, 37: 0, 38: 2, 39: 6, 40: -, 41: 0, 42: 8, 43: -, 44: 1, 45: 7, 46: _, 47: a, 48: t, 49: _, 50: 2, 51: ., 52: 3, 53: 2, 54: ., 55: 4, 56: 7, 57: _, 58: P, 59: M, 60: ., 61: j, 62: p, 63: e, 64: g | 0: f, 1: i, 2: l, 3: e, 4: s, 5: :, 6: :, 7: 6, 8: a, 9: 8, 10: 2, 11: e, 12: 8, 13: b, 14: e, 15: 6, 16: c, 17: b, 18: 3, 19: 9, 20: _, 21: W, 22: h, 23: a, 24: t, 25: s, 26: A, 27: p, 28: p, 29: _, 30: I, 31: m, 32: a, 33: g, 34: e, 35: _, 36: 2, 37: 0, 38: 2, 39: 6, 40: -, 41: 0, 42: 8, 43: -, 44: 1, 45: 7, 46: _, 47: a, 48: t, 49: _, 50: P, 51: M, 52: ., 53: j, 54: p, 55: e, 56: g | 0: files::6a82e8be675bf_WhatsApp_Image_2026-08-17_at_2.32.45_PM.jpeg, 1: files::6a82e8be6f048_WhatsApp_Image_2026-08-17_at_2.32.47_PM.jpeg, 2: files::6a82e8be6cb39_WhatsApp_Image_2026-08-17_at_PM.jpeg | 0: files::6a82e8be675bf_WhatsApp_Image_2026-08-17_at_2.32.45_PM.jpeg, 1: files::6a82e8be6f048_WhatsApp_Image_2026-08-17_at_2.32.47_PM.jpeg, 2: files::6a82e8be6cb39_WhatsApp_Image_2026-08-17_at_PM.jpeg | 0: files::6a82e8be675bf_WhatsApp_Image_2026-08-17_at_2.32.45_PM.jpeg, 1: files::6a82e8be6f048_WhatsApp_Image_2026-08-17_at_2.32.47_PM.jpeg, 2: files::6a82e8be6cb39_WhatsApp_Image_2026-08-17_at_PM.jpeg | 0: files::6a82e8be675bf_WhatsApp_Image_2026-08-17_at_2.32.45_PM.jpeg, 1: files::6a82e8be6f048_WhatsApp_Image_2026-08-17_at_2.32.47_PM.jpeg, 2: files::6a82e8be6cb39_WhatsApp_Image_2026-08-17_at_PM.jpeg | 0: files::6a82e8be675bf_WhatsApp_Image_2026-08-17_at_2.32.45_PM.jpeg, 1: files::6a82e8be6f048_WhatsApp_Image_2026-08-17_at_2.32.47_PM.jpeg, 2: files::6a82e8be6cb39_WhatsApp_Image_2026-08-17_at_PM.jpeg | 0: files::6a82e8be675bf_WhatsApp_Image_2026-08-17_at_2.32.45_PM.jpeg, 1: files::6a82e8be6f048_WhatsApp_Image_2026-08-17_at_2.32.47_PM.jpeg, 2: files::6a82e8be6cb39_WhatsApp_Image_2026-08-17_at_PM.jpeg | 0: files::6a82e8be675bf_WhatsApp_Image_2026-08-17_at_2.32.45_PM.jpeg, 1: files::6a82e8be6f048_WhatsApp_Image_2026-08-17_at_2.32.47_PM.jpeg, 2: files::6a82e8be6cb39_WhatsApp_Image_2026-08-17_at_PM.jpeg | 0: files::6a82e8be675bf_WhatsApp_Image_2026-08-17_at_2.32.45_PM.jpeg, 1: files::6a82e8be6f048_WhatsApp_Image_2026-08-17_at_2.32.47_PM.jpeg, 2: files::6a82e8be6cb39_WhatsApp_Image_2026-08-17_at_PM.jpeg | 0: files::6a82e8be675bf_WhatsApp_Image_2026-08-17_at_2.32.45_PM.jpeg, 1: files::6a82e8be6f048_WhatsApp_Image_2026-08-17_at_2.32.47_PM.jpeg, 2: files::6a82e8be6cb39_WhatsApp_Image_2026-08-17_at_PM.jpeg | 0: files::6a82e8be675bf_WhatsApp_Image_2026-08-17_at_2.32.45_PM.jpeg, 1: files::6a82e8be6f048_WhatsApp_Image_2026-08-17_at_2.32.47_PM.jpeg, 2: files::6a82e8be6cb39_WhatsApp_Image_2026-08-17_at_PM.jpeg</x:v>
       </x:c>
-      <x:c r="AG26" t="str"/>
-      <x:c r="AH26" t="str"/>
-      <x:c r="AI26" t="str"/>
-      <x:c r="AJ26" t="str"/>
-      <x:c r="AK26" t="str"/>
-      <x:c r="AL26" t="str"/>
-      <x:c r="AM26" t="str"/>
-      <x:c r="AN26" t="str"/>
-      <x:c r="AO26" t="str"/>
-      <x:c r="AP26" t="str"/>
-      <x:c r="AQ26" t="str"/>
-      <x:c r="AR26" t="str"/>
-      <x:c r="AS26" t="str"/>
-      <x:c r="AT26" t="str"/>
-      <x:c r="AU26" t="str"/>
-      <x:c r="AV26" t="str"/>
-      <x:c r="AW26" t="str"/>
+      <x:c r="AG26"/>
+      <x:c r="AH26"/>
+      <x:c r="AI26"/>
+      <x:c r="AJ26"/>
+      <x:c r="AK26"/>
+      <x:c r="AL26"/>
+      <x:c r="AM26"/>
+      <x:c r="AN26"/>
+      <x:c r="AO26"/>
+      <x:c r="AP26"/>
+      <x:c r="AQ26"/>
+      <x:c r="AR26"/>
+      <x:c r="AS26"/>
+      <x:c r="AT26"/>
+      <x:c r="AU26"/>
+      <x:c r="AV26"/>
+      <x:c r="AW26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
@@ -2777,19 +2777,19 @@
       <x:c r="K27" t="str">
         <x:v>Activity Type: IV, How Many: 1, Name Of Organization Planned with: Post Harvest Research Center, AARI, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-04-21, Remarks/Result: Visited and gain practical knowledge | Activity Type: IV, How Many: 1, Name Of Organization Planned with: Pak Korea Nutrition Center, PKNC, Faisalabad, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-04-21, Remarks/Result: Look into research opportunities | Activity Type: Research Collaboration, How Many: 1, Name Of Organization Planned with: Punjab Agriculture &amp; Meat Company (PAMCO), Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-04-09, Remarks/Result: Gained Practical Knowledge | Activity Type: IV, How Many: 1, Name Of Organization Planned with: Bonjour Reliance Foods, Lahore, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-05-07, Remarks/Result: Visited and Gained Practical Knowledge | Activity Type: IV, How Many: 1</x:v>
       </x:c>
-      <x:c r="L27" t="str"/>
-      <x:c r="M27" t="str"/>
-      <x:c r="N27" t="str"/>
-      <x:c r="O27" t="str"/>
-      <x:c r="P27" t="str"/>
-      <x:c r="Q27" t="str"/>
+      <x:c r="L27"/>
+      <x:c r="M27"/>
+      <x:c r="N27"/>
+      <x:c r="O27"/>
+      <x:c r="P27"/>
+      <x:c r="Q27"/>
       <x:c r="R27" t="str">
         <x:v>Item: Other, Evidence Attached: files::6a6c745b191ff.pdf, Remarks/Folder Reference/URLs: Email Attached | Item: Photo Evidence, Evidence Attached: files::6a6c748d75ef7.jpeg, Remarks/Folder Reference/URLs: Photo attached | Item: Other, Evidence Attached: files::6a6c74b627bd3.pdf, Remarks/Folder Reference/URLs: Email Attached | Item: Photo Evidence, Evidence Attached: files::6a6c765ac5def.jpeg | Item: Other, Evidence Attached: files::6a6c76780b332.pdf, Remarks/Folder Reference/URLs: Email Attached | Item: Other, Evidence Attached: files::6a6c77203ee70.pdf, Remarks/Folder Reference/URLs: email | Item: Photo Evidence, Evidence Attached: files::6a6c773117358.jpeg, Remarks/Folder Reference/URLs: Photo Attached</x:v>
       </x:c>
-      <x:c r="S27" t="str"/>
-      <x:c r="T27" t="str"/>
-      <x:c r="U27" t="str"/>
-      <x:c r="V27" t="str"/>
+      <x:c r="S27"/>
+      <x:c r="T27"/>
+      <x:c r="U27"/>
+      <x:c r="V27"/>
       <x:c r="W27" t="str">
         <x:v>2026-06-15</x:v>
       </x:c>
@@ -2805,28 +2805,28 @@
       <x:c r="AA27" t="str">
         <x:v>+923454169626</x:v>
       </x:c>
-      <x:c r="AB27" t="str"/>
-      <x:c r="AC27" t="str"/>
-      <x:c r="AD27" t="str"/>
-      <x:c r="AE27" t="str"/>
-      <x:c r="AF27" t="str"/>
-      <x:c r="AG27" t="str"/>
-      <x:c r="AH27" t="str"/>
-      <x:c r="AI27" t="str"/>
-      <x:c r="AJ27" t="str"/>
-      <x:c r="AK27" t="str"/>
-      <x:c r="AL27" t="str"/>
-      <x:c r="AM27" t="str"/>
-      <x:c r="AN27" t="str"/>
-      <x:c r="AO27" t="str"/>
-      <x:c r="AP27" t="str"/>
-      <x:c r="AQ27" t="str"/>
-      <x:c r="AR27" t="str"/>
-      <x:c r="AS27" t="str"/>
-      <x:c r="AT27" t="str"/>
-      <x:c r="AU27" t="str"/>
-      <x:c r="AV27" t="str"/>
-      <x:c r="AW27" t="str"/>
+      <x:c r="AB27"/>
+      <x:c r="AC27"/>
+      <x:c r="AD27"/>
+      <x:c r="AE27"/>
+      <x:c r="AF27"/>
+      <x:c r="AG27"/>
+      <x:c r="AH27"/>
+      <x:c r="AI27"/>
+      <x:c r="AJ27"/>
+      <x:c r="AK27"/>
+      <x:c r="AL27"/>
+      <x:c r="AM27"/>
+      <x:c r="AN27"/>
+      <x:c r="AO27"/>
+      <x:c r="AP27"/>
+      <x:c r="AQ27"/>
+      <x:c r="AR27"/>
+      <x:c r="AS27"/>
+      <x:c r="AT27"/>
+      <x:c r="AU27"/>
+      <x:c r="AV27"/>
+      <x:c r="AW27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
@@ -2862,16 +2862,16 @@
       <x:c r="K28" t="str">
         <x:v>Activity Type: Research Collaboration, How Many: 1, Name Of Organization Planned with: Benadir Univeristy, Somalia, Planned: No, Scheduled: No, Datev Planned on: 2026-01-13 | Activity Type: Others, Name Of Organization Planned with: College of Dentistry, Planned: No, Scheduled: No, Datev Planned on: 2026-01-25, Remarks/Result: Recognizing Student Achievement &amp; Community Services | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: College of Dentistry, Planned: No, Scheduled: No, Datev Planned on: 2026-01-28, Remarks/Result: Pathway &amp; Prospective to Pursue DDS in the U.S.A (UCD Alumni talk) | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: University College of medicine &amp; Dentistry, Planned: No, Scheduled: No, Datev Planned on: 2026-02-02, Remarks/Result: Oath Taking Ceremony for Palestinian’s Students | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: University College of medicine &amp; Dentistry, Planned: No, Scheduled: No, Datev Planned on: 2026-03-02, Remarks/Result: Oath Taking Ceremony for BDS New Session 2026 | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: College of Dentistry, Planned: No, Scheduled: No, Datev Planned on: 2026-04-08, Remarks/Result: Impact That Matters: Strengthening Your Academic Profile and Global Recognition through Quality Publications | Activity Type: Others, Name Of Organization Planned with: Queen Mary University of London (QMUL), United Kingdom, Planned: No, Scheduled: No, Datev Planned on: 2026-04-13, Remarks/Result: Research Collaboration | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: College of Dentistry, Planned: No, Scheduled: No, Datev Planned on: 2026-05-13, Remarks/Result: Career Counselling Seminar at ULDH. | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: College of Dentistry, Planned: No, Scheduled: No, Datev Planned on: 2026-06-03 | Activity Type: Others, How Many: 1, Name Of Organization Planned with: Lahore Medical &amp; Dental College, Planned: No, Scheduled: No, Datev Planned on: 2026-06-04, Remarks/Result: Participation &amp; Achievements of UCD in LMDC Dentosphere 2026 Dental Inter-Collegiate Academic &amp; Sports Fiesta | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: University college of Medicine &amp; Dentistry, The university of Lahore, Planned: No, Scheduled: No, Datev Planned on: 2026-06-09, Remarks/Result: TEDx UCMD First Ever TED Talks | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: College of Dentistry, Planned: No, Scheduled: No, Datev Planned on: 2026-06-10, Remarks/Result: Beyond the Comfort Zone: Psychological Strategies for  Growth and Performance | Activity Type: Seminar / Conference / Workshop, Name Of Organization Planned with: College of Dentistry, Planned: No, Scheduled: No, Remarks/Result: (Throughout the year) Weekly Continuous Professional Development (CPD) Activity</x:v>
       </x:c>
-      <x:c r="L28" t="str"/>
-      <x:c r="M28" t="str"/>
+      <x:c r="L28"/>
+      <x:c r="M28"/>
       <x:c r="N28" t="str">
         <x:v>Activities Conducted: Alumni Talks,, Other Remarks: 1, Purpose &amp; Outcomes:: Pathway &amp; Prospective to Pursue DDS in the U.S.A. (UCD Alumni Talk), Feedback Highlights / Reflections:: UCMD hosted distinguished alumnus Dr. Adreel William George for an insightful session on “Pathway &amp; Prospective to Pursue DDS in the U.S.A.” The talk provided students with valuable guidance on admission pathways, requirements, and career opportunities for pursuing a DDS degree in the United States.</x:v>
       </x:c>
       <x:c r="O28" t="str">
         <x:v>New Proposals Initiated: Queen Mary University of London (QMUL), United Kingdom.</x:v>
       </x:c>
-      <x:c r="P28" t="str"/>
-      <x:c r="Q28" t="str"/>
+      <x:c r="P28"/>
+      <x:c r="Q28"/>
       <x:c r="R28" t="str">
         <x:v>Item: Photo Evidence, Evidence Attached: files::6a6c4cc9f312f.pdf, Remarks/Folder Reference/URLs: Spring 2026 Progress report</x:v>
       </x:c>
@@ -2881,12 +2881,12 @@
 2. Community Dental Services  
 A community outreach initiative providing accessible dental care services through the Community Dental Clinic at the Noor Project. The program focused on promoting oral health awareness, delivering preventive and basic dental treatments, and serving the healthcare needs of underserved communities.</x:v>
       </x:c>
-      <x:c r="T28" t="str"/>
+      <x:c r="T28"/>
       <x:c r="U28" t="str">
         <x:v>Basic Sciences faculty 
 BDS 2nd year Students</x:v>
       </x:c>
-      <x:c r="V28" t="str"/>
+      <x:c r="V28"/>
       <x:c r="W28" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
@@ -2902,30 +2902,30 @@
       <x:c r="AA28" t="str">
         <x:v>+923444420953</x:v>
       </x:c>
-      <x:c r="AB28" t="str"/>
-      <x:c r="AC28" t="str"/>
-      <x:c r="AD28" t="str"/>
-      <x:c r="AE28" t="str"/>
-      <x:c r="AF28" t="str"/>
-      <x:c r="AG28" t="str"/>
+      <x:c r="AB28"/>
+      <x:c r="AC28"/>
+      <x:c r="AD28"/>
+      <x:c r="AE28"/>
+      <x:c r="AF28"/>
+      <x:c r="AG28"/>
       <x:c r="AH28" t="str">
         <x:v>The University College of Dentistry, The University of Lahore, strengthened its international research network through a collaborative initiative with Dr. Hina from the Department of Dental Physical Sciences, Queen Mary University of London (QMUL), United Kingdom. This collaboration promotes knowledge exchange, supports joint research activities, and enhances academic excellence by fostering innovation, interdisciplinary research, and international scholarly engagement.</x:v>
       </x:c>
-      <x:c r="AI28" t="str"/>
-      <x:c r="AJ28" t="str"/>
-      <x:c r="AK28" t="str"/>
-      <x:c r="AL28" t="str"/>
-      <x:c r="AM28" t="str"/>
-      <x:c r="AN28" t="str"/>
-      <x:c r="AO28" t="str"/>
-      <x:c r="AP28" t="str"/>
-      <x:c r="AQ28" t="str"/>
-      <x:c r="AR28" t="str"/>
-      <x:c r="AS28" t="str"/>
-      <x:c r="AT28" t="str"/>
-      <x:c r="AU28" t="str"/>
-      <x:c r="AV28" t="str"/>
-      <x:c r="AW28" t="str"/>
+      <x:c r="AI28"/>
+      <x:c r="AJ28"/>
+      <x:c r="AK28"/>
+      <x:c r="AL28"/>
+      <x:c r="AM28"/>
+      <x:c r="AN28"/>
+      <x:c r="AO28"/>
+      <x:c r="AP28"/>
+      <x:c r="AQ28"/>
+      <x:c r="AR28"/>
+      <x:c r="AS28"/>
+      <x:c r="AT28"/>
+      <x:c r="AU28"/>
+      <x:c r="AV28"/>
+      <x:c r="AW28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
@@ -2958,14 +2958,14 @@
       <x:c r="J29" t="str">
         <x:v>Department of Physics</x:v>
       </x:c>
-      <x:c r="K29" t="str"/>
-      <x:c r="L29" t="str"/>
-      <x:c r="M29" t="str"/>
-      <x:c r="N29" t="str"/>
+      <x:c r="K29"/>
+      <x:c r="L29"/>
+      <x:c r="M29"/>
+      <x:c r="N29"/>
       <x:c r="O29" t="str">
         <x:v>Evidence: files::6a6b67c53d6bc.docx, Current Status: Submitted | Current Status: Submitted, Evidence: files::6a719c151d69f.docx | Current Status: Submitted, Evidence: files::6a719c2b8bd0e.docx | Current Status: Submitted, Evidence: files::6a719c3f08261.docx | Current Status: Submitted, Evidence: files::6a719c53ad306.docx | Current Status: Submitted, Evidence: files::6a719c63e5684.docx | Current Status: Submitted, Evidence: files::6a719c73b2ee1.docx | Current Status: Submitted, Evidence: files::6a719c8825add.docx | Current Status: Submitted, Evidence: files::6a719c9672279.docx | Current Status: Submitted, Evidence: files::6a719ca40b765.docx | Current Status: Submitted, Evidence: files::6a719caf74583.docx | Current Status: Submitted, Evidence: files::6a719cbe268e6.docx | Current Status: Submitted, Evidence: files::6a719cd35a107.docx</x:v>
       </x:c>
-      <x:c r="P29" t="str"/>
+      <x:c r="P29"/>
       <x:c r="Q29" t="str">
         <x:v> | Planned Activity / Event: null, Tentative Date: null, Objective / Expected Outcome: null, Evidence: files::6a719d4decb94.pdf</x:v>
       </x:c>
@@ -2981,7 +2981,7 @@
       <x:c r="U29" t="str">
         <x:v>M.A Raoof Expo</x:v>
       </x:c>
-      <x:c r="V29" t="str"/>
+      <x:c r="V29"/>
       <x:c r="W29" t="str">
         <x:v>2026-07-30</x:v>
       </x:c>
@@ -2997,10 +2997,10 @@
       <x:c r="AA29" t="str">
         <x:v>+923365551881</x:v>
       </x:c>
-      <x:c r="AB29" t="str"/>
-      <x:c r="AC29" t="str"/>
-      <x:c r="AD29" t="str"/>
-      <x:c r="AE29" t="str"/>
+      <x:c r="AB29"/>
+      <x:c r="AC29"/>
+      <x:c r="AD29"/>
+      <x:c r="AE29"/>
       <x:c r="AF29" t="str">
         <x:v>files::6a6c1e0da39f0.docx</x:v>
       </x:c>
@@ -3010,21 +3010,21 @@
       <x:c r="AH29" t="str">
         <x:v>All submitted projevts are attached</x:v>
       </x:c>
-      <x:c r="AI29" t="str"/>
-      <x:c r="AJ29" t="str"/>
-      <x:c r="AK29" t="str"/>
-      <x:c r="AL29" t="str"/>
-      <x:c r="AM29" t="str"/>
-      <x:c r="AN29" t="str"/>
-      <x:c r="AO29" t="str"/>
-      <x:c r="AP29" t="str"/>
-      <x:c r="AQ29" t="str"/>
-      <x:c r="AR29" t="str"/>
-      <x:c r="AS29" t="str"/>
-      <x:c r="AT29" t="str"/>
-      <x:c r="AU29" t="str"/>
-      <x:c r="AV29" t="str"/>
-      <x:c r="AW29" t="str"/>
+      <x:c r="AI29"/>
+      <x:c r="AJ29"/>
+      <x:c r="AK29"/>
+      <x:c r="AL29"/>
+      <x:c r="AM29"/>
+      <x:c r="AN29"/>
+      <x:c r="AO29"/>
+      <x:c r="AP29"/>
+      <x:c r="AQ29"/>
+      <x:c r="AR29"/>
+      <x:c r="AS29"/>
+      <x:c r="AT29"/>
+      <x:c r="AU29"/>
+      <x:c r="AV29"/>
+      <x:c r="AW29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
@@ -3060,15 +3060,15 @@
       <x:c r="K30" t="str">
         <x:v>Activity Type: IV, How Many: 25, Name Of Organization Planned with: Punjab Forensic Science Agency Labs, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-05-07, Remarks/Result: Students of the UIMLT Department had an informative and educational visit to the Punjab Forensic Science Agency Labs. During the visit, students attended a detailed introductory lecture followed by brief sessions in different laboratories and workstations. The visit provided valuable exposure to modern forensic techniques, laboratory procedures, and practical applications in diagnostic and investigative sciences. It was a great learning opportunity for students to observe professional laboratory practices and interact with experts in the field. Special thanks to the Punjab Forensic Science Agency team for their hospitality and insightful guidance.</x:v>
       </x:c>
-      <x:c r="L30" t="str"/>
-      <x:c r="M30" t="str"/>
-      <x:c r="N30" t="str"/>
-      <x:c r="O30" t="str"/>
-      <x:c r="P30" t="str"/>
+      <x:c r="L30"/>
+      <x:c r="M30"/>
+      <x:c r="N30"/>
+      <x:c r="O30"/>
+      <x:c r="P30"/>
       <x:c r="Q30" t="str">
         <x:v>Planned Activity / Event: Role of Medical Laboratory Professionals in Disease Prevention, Tentative Date: 2026-08-30, Objective / Expected Outcome: To highlight the critical contribution of medical laboratory professionals in early disease detection, diagnosis, and prevention, and to create awareness among students and faculty about how accurate and timely laboratory testing supports public health outcomes, reduces disease transmission, and strengthens the overall healthcare system.</x:v>
       </x:c>
-      <x:c r="R30" t="str"/>
+      <x:c r="R30"/>
       <x:c r="S30" t="str">
         <x:v>The University of Lahore, in collaboration with the Medical Laboratory Conference (MLCON) and the Pakistan Medical Laboratory Association (PMLA), organized a celebration marking World Medical Laboratory Professionals Week 2026, themed "Bridging Expertise and Student Innovation in Laboratory Sciences." The event was held on 30th April 2026 (9:00 AM – 1:00 PM) at Lecture Theatre 1, EE-1, University Institute of Medical Laboratory Technology (UIMLT). The session brought together senior professionals and students to highlight advancements, innovations, and the evolving role of medical laboratory sciences.</x:v>
       </x:c>
@@ -3078,7 +3078,7 @@
       <x:c r="U30" t="str">
         <x:v>Faculty members from UIMLT and the Faculty of Allied Health Sciences coordinated and hosted the event, while students actively participated through attendance, innovation showcases, and interactive engagement with visiting professionals. Key figures involved included M. Nadeem Ashraf (Chairman, MLCON), Dr. Anam Farzand (General Secretary, MLCON), Hafiz Shahzad Hussain (Chief Organizer, MLCON), and Ihsan Ullah Shahid (President, PMLA).</x:v>
       </x:c>
-      <x:c r="V30" t="str"/>
+      <x:c r="V30"/>
       <x:c r="W30" t="str">
         <x:v>2026-07-30</x:v>
       </x:c>
@@ -3094,28 +3094,28 @@
       <x:c r="AA30" t="str">
         <x:v>+923144248700</x:v>
       </x:c>
-      <x:c r="AB30" t="str"/>
-      <x:c r="AC30" t="str"/>
-      <x:c r="AD30" t="str"/>
-      <x:c r="AE30" t="str"/>
-      <x:c r="AF30" t="str"/>
-      <x:c r="AG30" t="str"/>
-      <x:c r="AH30" t="str"/>
-      <x:c r="AI30" t="str"/>
-      <x:c r="AJ30" t="str"/>
-      <x:c r="AK30" t="str"/>
-      <x:c r="AL30" t="str"/>
-      <x:c r="AM30" t="str"/>
-      <x:c r="AN30" t="str"/>
-      <x:c r="AO30" t="str"/>
-      <x:c r="AP30" t="str"/>
-      <x:c r="AQ30" t="str"/>
-      <x:c r="AR30" t="str"/>
-      <x:c r="AS30" t="str"/>
-      <x:c r="AT30" t="str"/>
-      <x:c r="AU30" t="str"/>
-      <x:c r="AV30" t="str"/>
-      <x:c r="AW30" t="str"/>
+      <x:c r="AB30"/>
+      <x:c r="AC30"/>
+      <x:c r="AD30"/>
+      <x:c r="AE30"/>
+      <x:c r="AF30"/>
+      <x:c r="AG30"/>
+      <x:c r="AH30"/>
+      <x:c r="AI30"/>
+      <x:c r="AJ30"/>
+      <x:c r="AK30"/>
+      <x:c r="AL30"/>
+      <x:c r="AM30"/>
+      <x:c r="AN30"/>
+      <x:c r="AO30"/>
+      <x:c r="AP30"/>
+      <x:c r="AQ30"/>
+      <x:c r="AR30"/>
+      <x:c r="AS30"/>
+      <x:c r="AT30"/>
+      <x:c r="AU30"/>
+      <x:c r="AV30"/>
+      <x:c r="AW30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
@@ -3151,15 +3151,15 @@
       <x:c r="K31" t="str">
         <x:v>Activity Type: IV, Name Of Organization Planned with: Punjab Forensic Science Agency team, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-05-08, Remarks/Result: Students of the UIMLT Department had an informative and educational visit to the Punjab Forensic Science Agency Labs. During the visit, students attended a detailed introductory lecture followed by brief sessions in different laboratories and workstations. The visit provided valuable exposure to modern forensic techniques, laboratory procedures, and practical applications in diagnostic and investigative sciences. It was a great learning opportunity for students to observe professional laboratory practices and interact with experts in the field. Special thanks to the Punjab Forensic Science Agency team for their hospitality and insightful guidance. | </x:v>
       </x:c>
-      <x:c r="L31" t="str"/>
-      <x:c r="M31" t="str"/>
-      <x:c r="N31" t="str"/>
-      <x:c r="O31" t="str"/>
-      <x:c r="P31" t="str"/>
+      <x:c r="L31"/>
+      <x:c r="M31"/>
+      <x:c r="N31"/>
+      <x:c r="O31"/>
+      <x:c r="P31"/>
       <x:c r="Q31" t="str">
         <x:v>Planned Activity / Event: 1.	Advanced Techniques in Clinical Biochemistry, Tentative Date: 2026-08-31, Objective / Expected Outcome: 1.	Advanced Techniques in Clinical Biochemistry</x:v>
       </x:c>
-      <x:c r="R31" t="str"/>
+      <x:c r="R31"/>
       <x:c r="S31" t="str">
         <x:v>The University of Lahore, in collaboration with the Medical Laboratory Conference (MLCON) and the Pakistan Medical Laboratory Association (PMLA), organized a celebration marking World Medical Laboratory Professionals Week 2026, themed "Bridging Expertise and Student Innovation in Laboratory Sciences." The event was held on 30th April 2026 (9:00 AM – 1:00 PM) at Lecture Theatre 1, EE-1, University Institute of Medical Laboratory Technology (UIMLT). The session brought together senior professionals and students to highlight advancements, innovations, and the evolving role of medical laboratory sciences.</x:v>
       </x:c>
@@ -3169,7 +3169,7 @@
       <x:c r="U31" t="str">
         <x:v>Faculty members from UIMLT and the Faculty of Allied Health Sciences coordinated and hosted the event, while students actively participated through attendance, innovation showcases, and interactive engagement with visiting professionals. Key figures involved included M. Nadeem Ashraf (Chairman, MLCON), Dr. Anam Farzand (General Secretary, MLCON), Hafiz Shahzad Hussain (Chief Organizer, MLCON), and Ihsan Ullah Shahid (President, PMLA).</x:v>
       </x:c>
-      <x:c r="V31" t="str"/>
+      <x:c r="V31"/>
       <x:c r="W31" t="str">
         <x:v>2026-07-28</x:v>
       </x:c>
@@ -3185,30 +3185,30 @@
       <x:c r="AA31" t="str">
         <x:v>+923144248700</x:v>
       </x:c>
-      <x:c r="AB31" t="str"/>
-      <x:c r="AC31" t="str"/>
-      <x:c r="AD31" t="str"/>
-      <x:c r="AE31" t="str"/>
+      <x:c r="AB31"/>
+      <x:c r="AC31"/>
+      <x:c r="AD31"/>
+      <x:c r="AE31"/>
       <x:c r="AF31" t="str">
         <x:v>files::6a6afbcb07d9a.jpeg</x:v>
       </x:c>
-      <x:c r="AG31" t="str"/>
-      <x:c r="AH31" t="str"/>
-      <x:c r="AI31" t="str"/>
-      <x:c r="AJ31" t="str"/>
-      <x:c r="AK31" t="str"/>
-      <x:c r="AL31" t="str"/>
-      <x:c r="AM31" t="str"/>
-      <x:c r="AN31" t="str"/>
-      <x:c r="AO31" t="str"/>
-      <x:c r="AP31" t="str"/>
-      <x:c r="AQ31" t="str"/>
-      <x:c r="AR31" t="str"/>
-      <x:c r="AS31" t="str"/>
-      <x:c r="AT31" t="str"/>
-      <x:c r="AU31" t="str"/>
-      <x:c r="AV31" t="str"/>
-      <x:c r="AW31" t="str"/>
+      <x:c r="AG31"/>
+      <x:c r="AH31"/>
+      <x:c r="AI31"/>
+      <x:c r="AJ31"/>
+      <x:c r="AK31"/>
+      <x:c r="AL31"/>
+      <x:c r="AM31"/>
+      <x:c r="AN31"/>
+      <x:c r="AO31"/>
+      <x:c r="AP31"/>
+      <x:c r="AQ31"/>
+      <x:c r="AR31"/>
+      <x:c r="AS31"/>
+      <x:c r="AT31"/>
+      <x:c r="AU31"/>
+      <x:c r="AV31"/>
+      <x:c r="AW31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
@@ -3250,13 +3250,13 @@
       <x:c r="M32" t="str">
         <x:v>Company: University of Lahore Department of CS and IT, Sector: Travel, Number Of students: 3, Duration: 6 months, Type: Planned, Mode: Physical, Evidence: files::6a70304cc069c.pdf | Company: University of Lahore Department of CS and IT, Sector: Agriculture, Number Of students: 3, Duration: 6 months, Type: Planned, Mode: Physical, Evidence: files::6a7030541bbbb.pdf</x:v>
       </x:c>
-      <x:c r="N32" t="str"/>
+      <x:c r="N32"/>
       <x:c r="O32" t="str">
         <x:v>New Proposals Initiated: 1, External Collaborators: RASTA CGP8, Focus Areas / Themes: AI-Driven Policy Formulation for Circular Debt Management in Pakistan’s Power Sector, Current Status: Submitted</x:v>
       </x:c>
-      <x:c r="P32" t="str"/>
-      <x:c r="Q32" t="str"/>
-      <x:c r="R32" t="str"/>
+      <x:c r="P32"/>
+      <x:c r="Q32"/>
+      <x:c r="R32"/>
       <x:c r="S32" t="str">
         <x:v>OBE Training</x:v>
       </x:c>
@@ -3296,30 +3296,30 @@
       <x:c r="AA32" t="str">
         <x:v>+92322549114</x:v>
       </x:c>
-      <x:c r="AB32" t="str"/>
-      <x:c r="AC32" t="str"/>
-      <x:c r="AD32" t="str"/>
-      <x:c r="AE32" t="str"/>
+      <x:c r="AB32"/>
+      <x:c r="AC32"/>
+      <x:c r="AD32"/>
+      <x:c r="AE32"/>
       <x:c r="AF32" t="str">
         <x:v>files::6a6aee4b96cbc.jpeg</x:v>
       </x:c>
-      <x:c r="AG32" t="str"/>
-      <x:c r="AH32" t="str"/>
-      <x:c r="AI32" t="str"/>
-      <x:c r="AJ32" t="str"/>
-      <x:c r="AK32" t="str"/>
-      <x:c r="AL32" t="str"/>
-      <x:c r="AM32" t="str"/>
-      <x:c r="AN32" t="str"/>
-      <x:c r="AO32" t="str"/>
-      <x:c r="AP32" t="str"/>
-      <x:c r="AQ32" t="str"/>
-      <x:c r="AR32" t="str"/>
-      <x:c r="AS32" t="str"/>
-      <x:c r="AT32" t="str"/>
-      <x:c r="AU32" t="str"/>
-      <x:c r="AV32" t="str"/>
-      <x:c r="AW32" t="str"/>
+      <x:c r="AG32"/>
+      <x:c r="AH32"/>
+      <x:c r="AI32"/>
+      <x:c r="AJ32"/>
+      <x:c r="AK32"/>
+      <x:c r="AL32"/>
+      <x:c r="AM32"/>
+      <x:c r="AN32"/>
+      <x:c r="AO32"/>
+      <x:c r="AP32"/>
+      <x:c r="AQ32"/>
+      <x:c r="AR32"/>
+      <x:c r="AS32"/>
+      <x:c r="AT32"/>
+      <x:c r="AU32"/>
+      <x:c r="AV32"/>
+      <x:c r="AW32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
@@ -3355,48 +3355,48 @@
       <x:c r="K33" t="str">
         <x:v>Activity Type: Community Engagement, How Many: 60, Name Of Organization Planned with: SAFE Society, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-04-22 | Activity Type: Community Engagement, How Many: 60, Name Of Organization Planned with: Chaoon Foundation, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-04-26 | Activity Type: Community Engagement, How Many: 50, Name Of Organization Planned with: S.A.F.E Society, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-06-05 | Activity Type: Guest Lecture, How Many: 35, Name Of Organization Planned with: Emergency Services Department (Rescue 1122), Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-06-02 | Activity Type: Guest Lecture, How Many: 40, Name Of Organization Planned with: National Highway Authority, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-05-23</x:v>
       </x:c>
-      <x:c r="L33" t="str"/>
-      <x:c r="M33" t="str"/>
-      <x:c r="N33" t="str"/>
-      <x:c r="O33" t="str"/>
-      <x:c r="P33" t="str"/>
-      <x:c r="Q33" t="str"/>
-      <x:c r="R33" t="str"/>
-      <x:c r="S33" t="str"/>
-      <x:c r="T33" t="str"/>
-      <x:c r="U33" t="str"/>
-      <x:c r="V33" t="str"/>
+      <x:c r="L33"/>
+      <x:c r="M33"/>
+      <x:c r="N33"/>
+      <x:c r="O33"/>
+      <x:c r="P33"/>
+      <x:c r="Q33"/>
+      <x:c r="R33"/>
+      <x:c r="S33"/>
+      <x:c r="T33"/>
+      <x:c r="U33"/>
+      <x:c r="V33"/>
       <x:c r="W33" t="str">
         <x:v>2026-04-26</x:v>
       </x:c>
-      <x:c r="X33" t="str"/>
-      <x:c r="Y33" t="str"/>
+      <x:c r="X33"/>
+      <x:c r="Y33"/>
       <x:c r="Z33" t="str">
         <x:v>2026-07-29</x:v>
       </x:c>
-      <x:c r="AA33" t="str"/>
-      <x:c r="AB33" t="str"/>
-      <x:c r="AC33" t="str"/>
-      <x:c r="AD33" t="str"/>
-      <x:c r="AE33" t="str"/>
-      <x:c r="AF33" t="str"/>
-      <x:c r="AG33" t="str"/>
-      <x:c r="AH33" t="str"/>
-      <x:c r="AI33" t="str"/>
-      <x:c r="AJ33" t="str"/>
-      <x:c r="AK33" t="str"/>
-      <x:c r="AL33" t="str"/>
-      <x:c r="AM33" t="str"/>
-      <x:c r="AN33" t="str"/>
-      <x:c r="AO33" t="str"/>
-      <x:c r="AP33" t="str"/>
-      <x:c r="AQ33" t="str"/>
-      <x:c r="AR33" t="str"/>
-      <x:c r="AS33" t="str"/>
-      <x:c r="AT33" t="str"/>
-      <x:c r="AU33" t="str"/>
-      <x:c r="AV33" t="str"/>
-      <x:c r="AW33" t="str"/>
+      <x:c r="AA33"/>
+      <x:c r="AB33"/>
+      <x:c r="AC33"/>
+      <x:c r="AD33"/>
+      <x:c r="AE33"/>
+      <x:c r="AF33"/>
+      <x:c r="AG33"/>
+      <x:c r="AH33"/>
+      <x:c r="AI33"/>
+      <x:c r="AJ33"/>
+      <x:c r="AK33"/>
+      <x:c r="AL33"/>
+      <x:c r="AM33"/>
+      <x:c r="AN33"/>
+      <x:c r="AO33"/>
+      <x:c r="AP33"/>
+      <x:c r="AQ33"/>
+      <x:c r="AR33"/>
+      <x:c r="AS33"/>
+      <x:c r="AT33"/>
+      <x:c r="AU33"/>
+      <x:c r="AV33"/>
+      <x:c r="AW33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
@@ -3435,20 +3435,20 @@
       <x:c r="L34" t="str">
         <x:v>Partner Institution: Pakistan Institute of Living and Learning (PILL), Country: Pakistan, MOU Type: Academic, Key Activities: Joint research projects, clinical training and internships, faculty and student development, academic seminars, mental health awareness initiatives, and evidence-based practice collaboration., Status: Completed, Evidence: files::6a673a5e4f5d9.pdf</x:v>
       </x:c>
-      <x:c r="M34" t="str"/>
-      <x:c r="N34" t="str"/>
+      <x:c r="M34"/>
+      <x:c r="N34"/>
       <x:c r="O34" t="str">
         <x:v>New Proposals Initiated: APF-Visionary Grants., External Collaborators: Nill, Focus Areas / Themes: "Investigating Perceived Parental Shame in Individuals with Parental Substance Use Disorder:  A Solution-Focused Brief Therapy Intervention inPunjab, Pakistan", Current Status: Submitted | New Proposals Initiated: APF-Visionary Grants., External Collaborators: Nill, Focus Areas / Themes: Transforming Campus Climate: An Empathy and Emotional Regulation program toprevent agression and Narcissistic Behavior among University Students, Current Status: Submitted | New Proposals Initiated: APF-Visionary Grants., External Collaborators: Nill, Focus Areas / Themes: Do we Belong? Acculturative Experiences, Perceived rational Discrimination, andIdentity-Based Psychological Distress among Waziristan Students in Urban Universities of Pakistan: A mixed Method Study with Psychosocial Intervention., Current Status: Submitted | New Proposals Initiated: APF-Visionary Grants., External Collaborators: Nill, Focus Areas / Themes: Do we Belong? Acculturative Experiences, Perceived rational Discrimination, andIdentity-Based Psychological Distress among Waziristan Students in Urban Universities of Pakistan: A mixed Method Study with Psychosocial Intervention., Current Status: Submitted | New Proposals Initiated: APF-Visionary Grants., Focus Areas / Themes: Do we Belong? Acculturative Experiences, Perceived rational Discrimination, andIdentity-Based Psychological Distress among Waziristan Students in Urban Universities of Pakistan: A mixed Method Study with Psychosocial Intervention., Current Status: Submitted, Evidence: files::6a7ab41c82614.pdf,files::6a7ab4882f657.pdf | New Proposals Initiated: Original (APF-Visionary Grants), External Collaborators: Nil, Focus Areas / Themes: "Investigating Perceived Parental Shame in Individuals with Parental Substance Use Disorder:  A Solution-Focused Brief Therapy Intervention in Punjab, Pakistan", Current Status: Submitted, Evidence: files::6aa3af739b5a4_research_project_1.pdf | New Proposals Initiated: Original (APF-Visionary Grants), External Collaborators: Nil, Focus Areas / Themes: Transforming Campus Climate: An Empathy and Emotional Regulation program toprevent agression and Narcissistic Behavior among University Students, Current Status: Submitted, Evidence: files::6aa3afc610fca_research_project2.pdf | New Proposals Initiated: Original (APF-Visionary Grants), External Collaborators: Nil, Focus Areas / Themes: Do we Belong? Acculturative Experiences, Perceived rational Discrimination, andIdentity-Based Psychological Distress among Waziristan Students in Urban Universities of Pakistan: A mixed Method Study with Psychosocial Intervention., Current Status: Submitted, Evidence: files::6aa3afde1392c_research_project3.pdf</x:v>
       </x:c>
-      <x:c r="P34" t="str"/>
-      <x:c r="Q34" t="str"/>
+      <x:c r="P34"/>
+      <x:c r="Q34"/>
       <x:c r="R34" t="str">
         <x:v>Item: Event Flyers/Reports, Evidence Attached: files::6a673fed45dde.zip</x:v>
       </x:c>
-      <x:c r="S34" t="str"/>
-      <x:c r="T34" t="str"/>
-      <x:c r="U34" t="str"/>
-      <x:c r="V34" t="str"/>
+      <x:c r="S34"/>
+      <x:c r="T34"/>
+      <x:c r="U34"/>
+      <x:c r="V34"/>
       <x:c r="W34" t="str">
         <x:v>2026-02-19</x:v>
       </x:c>
@@ -3464,28 +3464,28 @@
       <x:c r="AA34" t="str">
         <x:v>+923331476668</x:v>
       </x:c>
-      <x:c r="AB34" t="str"/>
-      <x:c r="AC34" t="str"/>
-      <x:c r="AD34" t="str"/>
-      <x:c r="AE34" t="str"/>
-      <x:c r="AF34" t="str"/>
-      <x:c r="AG34" t="str"/>
-      <x:c r="AH34" t="str"/>
-      <x:c r="AI34" t="str"/>
-      <x:c r="AJ34" t="str"/>
-      <x:c r="AK34" t="str"/>
-      <x:c r="AL34" t="str"/>
-      <x:c r="AM34" t="str"/>
-      <x:c r="AN34" t="str"/>
-      <x:c r="AO34" t="str"/>
-      <x:c r="AP34" t="str"/>
-      <x:c r="AQ34" t="str"/>
-      <x:c r="AR34" t="str"/>
-      <x:c r="AS34" t="str"/>
-      <x:c r="AT34" t="str"/>
-      <x:c r="AU34" t="str"/>
-      <x:c r="AV34" t="str"/>
-      <x:c r="AW34" t="str"/>
+      <x:c r="AB34"/>
+      <x:c r="AC34"/>
+      <x:c r="AD34"/>
+      <x:c r="AE34"/>
+      <x:c r="AF34"/>
+      <x:c r="AG34"/>
+      <x:c r="AH34"/>
+      <x:c r="AI34"/>
+      <x:c r="AJ34"/>
+      <x:c r="AK34"/>
+      <x:c r="AL34"/>
+      <x:c r="AM34"/>
+      <x:c r="AN34"/>
+      <x:c r="AO34"/>
+      <x:c r="AP34"/>
+      <x:c r="AQ34"/>
+      <x:c r="AR34"/>
+      <x:c r="AS34"/>
+      <x:c r="AT34"/>
+      <x:c r="AU34"/>
+      <x:c r="AV34"/>
+      <x:c r="AW34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="str">
@@ -3518,45 +3518,45 @@
       <x:c r="J35" t="str">
         <x:v>Deptartment of English Language and Literature</x:v>
       </x:c>
-      <x:c r="K35" t="str"/>
-      <x:c r="L35" t="str"/>
-      <x:c r="M35" t="str"/>
-      <x:c r="N35" t="str"/>
-      <x:c r="O35" t="str"/>
-      <x:c r="P35" t="str"/>
-      <x:c r="Q35" t="str"/>
-      <x:c r="R35" t="str"/>
-      <x:c r="S35" t="str"/>
-      <x:c r="T35" t="str"/>
-      <x:c r="U35" t="str"/>
-      <x:c r="V35" t="str"/>
-      <x:c r="W35" t="str"/>
-      <x:c r="X35" t="str"/>
-      <x:c r="Y35" t="str"/>
-      <x:c r="Z35" t="str"/>
-      <x:c r="AA35" t="str"/>
-      <x:c r="AB35" t="str"/>
-      <x:c r="AC35" t="str"/>
-      <x:c r="AD35" t="str"/>
-      <x:c r="AE35" t="str"/>
-      <x:c r="AF35" t="str"/>
-      <x:c r="AG35" t="str"/>
-      <x:c r="AH35" t="str"/>
-      <x:c r="AI35" t="str"/>
-      <x:c r="AJ35" t="str"/>
-      <x:c r="AK35" t="str"/>
-      <x:c r="AL35" t="str"/>
-      <x:c r="AM35" t="str"/>
-      <x:c r="AN35" t="str"/>
-      <x:c r="AO35" t="str"/>
-      <x:c r="AP35" t="str"/>
-      <x:c r="AQ35" t="str"/>
-      <x:c r="AR35" t="str"/>
-      <x:c r="AS35" t="str"/>
-      <x:c r="AT35" t="str"/>
-      <x:c r="AU35" t="str"/>
-      <x:c r="AV35" t="str"/>
-      <x:c r="AW35" t="str"/>
+      <x:c r="K35"/>
+      <x:c r="L35"/>
+      <x:c r="M35"/>
+      <x:c r="N35"/>
+      <x:c r="O35"/>
+      <x:c r="P35"/>
+      <x:c r="Q35"/>
+      <x:c r="R35"/>
+      <x:c r="S35"/>
+      <x:c r="T35"/>
+      <x:c r="U35"/>
+      <x:c r="V35"/>
+      <x:c r="W35"/>
+      <x:c r="X35"/>
+      <x:c r="Y35"/>
+      <x:c r="Z35"/>
+      <x:c r="AA35"/>
+      <x:c r="AB35"/>
+      <x:c r="AC35"/>
+      <x:c r="AD35"/>
+      <x:c r="AE35"/>
+      <x:c r="AF35"/>
+      <x:c r="AG35"/>
+      <x:c r="AH35"/>
+      <x:c r="AI35"/>
+      <x:c r="AJ35"/>
+      <x:c r="AK35"/>
+      <x:c r="AL35"/>
+      <x:c r="AM35"/>
+      <x:c r="AN35"/>
+      <x:c r="AO35"/>
+      <x:c r="AP35"/>
+      <x:c r="AQ35"/>
+      <x:c r="AR35"/>
+      <x:c r="AS35"/>
+      <x:c r="AT35"/>
+      <x:c r="AU35"/>
+      <x:c r="AV35"/>
+      <x:c r="AW35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
@@ -3589,7 +3589,7 @@
       <x:c r="J36" t="str">
         <x:v>Lahore School of Aviation</x:v>
       </x:c>
-      <x:c r="K36" t="str"/>
+      <x:c r="K36"/>
       <x:c r="L36" t="str">
         <x:v>Partner Institution: air blue, Country: Pakistan, MOU Type: Industry, Status: Under Process, Evidence: files::6a7ae56d5229a.docx</x:v>
       </x:c>
@@ -3599,16 +3599,16 @@
       <x:c r="N36" t="str">
         <x:v>Activities Conducted: Mentorship, Purpose &amp; Outcomes:: Facilitated career guidance by connecting alumni with departmental initiatives, sharing employment opportunities, and supporting graduates in their professional development and placement., Feedback Highlights / Reflections:: Alumni appreciated the regular communication regarding job opportunities and expressed positive feedback on the department's continued career support and engagement. | Activities Conducted: Success Story Session, Purpose &amp; Outcomes:: Highlighted the professional achievements of alumni through the department's social media platforms to recognize their accomplishments, strengthen alumni connections, and inspire current students., Feedback Highlights / Reflections:: The success stories received positive engagement from alumni and students, enhancing the department's visibility and encouraging continued alumni participation. | Activities Conducted: Alumni Talks,, Purpose &amp; Outcomes:: Organized an Alumni Talk to provide students with industry insights, career guidance, and practical knowledge through the experiences of distinguished alumni., Feedback Highlights / Reflections:: Students found the session informative and motivating, while alumni appreciated the opportunity to reconnect with the department and share their professional experiences.</x:v>
       </x:c>
-      <x:c r="O36" t="str"/>
-      <x:c r="P36" t="str"/>
-      <x:c r="Q36" t="str"/>
-      <x:c r="R36" t="str"/>
-      <x:c r="S36" t="str"/>
-      <x:c r="T36" t="str"/>
-      <x:c r="U36" t="str"/>
-      <x:c r="V36" t="str"/>
-      <x:c r="W36" t="str"/>
-      <x:c r="X36" t="str"/>
+      <x:c r="O36"/>
+      <x:c r="P36"/>
+      <x:c r="Q36"/>
+      <x:c r="R36"/>
+      <x:c r="S36"/>
+      <x:c r="T36"/>
+      <x:c r="U36"/>
+      <x:c r="V36"/>
+      <x:c r="W36"/>
+      <x:c r="X36"/>
       <x:c r="Y36" t="str">
         <x:v>Assistant Professor</x:v>
       </x:c>
@@ -3618,28 +3618,28 @@
       <x:c r="AA36" t="str">
         <x:v>+3030499676</x:v>
       </x:c>
-      <x:c r="AB36" t="str"/>
-      <x:c r="AC36" t="str"/>
-      <x:c r="AD36" t="str"/>
-      <x:c r="AE36" t="str"/>
-      <x:c r="AF36" t="str"/>
-      <x:c r="AG36" t="str"/>
-      <x:c r="AH36" t="str"/>
-      <x:c r="AI36" t="str"/>
-      <x:c r="AJ36" t="str"/>
-      <x:c r="AK36" t="str"/>
-      <x:c r="AL36" t="str"/>
-      <x:c r="AM36" t="str"/>
-      <x:c r="AN36" t="str"/>
-      <x:c r="AO36" t="str"/>
-      <x:c r="AP36" t="str"/>
-      <x:c r="AQ36" t="str"/>
-      <x:c r="AR36" t="str"/>
-      <x:c r="AS36" t="str"/>
-      <x:c r="AT36" t="str"/>
-      <x:c r="AU36" t="str"/>
-      <x:c r="AV36" t="str"/>
-      <x:c r="AW36" t="str"/>
+      <x:c r="AB36"/>
+      <x:c r="AC36"/>
+      <x:c r="AD36"/>
+      <x:c r="AE36"/>
+      <x:c r="AF36"/>
+      <x:c r="AG36"/>
+      <x:c r="AH36"/>
+      <x:c r="AI36"/>
+      <x:c r="AJ36"/>
+      <x:c r="AK36"/>
+      <x:c r="AL36"/>
+      <x:c r="AM36"/>
+      <x:c r="AN36"/>
+      <x:c r="AO36"/>
+      <x:c r="AP36"/>
+      <x:c r="AQ36"/>
+      <x:c r="AR36"/>
+      <x:c r="AS36"/>
+      <x:c r="AT36"/>
+      <x:c r="AU36"/>
+      <x:c r="AV36"/>
+      <x:c r="AW36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
@@ -3675,46 +3675,46 @@
       <x:c r="K37" t="str">
         <x:v>Activity Type: Guest Lecture | Activity Type: Industrial Visit | Activity Type: IAB Meeting / Industry Consultation |  | Activity Type: MoU Signing (Memorandum of Understanding), Planned: Yes, Scheduled: Yes</x:v>
       </x:c>
-      <x:c r="L37" t="str"/>
-      <x:c r="M37" t="str"/>
+      <x:c r="L37"/>
+      <x:c r="M37"/>
       <x:c r="N37" t="str">
         <x:v>Activities Conducted: Panels</x:v>
       </x:c>
-      <x:c r="O37" t="str"/>
-      <x:c r="P37" t="str"/>
-      <x:c r="Q37" t="str"/>
-      <x:c r="R37" t="str"/>
-      <x:c r="S37" t="str"/>
-      <x:c r="T37" t="str"/>
-      <x:c r="U37" t="str"/>
-      <x:c r="V37" t="str"/>
-      <x:c r="W37" t="str"/>
-      <x:c r="X37" t="str"/>
-      <x:c r="Y37" t="str"/>
-      <x:c r="Z37" t="str"/>
-      <x:c r="AA37" t="str"/>
-      <x:c r="AB37" t="str"/>
-      <x:c r="AC37" t="str"/>
-      <x:c r="AD37" t="str"/>
-      <x:c r="AE37" t="str"/>
-      <x:c r="AF37" t="str"/>
-      <x:c r="AG37" t="str"/>
-      <x:c r="AH37" t="str"/>
-      <x:c r="AI37" t="str"/>
-      <x:c r="AJ37" t="str"/>
-      <x:c r="AK37" t="str"/>
-      <x:c r="AL37" t="str"/>
-      <x:c r="AM37" t="str"/>
-      <x:c r="AN37" t="str"/>
-      <x:c r="AO37" t="str"/>
-      <x:c r="AP37" t="str"/>
-      <x:c r="AQ37" t="str"/>
-      <x:c r="AR37" t="str"/>
-      <x:c r="AS37" t="str"/>
-      <x:c r="AT37" t="str"/>
-      <x:c r="AU37" t="str"/>
-      <x:c r="AV37" t="str"/>
-      <x:c r="AW37" t="str"/>
+      <x:c r="O37"/>
+      <x:c r="P37"/>
+      <x:c r="Q37"/>
+      <x:c r="R37"/>
+      <x:c r="S37"/>
+      <x:c r="T37"/>
+      <x:c r="U37"/>
+      <x:c r="V37"/>
+      <x:c r="W37"/>
+      <x:c r="X37"/>
+      <x:c r="Y37"/>
+      <x:c r="Z37"/>
+      <x:c r="AA37"/>
+      <x:c r="AB37"/>
+      <x:c r="AC37"/>
+      <x:c r="AD37"/>
+      <x:c r="AE37"/>
+      <x:c r="AF37"/>
+      <x:c r="AG37"/>
+      <x:c r="AH37"/>
+      <x:c r="AI37"/>
+      <x:c r="AJ37"/>
+      <x:c r="AK37"/>
+      <x:c r="AL37"/>
+      <x:c r="AM37"/>
+      <x:c r="AN37"/>
+      <x:c r="AO37"/>
+      <x:c r="AP37"/>
+      <x:c r="AQ37"/>
+      <x:c r="AR37"/>
+      <x:c r="AS37"/>
+      <x:c r="AT37"/>
+      <x:c r="AU37"/>
+      <x:c r="AV37"/>
+      <x:c r="AW37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
@@ -3750,23 +3750,23 @@
       <x:c r="K38" t="str">
         <x:v>Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: Saleem Memorial Hospital, Lahore General Hospital, Fatima Memorial Hospital, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-05-14, Remarks/Result: Completed/Successful</x:v>
       </x:c>
-      <x:c r="L38" t="str"/>
+      <x:c r="L38"/>
       <x:c r="M38" t="str">
         <x:v>Company: Shaukat Khanum Memorial Cancer Hospital and Research Centre, Sector: Private, Number Of students: 20, Duration: 6 months, Type: Intership, Mode: Physical, Evidence: files::6a61ccd5ecab6.zip</x:v>
       </x:c>
-      <x:c r="N38" t="str"/>
+      <x:c r="N38"/>
       <x:c r="O38" t="str">
         <x:v>New Proposals Initiated: Comparative Analysis of Larger and Smaller Airway Function in Female Students from Smog-Endemic Regions: A Cohort Study Based on Air Quality Index Analyzing Subclinical Small Airway Impairment Using FEF25–75, External Collaborators: Dr. Muhammad Ahmad (Department of Pulmonology and Critical Care, Saleem Memorial Hospital), Dr. Muhammad Sufyan (Department of Pulmonology and Sleep Medicine, Lahore General Hospital), RT. Maham (Head of Respiratory Care Department, Fatima Memorial Hospital), Mr. Abdul Wakeel (Clinical Specialist), Focus Areas / Themes: Larger and Smaller Airway Function in Female Students from Smog-Endemic Regions, Current Status: Submitted, Evidence: files::6a61c881db71a.docx</x:v>
       </x:c>
-      <x:c r="P38" t="str"/>
-      <x:c r="Q38" t="str"/>
+      <x:c r="P38"/>
+      <x:c r="Q38"/>
       <x:c r="R38" t="str">
         <x:v>Item: Media Coverage/Social Links, Evidence Attached: files::6a62f2b7d4b6a.JPG, Remarks/Folder Reference/URLs: From Non-Invasive to Invasive Ventilation: A Hands-on Clinical Workshop (Workshop evidence) | Item: Photo Evidence, Evidence Attached: files::6a62f2c8d3055.JPG, Remarks/Folder Reference/URLs: rom Non-Invasive to Invasive Ventilation: A Hands-on Clinical Workshop (Workshop evidence) | Item: Photo Evidence, Evidence Attached: files::6a62f2d164bb6.JPG, Remarks/Folder Reference/URLs: rom Non-Invasive to Invasive Ventilation: A Hands-on Clinical Workshop (Workshop evidence) | Item: Photo Evidence, Evidence Attached: files::6a62f2de06ea4.JPG, Remarks/Folder Reference/URLs: rom Non-Invasive to Invasive Ventilation: A Hands-on Clinical Workshop (Workshop evidence) | Item: Photo Evidence, Evidence Attached: files::6a62f308807e6.JPG, Remarks/Folder Reference/URLs: Project evidence | Item: Media Coverage/Social Links, Remarks/Folder Reference/URLs: https://www.facebook.com/share/p/19PiHxEZur/ (workshop), Evidence Attached: files::6a62f32b913f3.zip | Item: Internship Lists (Excel), Evidence Attached: files::6a62f37c3f928.xlsx, Remarks/Folder Reference/URLs: Internship List Anesthesia Technology Students</x:v>
       </x:c>
-      <x:c r="S38" t="str"/>
-      <x:c r="T38" t="str"/>
-      <x:c r="U38" t="str"/>
-      <x:c r="V38" t="str"/>
+      <x:c r="S38"/>
+      <x:c r="T38"/>
+      <x:c r="U38"/>
+      <x:c r="V38"/>
       <x:c r="W38" t="str">
         <x:v>2026-07-23</x:v>
       </x:c>
@@ -3782,28 +3782,28 @@
       <x:c r="AA38" t="str">
         <x:v>+923215675168</x:v>
       </x:c>
-      <x:c r="AB38" t="str"/>
-      <x:c r="AC38" t="str"/>
-      <x:c r="AD38" t="str"/>
-      <x:c r="AE38" t="str"/>
-      <x:c r="AF38" t="str"/>
-      <x:c r="AG38" t="str"/>
-      <x:c r="AH38" t="str"/>
-      <x:c r="AI38" t="str"/>
-      <x:c r="AJ38" t="str"/>
-      <x:c r="AK38" t="str"/>
-      <x:c r="AL38" t="str"/>
-      <x:c r="AM38" t="str"/>
-      <x:c r="AN38" t="str"/>
-      <x:c r="AO38" t="str"/>
-      <x:c r="AP38" t="str"/>
-      <x:c r="AQ38" t="str"/>
-      <x:c r="AR38" t="str"/>
-      <x:c r="AS38" t="str"/>
-      <x:c r="AT38" t="str"/>
-      <x:c r="AU38" t="str"/>
-      <x:c r="AV38" t="str"/>
-      <x:c r="AW38" t="str"/>
+      <x:c r="AB38"/>
+      <x:c r="AC38"/>
+      <x:c r="AD38"/>
+      <x:c r="AE38"/>
+      <x:c r="AF38"/>
+      <x:c r="AG38"/>
+      <x:c r="AH38"/>
+      <x:c r="AI38"/>
+      <x:c r="AJ38"/>
+      <x:c r="AK38"/>
+      <x:c r="AL38"/>
+      <x:c r="AM38"/>
+      <x:c r="AN38"/>
+      <x:c r="AO38"/>
+      <x:c r="AP38"/>
+      <x:c r="AQ38"/>
+      <x:c r="AR38"/>
+      <x:c r="AS38"/>
+      <x:c r="AT38"/>
+      <x:c r="AU38"/>
+      <x:c r="AV38"/>
+      <x:c r="AW38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="str">
@@ -3845,7 +3845,7 @@
       <x:c r="M39" t="str">
         <x:v>Company: SMC Hanjurwal, Sector: Private, Number Of students: 3, Duration: 3 months, Type: Placement, Mode: Physical | Company: UOLTH, Sector: private, Number Of students: 4, Duration: 3 months, Type: Placement, Mode: Physical | Company: Children Hospital, Sector: Private, Number Of students: 2, Duration: 3months, Type: Placement, Mode: Physical | Company: PESSI KOT LAKHPAT, Sector: private, Number Of students: 2, Duration: 3 months, Type: Placement, Mode: Physical | Company: PESSI, Multan Road, Sector: private, Number Of students: 2, Duration: 3 months, Type: Placement, Mode: Physical | Company: Al- Mustafa Mazang, Sector: private, Number Of students: 2, Duration: 3 months, Type: Placement, Mode: Physical | Company: Ibrahim Eye Center, Sector: private, Number Of students: 5, Duration: 3 months, Type: Placement, Mode: Physical | Company: National Eye Hospital, Sector: private, Number Of students: 2, Duration: 3 months, Type: Placement, Mode: Physical | Company: Khizar Eye Center, Sector: private, Number Of students: 2, Duration: 3 months, Type: Placement, Mode: Physical</x:v>
       </x:c>
-      <x:c r="N39" t="str"/>
+      <x:c r="N39"/>
       <x:c r="O39" t="str">
         <x:v>New Proposals Initiated: Effect of Vitamin D Deficiency on Progression of Myopia, External Collaborators: World Council of Optometry (WCO), Focus Areas / Themes: Myopia, Current Status: Approved, Evidence: files::6a632d25350cf.jpeg</x:v>
       </x:c>
@@ -3905,22 +3905,22 @@
       <x:c r="AG39" t="str">
         <x:v>files::6a6328949fb23.pdf</x:v>
       </x:c>
-      <x:c r="AH39" t="str"/>
-      <x:c r="AI39" t="str"/>
-      <x:c r="AJ39" t="str"/>
-      <x:c r="AK39" t="str"/>
-      <x:c r="AL39" t="str"/>
-      <x:c r="AM39" t="str"/>
-      <x:c r="AN39" t="str"/>
-      <x:c r="AO39" t="str"/>
-      <x:c r="AP39" t="str"/>
-      <x:c r="AQ39" t="str"/>
-      <x:c r="AR39" t="str"/>
-      <x:c r="AS39" t="str"/>
-      <x:c r="AT39" t="str"/>
-      <x:c r="AU39" t="str"/>
-      <x:c r="AV39" t="str"/>
-      <x:c r="AW39" t="str"/>
+      <x:c r="AH39"/>
+      <x:c r="AI39"/>
+      <x:c r="AJ39"/>
+      <x:c r="AK39"/>
+      <x:c r="AL39"/>
+      <x:c r="AM39"/>
+      <x:c r="AN39"/>
+      <x:c r="AO39"/>
+      <x:c r="AP39"/>
+      <x:c r="AQ39"/>
+      <x:c r="AR39"/>
+      <x:c r="AS39"/>
+      <x:c r="AT39"/>
+      <x:c r="AU39"/>
+      <x:c r="AV39"/>
+      <x:c r="AW39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str">
@@ -3956,44 +3956,44 @@
       <x:c r="K40" t="str">
         <x:v>Activity Type: IV, How Many: 1, Name Of Organization Planned with: Shaukat Khanum Memorial Cancer Hospital, Lahore, Planned: Yes, Datev Planned on: 2026-05-20 | Activity Type: IV, How Many: 1, Name Of Organization Planned with: The University of Lahore Teaching Hospital, Lahore, Planned: Yes, Datev Planned on: 2026-04-21 | Activity Type: IV, How Many: 1, Name Of Organization Planned with: Akhter Saeed Hospital, DHA EME, Canal Road, Lahore, Planned: Yes, Datev Planned on: 2026-05-20 | Activity Type: IV, How Many: 1, Name Of Organization Planned with: Farooq Hospital, Westwood Colony Lahore, Planned: Yes, Datev Planned on: 2026-05-20 | Activity Type: IV, How Many: 1, Name Of Organization Planned with: Luxurious Design &amp; Built (Pvt.) Ltd. Chinar Bag, Lahore, Planned: Yes, Datev Planned on: 2026-05-07 | Activity Type: IV, How Many: 1, Name Of Organization Planned with: Eratech Engineering Company, Khayaban-e-Amin, Lahore, Planned: Yes, Datev Planned on: 2026-05-28 | Activity Type: IV, How Many: 1, Name Of Organization Planned with: Lahore Engineering Consultant (LEC), Bahria Orchard, Lahore, Planned: Yes, Datev Planned on: 2026-06-18 | Activity Type: IV, How Many: 1, Name Of Organization Planned with: Raza Engineers Construction, Piass College, Kasur, Planned: Yes, Datev Planned on: 2026-06-18 | Activity Type: IV, How Many: 1, Name Of Organization Planned with: Technology Links (Pvt.) Ltd., Gulberg III, Lahore, Planned: Yes, Datev Planned on: 2026-05-22 | Activity Type: IV, How Many: 1, Name Of Organization Planned with: Lahore Electric Supply Company (LESCO), Rana Town, Lahore, Planned: Yes, Datev Planned on: 2026-05-13 | Activity Type: IV, How Many: 1, Name Of Organization Planned with: US Digihub, Gulberg Main Market Lahore, Planned: Yes, Datev Planned on: 2026-04-06 | Activity Type: IV, How Many: 1, Name Of Organization Planned with: US Mobile, Gulberg III, Lahore, Planned: Yes, Datev Planned on: 2026-04-16 | </x:v>
       </x:c>
-      <x:c r="L40" t="str"/>
-      <x:c r="M40" t="str"/>
-      <x:c r="N40" t="str"/>
-      <x:c r="O40" t="str"/>
-      <x:c r="P40" t="str"/>
-      <x:c r="Q40" t="str"/>
-      <x:c r="R40" t="str"/>
-      <x:c r="S40" t="str"/>
-      <x:c r="T40" t="str"/>
-      <x:c r="U40" t="str"/>
-      <x:c r="V40" t="str"/>
-      <x:c r="W40" t="str"/>
-      <x:c r="X40" t="str"/>
-      <x:c r="Y40" t="str"/>
-      <x:c r="Z40" t="str"/>
-      <x:c r="AA40" t="str"/>
-      <x:c r="AB40" t="str"/>
-      <x:c r="AC40" t="str"/>
-      <x:c r="AD40" t="str"/>
-      <x:c r="AE40" t="str"/>
-      <x:c r="AF40" t="str"/>
-      <x:c r="AG40" t="str"/>
-      <x:c r="AH40" t="str"/>
-      <x:c r="AI40" t="str"/>
-      <x:c r="AJ40" t="str"/>
-      <x:c r="AK40" t="str"/>
-      <x:c r="AL40" t="str"/>
-      <x:c r="AM40" t="str"/>
-      <x:c r="AN40" t="str"/>
-      <x:c r="AO40" t="str"/>
-      <x:c r="AP40" t="str"/>
-      <x:c r="AQ40" t="str"/>
-      <x:c r="AR40" t="str"/>
-      <x:c r="AS40" t="str"/>
-      <x:c r="AT40" t="str"/>
-      <x:c r="AU40" t="str"/>
-      <x:c r="AV40" t="str"/>
-      <x:c r="AW40" t="str"/>
+      <x:c r="L40"/>
+      <x:c r="M40"/>
+      <x:c r="N40"/>
+      <x:c r="O40"/>
+      <x:c r="P40"/>
+      <x:c r="Q40"/>
+      <x:c r="R40"/>
+      <x:c r="S40"/>
+      <x:c r="T40"/>
+      <x:c r="U40"/>
+      <x:c r="V40"/>
+      <x:c r="W40"/>
+      <x:c r="X40"/>
+      <x:c r="Y40"/>
+      <x:c r="Z40"/>
+      <x:c r="AA40"/>
+      <x:c r="AB40"/>
+      <x:c r="AC40"/>
+      <x:c r="AD40"/>
+      <x:c r="AE40"/>
+      <x:c r="AF40"/>
+      <x:c r="AG40"/>
+      <x:c r="AH40"/>
+      <x:c r="AI40"/>
+      <x:c r="AJ40"/>
+      <x:c r="AK40"/>
+      <x:c r="AL40"/>
+      <x:c r="AM40"/>
+      <x:c r="AN40"/>
+      <x:c r="AO40"/>
+      <x:c r="AP40"/>
+      <x:c r="AQ40"/>
+      <x:c r="AR40"/>
+      <x:c r="AS40"/>
+      <x:c r="AT40"/>
+      <x:c r="AU40"/>
+      <x:c r="AV40"/>
+      <x:c r="AW40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="str">
@@ -4029,12 +4029,12 @@
       <x:c r="K41" t="str">
         <x:v>Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: Mediterranean Agronomic Institute of Montpellier (CIHEAM Montpellier), France, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-11-05, Remarks/Result: Successfully conducted Guest Lecture Series Episode 12 titled "Adoption of Innovative Food Processing Technologies: Insights from the EXCEL4MED Project and Implications for Emerging Economies." The session was delivered by Dr. Aybike Bayraktar, Postdoctoral Researcher, CIHEAM Montpellier, France, with participation of approximately 40 students and faculty members. The lecture strengthened international academic engagement and exposed participants to global research collaborations, sustainable agri-food systems, and technology adoption in emerging economies. | Activity Type: Alumni Talk / Mentoring, How Many: -1, Name Of Organization Planned with: University of Okara, Planned: Yes, Scheduled: Yes, Datev Planned on: 2027-05-06, Remarks/Result: uccessfully organized an Alumni Session titled "Economics in the Age of AI: Future Careers, Skills &amp; Opportunities." The session was delivered by alumna Ms. Aniqa Ijaz (University of Okara) and hosted by Dr. Afshan Hamid. Students were mentored on emerging career opportunities, AI applications in economics, required future skills, and higher education pathways. The session strengthened alumni engagement, promoted career awareness, and fostered professional networking between alumni and current students. | Activity Type: Alumni Talk / Mentoring, How Many: -1, Name Of Organization Planned with: University of Okara, Planned: Yes, Scheduled: Yes, Datev Planned on: 2027-05-06, Remarks/Result: uccessfully organized an Alumni Session titled "Economics in the Age of AI: Future Careers, Skills &amp; Opportunities." The session was delivered by alumna Ms. Aniqa Ijaz (University of Okara) and hosted by Dr. Afshan Hamid. Students were mentored on emerging career opportunities, AI applications in economics, required future skills, and higher education pathways. The session strengthened alumni engagement, promoted career awareness, and fostered professional networking between alumni and current students. | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: Forman Christian College (A Chartered University), University of Karachi, SOAS University of London, University of Oxford, Charter Cities Institute (CCI), Africa Urban Lab (AUL), Zanzibar Research Centre for Socio-Economic and Policy Analysis (ZRCP), Parsons Corporation, Royal Commission for Yanbu (Saudi Arabia), Urban Unit (Punjab Board of Investment &amp; Trade), Planned: Yes, Scheduled: Yes</x:v>
       </x:c>
-      <x:c r="L41" t="str"/>
-      <x:c r="M41" t="str"/>
-      <x:c r="N41" t="str"/>
-      <x:c r="O41" t="str"/>
-      <x:c r="P41" t="str"/>
-      <x:c r="Q41" t="str"/>
+      <x:c r="L41"/>
+      <x:c r="M41"/>
+      <x:c r="N41"/>
+      <x:c r="O41"/>
+      <x:c r="P41"/>
+      <x:c r="Q41"/>
       <x:c r="R41" t="str">
         <x:v>Item: Guest Visit/Meeting Reports, Evidence Attached: files::6a6057d3e445e.jpeg, Remarks/Folder Reference/URLs: https://uolconnect.workvivo.com/news/303776 | Item: Photo Evidence, Evidence Attached: files::6a6057ed0d60c.jpeg | Item: Photo Evidence, Evidence Attached: files::6a6057ba8552a.jpeg</x:v>
       </x:c>
@@ -4110,22 +4110,22 @@
       <x:c r="AG41" t="str">
         <x:v>files::6a701c156dab9.jpeg</x:v>
       </x:c>
-      <x:c r="AH41" t="str"/>
-      <x:c r="AI41" t="str"/>
-      <x:c r="AJ41" t="str"/>
-      <x:c r="AK41" t="str"/>
-      <x:c r="AL41" t="str"/>
-      <x:c r="AM41" t="str"/>
-      <x:c r="AN41" t="str"/>
-      <x:c r="AO41" t="str"/>
-      <x:c r="AP41" t="str"/>
-      <x:c r="AQ41" t="str"/>
-      <x:c r="AR41" t="str"/>
-      <x:c r="AS41" t="str"/>
-      <x:c r="AT41" t="str"/>
-      <x:c r="AU41" t="str"/>
-      <x:c r="AV41" t="str"/>
-      <x:c r="AW41" t="str"/>
+      <x:c r="AH41"/>
+      <x:c r="AI41"/>
+      <x:c r="AJ41"/>
+      <x:c r="AK41"/>
+      <x:c r="AL41"/>
+      <x:c r="AM41"/>
+      <x:c r="AN41"/>
+      <x:c r="AO41"/>
+      <x:c r="AP41"/>
+      <x:c r="AQ41"/>
+      <x:c r="AR41"/>
+      <x:c r="AS41"/>
+      <x:c r="AT41"/>
+      <x:c r="AU41"/>
+      <x:c r="AV41"/>
+      <x:c r="AW41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="str">
@@ -4161,44 +4161,44 @@
       <x:c r="K42" t="str">
         <x:v>Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: GC College Railway Road, Lahore, Planned: Yes, Datev Planned on: 2026-02-26 | Activity Type: Seminar / Conference / Workshop, How Many: 1, Planned: Yes, Datev Planned on: 2026-02-10 | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: STC Faisalabad, Planned: Yes, Datev Planned on: 2026-04-23 | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: GCT Samanabad, Lahore, Planned: Yes, Datev Planned on: 2026-04-22 | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: GCT Pindi Bhattian, Planned: Yes, Datev Planned on: 2026-04-22 | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: GCT Sangla Hill, Planned: Yes, Datev Planned on: 2026-05-14</x:v>
       </x:c>
-      <x:c r="L42" t="str"/>
-      <x:c r="M42" t="str"/>
-      <x:c r="N42" t="str"/>
-      <x:c r="O42" t="str"/>
-      <x:c r="P42" t="str"/>
-      <x:c r="Q42" t="str"/>
-      <x:c r="R42" t="str"/>
-      <x:c r="S42" t="str"/>
-      <x:c r="T42" t="str"/>
-      <x:c r="U42" t="str"/>
-      <x:c r="V42" t="str"/>
-      <x:c r="W42" t="str"/>
-      <x:c r="X42" t="str"/>
-      <x:c r="Y42" t="str"/>
-      <x:c r="Z42" t="str"/>
-      <x:c r="AA42" t="str"/>
-      <x:c r="AB42" t="str"/>
-      <x:c r="AC42" t="str"/>
-      <x:c r="AD42" t="str"/>
-      <x:c r="AE42" t="str"/>
-      <x:c r="AF42" t="str"/>
-      <x:c r="AG42" t="str"/>
-      <x:c r="AH42" t="str"/>
-      <x:c r="AI42" t="str"/>
-      <x:c r="AJ42" t="str"/>
-      <x:c r="AK42" t="str"/>
-      <x:c r="AL42" t="str"/>
-      <x:c r="AM42" t="str"/>
-      <x:c r="AN42" t="str"/>
-      <x:c r="AO42" t="str"/>
-      <x:c r="AP42" t="str"/>
-      <x:c r="AQ42" t="str"/>
-      <x:c r="AR42" t="str"/>
-      <x:c r="AS42" t="str"/>
-      <x:c r="AT42" t="str"/>
-      <x:c r="AU42" t="str"/>
-      <x:c r="AV42" t="str"/>
-      <x:c r="AW42" t="str"/>
+      <x:c r="L42"/>
+      <x:c r="M42"/>
+      <x:c r="N42"/>
+      <x:c r="O42"/>
+      <x:c r="P42"/>
+      <x:c r="Q42"/>
+      <x:c r="R42"/>
+      <x:c r="S42"/>
+      <x:c r="T42"/>
+      <x:c r="U42"/>
+      <x:c r="V42"/>
+      <x:c r="W42"/>
+      <x:c r="X42"/>
+      <x:c r="Y42"/>
+      <x:c r="Z42"/>
+      <x:c r="AA42"/>
+      <x:c r="AB42"/>
+      <x:c r="AC42"/>
+      <x:c r="AD42"/>
+      <x:c r="AE42"/>
+      <x:c r="AF42"/>
+      <x:c r="AG42"/>
+      <x:c r="AH42"/>
+      <x:c r="AI42"/>
+      <x:c r="AJ42"/>
+      <x:c r="AK42"/>
+      <x:c r="AL42"/>
+      <x:c r="AM42"/>
+      <x:c r="AN42"/>
+      <x:c r="AO42"/>
+      <x:c r="AP42"/>
+      <x:c r="AQ42"/>
+      <x:c r="AR42"/>
+      <x:c r="AS42"/>
+      <x:c r="AT42"/>
+      <x:c r="AU42"/>
+      <x:c r="AV42"/>
+      <x:c r="AW42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="str">
@@ -4216,54 +4216,54 @@
       <x:c r="E43" t="str">
         <x:v>22 July 2026</x:v>
       </x:c>
-      <x:c r="F43" t="str"/>
-      <x:c r="G43" t="str"/>
-      <x:c r="H43" t="str"/>
-      <x:c r="I43" t="str"/>
-      <x:c r="J43" t="str"/>
+      <x:c r="F43"/>
+      <x:c r="G43"/>
+      <x:c r="H43"/>
+      <x:c r="I43"/>
+      <x:c r="J43"/>
       <x:c r="K43" t="str">
         <x:v>Activity Type: Guest Lecture, How Many: 1, Name Of Organization Planned with: Franklin University Switzerland, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-04-06, Remarks/Result: An interactive session</x:v>
       </x:c>
-      <x:c r="L43" t="str"/>
-      <x:c r="M43" t="str"/>
-      <x:c r="N43" t="str"/>
-      <x:c r="O43" t="str"/>
-      <x:c r="P43" t="str"/>
-      <x:c r="Q43" t="str"/>
+      <x:c r="L43"/>
+      <x:c r="M43"/>
+      <x:c r="N43"/>
+      <x:c r="O43"/>
+      <x:c r="P43"/>
+      <x:c r="Q43"/>
       <x:c r="R43" t="str">
         <x:v>Item: Guest Visit/Meeting Reports, Evidence Attached: files::6a60509db70f8.jpg</x:v>
       </x:c>
-      <x:c r="S43" t="str"/>
-      <x:c r="T43" t="str"/>
-      <x:c r="U43" t="str"/>
-      <x:c r="V43" t="str"/>
-      <x:c r="W43" t="str"/>
-      <x:c r="X43" t="str"/>
-      <x:c r="Y43" t="str"/>
-      <x:c r="Z43" t="str"/>
-      <x:c r="AA43" t="str"/>
-      <x:c r="AB43" t="str"/>
-      <x:c r="AC43" t="str"/>
-      <x:c r="AD43" t="str"/>
-      <x:c r="AE43" t="str"/>
-      <x:c r="AF43" t="str"/>
-      <x:c r="AG43" t="str"/>
-      <x:c r="AH43" t="str"/>
-      <x:c r="AI43" t="str"/>
-      <x:c r="AJ43" t="str"/>
-      <x:c r="AK43" t="str"/>
-      <x:c r="AL43" t="str"/>
-      <x:c r="AM43" t="str"/>
-      <x:c r="AN43" t="str"/>
-      <x:c r="AO43" t="str"/>
-      <x:c r="AP43" t="str"/>
-      <x:c r="AQ43" t="str"/>
-      <x:c r="AR43" t="str"/>
-      <x:c r="AS43" t="str"/>
-      <x:c r="AT43" t="str"/>
-      <x:c r="AU43" t="str"/>
-      <x:c r="AV43" t="str"/>
-      <x:c r="AW43" t="str"/>
+      <x:c r="S43"/>
+      <x:c r="T43"/>
+      <x:c r="U43"/>
+      <x:c r="V43"/>
+      <x:c r="W43"/>
+      <x:c r="X43"/>
+      <x:c r="Y43"/>
+      <x:c r="Z43"/>
+      <x:c r="AA43"/>
+      <x:c r="AB43"/>
+      <x:c r="AC43"/>
+      <x:c r="AD43"/>
+      <x:c r="AE43"/>
+      <x:c r="AF43"/>
+      <x:c r="AG43"/>
+      <x:c r="AH43"/>
+      <x:c r="AI43"/>
+      <x:c r="AJ43"/>
+      <x:c r="AK43"/>
+      <x:c r="AL43"/>
+      <x:c r="AM43"/>
+      <x:c r="AN43"/>
+      <x:c r="AO43"/>
+      <x:c r="AP43"/>
+      <x:c r="AQ43"/>
+      <x:c r="AR43"/>
+      <x:c r="AS43"/>
+      <x:c r="AT43"/>
+      <x:c r="AU43"/>
+      <x:c r="AV43"/>
+      <x:c r="AW43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="str">
@@ -4299,52 +4299,52 @@
       <x:c r="K44" t="str">
         <x:v>Activity Type: Internship/Placement, How Many: 5 | </x:v>
       </x:c>
-      <x:c r="L44" t="str"/>
+      <x:c r="L44"/>
       <x:c r="M44" t="str">
         <x:v>Company: Multiple, Sector: Public and private, Number Of students: 102, Duration: 4 to 6 weeks, Type: Intership, Mode: Physical, Evidence: files::6a604efa01357.xlsx | </x:v>
       </x:c>
-      <x:c r="N44" t="str"/>
-      <x:c r="O44" t="str"/>
-      <x:c r="P44" t="str"/>
-      <x:c r="Q44" t="str"/>
-      <x:c r="R44" t="str"/>
-      <x:c r="S44" t="str"/>
-      <x:c r="T44" t="str"/>
-      <x:c r="U44" t="str"/>
-      <x:c r="V44" t="str"/>
-      <x:c r="W44" t="str"/>
+      <x:c r="N44"/>
+      <x:c r="O44"/>
+      <x:c r="P44"/>
+      <x:c r="Q44"/>
+      <x:c r="R44"/>
+      <x:c r="S44"/>
+      <x:c r="T44"/>
+      <x:c r="U44"/>
+      <x:c r="V44"/>
+      <x:c r="W44"/>
       <x:c r="X44" t="str">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="Y44" t="str">
         <x:v>Lecturer</x:v>
       </x:c>
-      <x:c r="Z44" t="str"/>
+      <x:c r="Z44"/>
       <x:c r="AA44" t="str">
         <x:v>+923334805118</x:v>
       </x:c>
-      <x:c r="AB44" t="str"/>
-      <x:c r="AC44" t="str"/>
-      <x:c r="AD44" t="str"/>
-      <x:c r="AE44" t="str"/>
-      <x:c r="AF44" t="str"/>
-      <x:c r="AG44" t="str"/>
-      <x:c r="AH44" t="str"/>
-      <x:c r="AI44" t="str"/>
-      <x:c r="AJ44" t="str"/>
-      <x:c r="AK44" t="str"/>
-      <x:c r="AL44" t="str"/>
-      <x:c r="AM44" t="str"/>
-      <x:c r="AN44" t="str"/>
-      <x:c r="AO44" t="str"/>
-      <x:c r="AP44" t="str"/>
-      <x:c r="AQ44" t="str"/>
-      <x:c r="AR44" t="str"/>
-      <x:c r="AS44" t="str"/>
-      <x:c r="AT44" t="str"/>
-      <x:c r="AU44" t="str"/>
-      <x:c r="AV44" t="str"/>
-      <x:c r="AW44" t="str"/>
+      <x:c r="AB44"/>
+      <x:c r="AC44"/>
+      <x:c r="AD44"/>
+      <x:c r="AE44"/>
+      <x:c r="AF44"/>
+      <x:c r="AG44"/>
+      <x:c r="AH44"/>
+      <x:c r="AI44"/>
+      <x:c r="AJ44"/>
+      <x:c r="AK44"/>
+      <x:c r="AL44"/>
+      <x:c r="AM44"/>
+      <x:c r="AN44"/>
+      <x:c r="AO44"/>
+      <x:c r="AP44"/>
+      <x:c r="AQ44"/>
+      <x:c r="AR44"/>
+      <x:c r="AS44"/>
+      <x:c r="AT44"/>
+      <x:c r="AU44"/>
+      <x:c r="AV44"/>
+      <x:c r="AW44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="str">
@@ -4383,43 +4383,43 @@
       <x:c r="L45" t="str">
         <x:v>MOU Type: Industry</x:v>
       </x:c>
-      <x:c r="M45" t="str"/>
-      <x:c r="N45" t="str"/>
-      <x:c r="O45" t="str"/>
-      <x:c r="P45" t="str"/>
-      <x:c r="Q45" t="str"/>
-      <x:c r="R45" t="str"/>
-      <x:c r="S45" t="str"/>
-      <x:c r="T45" t="str"/>
-      <x:c r="U45" t="str"/>
-      <x:c r="V45" t="str"/>
-      <x:c r="W45" t="str"/>
-      <x:c r="X45" t="str"/>
-      <x:c r="Y45" t="str"/>
-      <x:c r="Z45" t="str"/>
-      <x:c r="AA45" t="str"/>
-      <x:c r="AB45" t="str"/>
-      <x:c r="AC45" t="str"/>
-      <x:c r="AD45" t="str"/>
-      <x:c r="AE45" t="str"/>
-      <x:c r="AF45" t="str"/>
-      <x:c r="AG45" t="str"/>
-      <x:c r="AH45" t="str"/>
-      <x:c r="AI45" t="str"/>
-      <x:c r="AJ45" t="str"/>
-      <x:c r="AK45" t="str"/>
-      <x:c r="AL45" t="str"/>
-      <x:c r="AM45" t="str"/>
-      <x:c r="AN45" t="str"/>
-      <x:c r="AO45" t="str"/>
-      <x:c r="AP45" t="str"/>
-      <x:c r="AQ45" t="str"/>
-      <x:c r="AR45" t="str"/>
-      <x:c r="AS45" t="str"/>
-      <x:c r="AT45" t="str"/>
-      <x:c r="AU45" t="str"/>
-      <x:c r="AV45" t="str"/>
-      <x:c r="AW45" t="str"/>
+      <x:c r="M45"/>
+      <x:c r="N45"/>
+      <x:c r="O45"/>
+      <x:c r="P45"/>
+      <x:c r="Q45"/>
+      <x:c r="R45"/>
+      <x:c r="S45"/>
+      <x:c r="T45"/>
+      <x:c r="U45"/>
+      <x:c r="V45"/>
+      <x:c r="W45"/>
+      <x:c r="X45"/>
+      <x:c r="Y45"/>
+      <x:c r="Z45"/>
+      <x:c r="AA45"/>
+      <x:c r="AB45"/>
+      <x:c r="AC45"/>
+      <x:c r="AD45"/>
+      <x:c r="AE45"/>
+      <x:c r="AF45"/>
+      <x:c r="AG45"/>
+      <x:c r="AH45"/>
+      <x:c r="AI45"/>
+      <x:c r="AJ45"/>
+      <x:c r="AK45"/>
+      <x:c r="AL45"/>
+      <x:c r="AM45"/>
+      <x:c r="AN45"/>
+      <x:c r="AO45"/>
+      <x:c r="AP45"/>
+      <x:c r="AQ45"/>
+      <x:c r="AR45"/>
+      <x:c r="AS45"/>
+      <x:c r="AT45"/>
+      <x:c r="AU45"/>
+      <x:c r="AV45"/>
+      <x:c r="AW45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
@@ -4455,19 +4455,19 @@
       <x:c r="K46" t="str">
         <x:v>Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: UOL, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-05-10, Remarks/Result: Mr Tahir Fareed delivered a lecture on research techniques. Activity Concluded. | Activity Type: GLIT, How Many: 1, Name Of Organization Planned with: UOL, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-05-24, Remarks/Result: Ms Rimsha Qayyum delivered a lectur on Qualitative Research Methods. Activity Concluded. | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: UK, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-06-18, Remarks/Result: International Webinar Series 2026; Writing Literature Review Ethically in the Age of AI (Resource Person Yanhua Liu) UK, The webinar aimed to enhance participants’ understanding of effective literature review practices, ethical academic writing, and the responsible use of Artificial Intelligence (AI) in research. Activity Concluded. | Activity Type: Others, How Many: 1, Name Of Organization Planned with: Department of Information Management (DoIM) UOL, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-06-22, Remarks/Result: Student Poster Exhibition and Competition 2026 at The Department of Information Management &amp; Completion of Batch Spring 2026 First Semester, and 2nd Semester by Batch Fall 2025. To promoted research culture and academic creativity among students  and	strengthened research communication and poster presentation skills. Activity Concluded. | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: Department of Information Management (DoIM) UOL, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-07-09, Remarks/Result: 𝐁𝐞𝐡𝐚𝐯𝐢𝐨𝐫𝐚𝐥 𝐌𝐚𝐧𝐚𝐠𝐞𝐦𝐞𝐧𝐭: 𝐓𝐡𝐞 𝐉𝐨𝐮𝐫𝐧𝐞𝐲 𝐨𝐟 𝐏𝐫𝐨𝐟𝐞𝐬𝐢𝐨𝐧𝐚𝐥 𝐄𝐱𝐜𝐞𝐥𝐞𝐧𝐜𝐞. (Resource Person Prf. Dr. Zaheer Ahmad)An excellent opportunity for library professionals to enhance the attitudes, skills, and behaviors essential for professional success. Activity Concluded. | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: COMSATS University Islamabad, Lahore Campus, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-07-14, Remarks/Result: 𝐆𝐥𝐨𝐛𝐚𝐥 𝐃𝐢𝐚𝐥𝐨𝐠𝐮𝐞 𝐨𝐧 𝐑𝐞𝐬𝐞𝐚𝐫𝐜𝐡 𝐁𝐞𝐲𝐨𝐧𝐝 𝐁𝐨𝐮𝐧𝐝, This academic dialogue aims to bring together researchers, faculty members, and professionals to explore emerging avenues for international research collaboration, interdisciplinary engagement, and global academic networking. Activity Concluded.𝐚𝐫𝐢𝐞𝐬: 𝐎𝐩𝐩𝐨𝐫𝐭𝐮𝐧𝐢𝐭𝐢𝐞𝐬 𝐟𝐨𝐫 𝐈𝐧𝐭𝐞𝐫𝐧𝐚𝐭𝐢𝐨𝐧𝐚𝐥 𝐂𝐨𝐥𝐥𝐚𝐛𝐨𝐫𝐚𝐭𝐢𝐨𝐧, | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: Sustainable Development Policy Institute (SDPI), Islamabad, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-07-23, Remarks/Result: Synthesizing Evidence for Policy Research, during the workshop, Dr. Zaheer highlighted the importance of evidence synthesis in producing credible and policy-relevant research. He introduced systematic approaches to identifying, evaluating, and synthesizing scholarly literature, while demonstrating the responsible use of AI tools to support literature reviews and evidence-based policymaking. The session concluded with practical activities on effective literature searching, reference management, and integrating evidence into policy narratives. Participants gained valuable insights into strengthening the quality, transparency, and impact of policy research through ethical and responsible research practices. | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: The Pakistan Scientific and Technological Information Centre (PSTIC), Regional Office Lahore, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-07-28, Remarks/Result: The webinar on Intelligent Literature Reviews: AI Tools, Critical Thinking, and Research Ethics,  Prof. Dr. Zaheer Ahmad, Resource Person, discussed the significance of literature reviews in identifying research gaps and building a strong scholarly foundation. He demonstrated how AI-powered tools can support literature searching, evidence synthesis, summarization, reference management, and academic writing while emphasizing that researchers must apply critical thinking, sound judgment, and ethical practices throughout the research process. He also stressed the importance of verifying AI-generated content, avoiding plagiarism and fabricated citations, and ensuring transparency in the responsible use of AI.</x:v>
       </x:c>
-      <x:c r="L46" t="str"/>
-      <x:c r="M46" t="str"/>
-      <x:c r="N46" t="str"/>
-      <x:c r="O46" t="str"/>
-      <x:c r="P46" t="str"/>
-      <x:c r="Q46" t="str"/>
+      <x:c r="L46"/>
+      <x:c r="M46"/>
+      <x:c r="N46"/>
+      <x:c r="O46"/>
+      <x:c r="P46"/>
+      <x:c r="Q46"/>
       <x:c r="R46" t="str">
         <x:v>Item: Event Flyers/Reports, Remarks/Folder Reference/URLs: workbook day | Item: Event Flyers/Reports, Remarks/Folder Reference/URLs: workshop</x:v>
       </x:c>
-      <x:c r="S46" t="str"/>
-      <x:c r="T46" t="str"/>
-      <x:c r="U46" t="str"/>
-      <x:c r="V46" t="str"/>
+      <x:c r="S46"/>
+      <x:c r="T46"/>
+      <x:c r="U46"/>
+      <x:c r="V46"/>
       <x:c r="W46" t="str">
         <x:v>2026-02-01</x:v>
       </x:c>
@@ -4489,26 +4489,26 @@
       <x:c r="AC46" t="str">
         <x:v>Resource Person Yanhua Liu (UK)</x:v>
       </x:c>
-      <x:c r="AD46" t="str"/>
-      <x:c r="AE46" t="str"/>
-      <x:c r="AF46" t="str"/>
-      <x:c r="AG46" t="str"/>
-      <x:c r="AH46" t="str"/>
-      <x:c r="AI46" t="str"/>
-      <x:c r="AJ46" t="str"/>
-      <x:c r="AK46" t="str"/>
-      <x:c r="AL46" t="str"/>
-      <x:c r="AM46" t="str"/>
-      <x:c r="AN46" t="str"/>
-      <x:c r="AO46" t="str"/>
-      <x:c r="AP46" t="str"/>
-      <x:c r="AQ46" t="str"/>
-      <x:c r="AR46" t="str"/>
-      <x:c r="AS46" t="str"/>
-      <x:c r="AT46" t="str"/>
-      <x:c r="AU46" t="str"/>
-      <x:c r="AV46" t="str"/>
-      <x:c r="AW46" t="str"/>
+      <x:c r="AD46"/>
+      <x:c r="AE46"/>
+      <x:c r="AF46"/>
+      <x:c r="AG46"/>
+      <x:c r="AH46"/>
+      <x:c r="AI46"/>
+      <x:c r="AJ46"/>
+      <x:c r="AK46"/>
+      <x:c r="AL46"/>
+      <x:c r="AM46"/>
+      <x:c r="AN46"/>
+      <x:c r="AO46"/>
+      <x:c r="AP46"/>
+      <x:c r="AQ46"/>
+      <x:c r="AR46"/>
+      <x:c r="AS46"/>
+      <x:c r="AT46"/>
+      <x:c r="AU46"/>
+      <x:c r="AV46"/>
+      <x:c r="AW46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="str">
@@ -4553,7 +4553,7 @@
       <x:c r="N47" t="str">
         <x:v>Activities Conducted: Alumni Talks,, Other Remarks: The sessions encouraged stronger alumni-university relationships and created opportunities for future collaboration., Purpose &amp; Outcomes:: The activities aimed to enhance students' career awareness, build professional networks, and motivate them through real-world success stories., Feedback Highlights / Reflections:: Students found the sessions informative and motivating, appreciating the practical insights and interactive discussions with alumni., Evidence: files::6a60651f1da83.zip</x:v>
       </x:c>
-      <x:c r="O47" t="str"/>
+      <x:c r="O47"/>
       <x:c r="P47" t="str">
         <x:v>Area / Domain: Research and Innovation, Challenge Description: Limited resources and exposure to emerging 
 research trends and technologies., Support Needed: Access to research databases, funding opportunities, and 
@@ -4567,10 +4567,10 @@
       <x:c r="R47" t="str">
         <x:v>Item: Media Coverage/Social Links, Evidence Attached: files::6a619eb6b1ca5.zip, Remarks/Folder Reference/URLs: All Supporting Documents Uploaded | Item: Photo Evidence, Evidence Attached: files::6a619ebfb3a30.zip, Remarks/Folder Reference/URLs: All Supporting Documents Uploaded | Item: Guest Visit/Meeting Reports, Evidence Attached: files::6a619f1b212cd.zip, Remarks/Folder Reference/URLs: All Supporting Documents Uploaded | </x:v>
       </x:c>
-      <x:c r="S47" t="str"/>
-      <x:c r="T47" t="str"/>
-      <x:c r="U47" t="str"/>
-      <x:c r="V47" t="str"/>
+      <x:c r="S47"/>
+      <x:c r="T47"/>
+      <x:c r="U47"/>
+      <x:c r="V47"/>
       <x:c r="W47" t="str">
         <x:v>2026-07-21</x:v>
       </x:c>
@@ -4586,28 +4586,28 @@
       <x:c r="AA47" t="str">
         <x:v>+923070573791</x:v>
       </x:c>
-      <x:c r="AB47" t="str"/>
-      <x:c r="AC47" t="str"/>
-      <x:c r="AD47" t="str"/>
-      <x:c r="AE47" t="str"/>
-      <x:c r="AF47" t="str"/>
-      <x:c r="AG47" t="str"/>
-      <x:c r="AH47" t="str"/>
-      <x:c r="AI47" t="str"/>
-      <x:c r="AJ47" t="str"/>
-      <x:c r="AK47" t="str"/>
-      <x:c r="AL47" t="str"/>
-      <x:c r="AM47" t="str"/>
-      <x:c r="AN47" t="str"/>
-      <x:c r="AO47" t="str"/>
-      <x:c r="AP47" t="str"/>
-      <x:c r="AQ47" t="str"/>
-      <x:c r="AR47" t="str"/>
-      <x:c r="AS47" t="str"/>
-      <x:c r="AT47" t="str"/>
-      <x:c r="AU47" t="str"/>
-      <x:c r="AV47" t="str"/>
-      <x:c r="AW47" t="str"/>
+      <x:c r="AB47"/>
+      <x:c r="AC47"/>
+      <x:c r="AD47"/>
+      <x:c r="AE47"/>
+      <x:c r="AF47"/>
+      <x:c r="AG47"/>
+      <x:c r="AH47"/>
+      <x:c r="AI47"/>
+      <x:c r="AJ47"/>
+      <x:c r="AK47"/>
+      <x:c r="AL47"/>
+      <x:c r="AM47"/>
+      <x:c r="AN47"/>
+      <x:c r="AO47"/>
+      <x:c r="AP47"/>
+      <x:c r="AQ47"/>
+      <x:c r="AR47"/>
+      <x:c r="AS47"/>
+      <x:c r="AT47"/>
+      <x:c r="AU47"/>
+      <x:c r="AV47"/>
+      <x:c r="AW47"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="str">
@@ -4646,16 +4646,16 @@
       <x:c r="L48" t="str">
         <x:v>Partner Institution: Chonnam National University, South Korea, Country: Korea, MOU Type: Academic, Key Activities: The agreement will open avenue of collaboration for future joint research, and project submission, Status: Under Process | Partner Institution: Ayshx, Lahore, Country: Pakistan, MOU Type: Industry, Key Activities: for R &amp; D, Status: Under Process | Partner Institution: Health Security Partners, USA, MOU Type: Industry, Key Activities: Biorisk management Pakistan, Status: Under Process</x:v>
       </x:c>
-      <x:c r="M48" t="str"/>
-      <x:c r="N48" t="str"/>
-      <x:c r="O48" t="str"/>
-      <x:c r="P48" t="str"/>
-      <x:c r="Q48" t="str"/>
-      <x:c r="R48" t="str"/>
-      <x:c r="S48" t="str"/>
-      <x:c r="T48" t="str"/>
-      <x:c r="U48" t="str"/>
-      <x:c r="V48" t="str"/>
+      <x:c r="M48"/>
+      <x:c r="N48"/>
+      <x:c r="O48"/>
+      <x:c r="P48"/>
+      <x:c r="Q48"/>
+      <x:c r="R48"/>
+      <x:c r="S48"/>
+      <x:c r="T48"/>
+      <x:c r="U48"/>
+      <x:c r="V48"/>
       <x:c r="W48" t="str">
         <x:v>2026-10-05</x:v>
       </x:c>
@@ -4668,29 +4668,29 @@
       <x:c r="Z48" t="str">
         <x:v>2026-07-20</x:v>
       </x:c>
-      <x:c r="AA48" t="str"/>
-      <x:c r="AB48" t="str"/>
-      <x:c r="AC48" t="str"/>
-      <x:c r="AD48" t="str"/>
-      <x:c r="AE48" t="str"/>
-      <x:c r="AF48" t="str"/>
-      <x:c r="AG48" t="str"/>
-      <x:c r="AH48" t="str"/>
-      <x:c r="AI48" t="str"/>
-      <x:c r="AJ48" t="str"/>
-      <x:c r="AK48" t="str"/>
-      <x:c r="AL48" t="str"/>
-      <x:c r="AM48" t="str"/>
-      <x:c r="AN48" t="str"/>
-      <x:c r="AO48" t="str"/>
-      <x:c r="AP48" t="str"/>
-      <x:c r="AQ48" t="str"/>
-      <x:c r="AR48" t="str"/>
-      <x:c r="AS48" t="str"/>
-      <x:c r="AT48" t="str"/>
-      <x:c r="AU48" t="str"/>
-      <x:c r="AV48" t="str"/>
-      <x:c r="AW48" t="str"/>
+      <x:c r="AA48"/>
+      <x:c r="AB48"/>
+      <x:c r="AC48"/>
+      <x:c r="AD48"/>
+      <x:c r="AE48"/>
+      <x:c r="AF48"/>
+      <x:c r="AG48"/>
+      <x:c r="AH48"/>
+      <x:c r="AI48"/>
+      <x:c r="AJ48"/>
+      <x:c r="AK48"/>
+      <x:c r="AL48"/>
+      <x:c r="AM48"/>
+      <x:c r="AN48"/>
+      <x:c r="AO48"/>
+      <x:c r="AP48"/>
+      <x:c r="AQ48"/>
+      <x:c r="AR48"/>
+      <x:c r="AS48"/>
+      <x:c r="AT48"/>
+      <x:c r="AU48"/>
+      <x:c r="AV48"/>
+      <x:c r="AW48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="str">
@@ -4726,44 +4726,44 @@
       <x:c r="K49" t="str">
         <x:v>Activity Type: IP, How Many: 1, Name Of Organization Planned with: 2 Space, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: AB Technologies, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Ahmaar (Pvt.) Ltd., Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 5, Name Of Organization Planned with: Async Digital, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Async Digital Software House, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 2, Name Of Organization Planned with: AWS Tech, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Bytewise Technologies, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Codexiom, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Corvit Systems, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Devsinc, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Dgware Solutions, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Ebryx (Pvt.) Ltd., Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: E-Care Solution, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Eyra Tech, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Fermi Soft, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Flicken, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: GulfBase, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Hoster99 (Web Hosting Company), Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Ibex, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: IIFA Tech, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Infinity Wave, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Innosoft Works (SMC-Private) Ltd., Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Invosage, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Kashf Foundation, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Kings Solutions, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Nexrupt technologies pvt ltd, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: OMNI Soft, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Prismware Technologies, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 5, Name Of Organization Planned with: Qubit Dynamics, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Rstack Labs, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Strategic System, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Studio 93, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Tech Lynx Overdrive, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Thingtrax, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Tx Labs, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 5, Name Of Organization Planned with: University of Engineering &amp; Technology (UET), Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Upvave, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: US Mobile, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Wix Patriots, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Wordx BPO, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Planned: Yes, Datev Planned on: 2026-02-24 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Z Space, Planned: Yes, Datev Planned on: 2026-02-24</x:v>
       </x:c>
-      <x:c r="L49" t="str"/>
-      <x:c r="M49" t="str"/>
-      <x:c r="N49" t="str"/>
-      <x:c r="O49" t="str"/>
-      <x:c r="P49" t="str"/>
-      <x:c r="Q49" t="str"/>
-      <x:c r="R49" t="str"/>
-      <x:c r="S49" t="str"/>
-      <x:c r="T49" t="str"/>
-      <x:c r="U49" t="str"/>
-      <x:c r="V49" t="str"/>
-      <x:c r="W49" t="str"/>
-      <x:c r="X49" t="str"/>
-      <x:c r="Y49" t="str"/>
-      <x:c r="Z49" t="str"/>
-      <x:c r="AA49" t="str"/>
-      <x:c r="AB49" t="str"/>
-      <x:c r="AC49" t="str"/>
-      <x:c r="AD49" t="str"/>
-      <x:c r="AE49" t="str"/>
-      <x:c r="AF49" t="str"/>
-      <x:c r="AG49" t="str"/>
-      <x:c r="AH49" t="str"/>
-      <x:c r="AI49" t="str"/>
-      <x:c r="AJ49" t="str"/>
-      <x:c r="AK49" t="str"/>
-      <x:c r="AL49" t="str"/>
-      <x:c r="AM49" t="str"/>
-      <x:c r="AN49" t="str"/>
-      <x:c r="AO49" t="str"/>
-      <x:c r="AP49" t="str"/>
-      <x:c r="AQ49" t="str"/>
-      <x:c r="AR49" t="str"/>
-      <x:c r="AS49" t="str"/>
-      <x:c r="AT49" t="str"/>
-      <x:c r="AU49" t="str"/>
-      <x:c r="AV49" t="str"/>
-      <x:c r="AW49" t="str"/>
+      <x:c r="L49"/>
+      <x:c r="M49"/>
+      <x:c r="N49"/>
+      <x:c r="O49"/>
+      <x:c r="P49"/>
+      <x:c r="Q49"/>
+      <x:c r="R49"/>
+      <x:c r="S49"/>
+      <x:c r="T49"/>
+      <x:c r="U49"/>
+      <x:c r="V49"/>
+      <x:c r="W49"/>
+      <x:c r="X49"/>
+      <x:c r="Y49"/>
+      <x:c r="Z49"/>
+      <x:c r="AA49"/>
+      <x:c r="AB49"/>
+      <x:c r="AC49"/>
+      <x:c r="AD49"/>
+      <x:c r="AE49"/>
+      <x:c r="AF49"/>
+      <x:c r="AG49"/>
+      <x:c r="AH49"/>
+      <x:c r="AI49"/>
+      <x:c r="AJ49"/>
+      <x:c r="AK49"/>
+      <x:c r="AL49"/>
+      <x:c r="AM49"/>
+      <x:c r="AN49"/>
+      <x:c r="AO49"/>
+      <x:c r="AP49"/>
+      <x:c r="AQ49"/>
+      <x:c r="AR49"/>
+      <x:c r="AS49"/>
+      <x:c r="AT49"/>
+      <x:c r="AU49"/>
+      <x:c r="AV49"/>
+      <x:c r="AW49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="str">
@@ -4799,44 +4799,44 @@
       <x:c r="K50" t="str">
         <x:v>Activity Type: IP, How Many: 2, Name Of Organization Planned with: Azhar Engineering and Power Generation (Pvt.) Ltd., Planned: Yes, Datev Planned on: 2026-02-23 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: M.S.B Engineering Services, Planned: Yes, Datev Planned on: 2026-02-23 | Activity Type: IP, How Many: 3, Name Of Organization Planned with: Machine Zone (Pvt.) Ltd., Planned: Yes, Datev Planned on: 2026-02-23 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: NIMIR Group of Companies, Planned: Yes, Datev Planned on: 2026-02-23 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Nishat Power Plant, Planned: Yes, Datev Planned on: 2026-02-23 | Activity Type: IP, How Many: 3, Name Of Organization Planned with: Project Cell (HVAC), The University of Lahore, Planned: Yes, Datev Planned on: 2026-02-23 | Activity Type: IP, How Many: 2, Name Of Organization Planned with: S.T Engineering Services (Pvt.) Ltd., Planned: Yes, Datev Planned on: 2026-02-23 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Saab Moulded Industry (MDK), Planned: Yes, Datev Planned on: 2026-02-23 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Toyota HN Motors, Planned: Yes, Datev Planned on: 2026-02-23 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Xida Mould, Planned: Yes, Datev Planned on: 2026-02-23</x:v>
       </x:c>
-      <x:c r="L50" t="str"/>
-      <x:c r="M50" t="str"/>
-      <x:c r="N50" t="str"/>
-      <x:c r="O50" t="str"/>
-      <x:c r="P50" t="str"/>
-      <x:c r="Q50" t="str"/>
-      <x:c r="R50" t="str"/>
-      <x:c r="S50" t="str"/>
-      <x:c r="T50" t="str"/>
-      <x:c r="U50" t="str"/>
-      <x:c r="V50" t="str"/>
-      <x:c r="W50" t="str"/>
-      <x:c r="X50" t="str"/>
-      <x:c r="Y50" t="str"/>
-      <x:c r="Z50" t="str"/>
-      <x:c r="AA50" t="str"/>
-      <x:c r="AB50" t="str"/>
-      <x:c r="AC50" t="str"/>
-      <x:c r="AD50" t="str"/>
-      <x:c r="AE50" t="str"/>
-      <x:c r="AF50" t="str"/>
-      <x:c r="AG50" t="str"/>
-      <x:c r="AH50" t="str"/>
-      <x:c r="AI50" t="str"/>
-      <x:c r="AJ50" t="str"/>
-      <x:c r="AK50" t="str"/>
-      <x:c r="AL50" t="str"/>
-      <x:c r="AM50" t="str"/>
-      <x:c r="AN50" t="str"/>
-      <x:c r="AO50" t="str"/>
-      <x:c r="AP50" t="str"/>
-      <x:c r="AQ50" t="str"/>
-      <x:c r="AR50" t="str"/>
-      <x:c r="AS50" t="str"/>
-      <x:c r="AT50" t="str"/>
-      <x:c r="AU50" t="str"/>
-      <x:c r="AV50" t="str"/>
-      <x:c r="AW50" t="str"/>
+      <x:c r="L50"/>
+      <x:c r="M50"/>
+      <x:c r="N50"/>
+      <x:c r="O50"/>
+      <x:c r="P50"/>
+      <x:c r="Q50"/>
+      <x:c r="R50"/>
+      <x:c r="S50"/>
+      <x:c r="T50"/>
+      <x:c r="U50"/>
+      <x:c r="V50"/>
+      <x:c r="W50"/>
+      <x:c r="X50"/>
+      <x:c r="Y50"/>
+      <x:c r="Z50"/>
+      <x:c r="AA50"/>
+      <x:c r="AB50"/>
+      <x:c r="AC50"/>
+      <x:c r="AD50"/>
+      <x:c r="AE50"/>
+      <x:c r="AF50"/>
+      <x:c r="AG50"/>
+      <x:c r="AH50"/>
+      <x:c r="AI50"/>
+      <x:c r="AJ50"/>
+      <x:c r="AK50"/>
+      <x:c r="AL50"/>
+      <x:c r="AM50"/>
+      <x:c r="AN50"/>
+      <x:c r="AO50"/>
+      <x:c r="AP50"/>
+      <x:c r="AQ50"/>
+      <x:c r="AR50"/>
+      <x:c r="AS50"/>
+      <x:c r="AT50"/>
+      <x:c r="AU50"/>
+      <x:c r="AV50"/>
+      <x:c r="AW50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="str">
@@ -4872,44 +4872,44 @@
       <x:c r="K51" t="str">
         <x:v>Activity Type: IP, How Many: 1, Name Of Organization Planned with: Akhter Saeed Hospital, Planned: Yes, Datev Planned on: 2026-02-22 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Alam Medix Company, Planned: Yes, Datev Planned on: 2026-02-22 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Amarant Medical Technologies, Planned: Yes, Datev Planned on: 2026-02-22 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Econ Whizz, Planned: Yes, Datev Planned on: 2026-02-22 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Farooq Hospital, Planned: Yes, Datev Planned on: 2026-02-22 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Jinnah Hospital Lahore, Planned: Yes, Datev Planned on: 2026-02-22 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: RM Scientific Lab, UOL, Planned: Yes, Datev Planned on: 2026-02-22 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Saleem Memorial Hospital, Planned: Yes, Datev Planned on: 2026-02-22 | Activity Type: IP, How Many: 4, Name Of Organization Planned with: Shaukat Khanum Memorial Cancer Hospital, Planned: Yes, Datev Planned on: 2026-02-22 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Shifa International Hospital, Planned: Yes, Datev Planned on: 2026-02-22 | Activity Type: IP, How Many: 5, Name Of Organization Planned with: University of Lahore Teaching Hospital, Planned: Yes, Datev Planned on: 2026-02-22</x:v>
       </x:c>
-      <x:c r="L51" t="str"/>
-      <x:c r="M51" t="str"/>
-      <x:c r="N51" t="str"/>
-      <x:c r="O51" t="str"/>
-      <x:c r="P51" t="str"/>
-      <x:c r="Q51" t="str"/>
-      <x:c r="R51" t="str"/>
-      <x:c r="S51" t="str"/>
-      <x:c r="T51" t="str"/>
-      <x:c r="U51" t="str"/>
-      <x:c r="V51" t="str"/>
-      <x:c r="W51" t="str"/>
-      <x:c r="X51" t="str"/>
-      <x:c r="Y51" t="str"/>
-      <x:c r="Z51" t="str"/>
-      <x:c r="AA51" t="str"/>
-      <x:c r="AB51" t="str"/>
-      <x:c r="AC51" t="str"/>
-      <x:c r="AD51" t="str"/>
-      <x:c r="AE51" t="str"/>
-      <x:c r="AF51" t="str"/>
-      <x:c r="AG51" t="str"/>
-      <x:c r="AH51" t="str"/>
-      <x:c r="AI51" t="str"/>
-      <x:c r="AJ51" t="str"/>
-      <x:c r="AK51" t="str"/>
-      <x:c r="AL51" t="str"/>
-      <x:c r="AM51" t="str"/>
-      <x:c r="AN51" t="str"/>
-      <x:c r="AO51" t="str"/>
-      <x:c r="AP51" t="str"/>
-      <x:c r="AQ51" t="str"/>
-      <x:c r="AR51" t="str"/>
-      <x:c r="AS51" t="str"/>
-      <x:c r="AT51" t="str"/>
-      <x:c r="AU51" t="str"/>
-      <x:c r="AV51" t="str"/>
-      <x:c r="AW51" t="str"/>
+      <x:c r="L51"/>
+      <x:c r="M51"/>
+      <x:c r="N51"/>
+      <x:c r="O51"/>
+      <x:c r="P51"/>
+      <x:c r="Q51"/>
+      <x:c r="R51"/>
+      <x:c r="S51"/>
+      <x:c r="T51"/>
+      <x:c r="U51"/>
+      <x:c r="V51"/>
+      <x:c r="W51"/>
+      <x:c r="X51"/>
+      <x:c r="Y51"/>
+      <x:c r="Z51"/>
+      <x:c r="AA51"/>
+      <x:c r="AB51"/>
+      <x:c r="AC51"/>
+      <x:c r="AD51"/>
+      <x:c r="AE51"/>
+      <x:c r="AF51"/>
+      <x:c r="AG51"/>
+      <x:c r="AH51"/>
+      <x:c r="AI51"/>
+      <x:c r="AJ51"/>
+      <x:c r="AK51"/>
+      <x:c r="AL51"/>
+      <x:c r="AM51"/>
+      <x:c r="AN51"/>
+      <x:c r="AO51"/>
+      <x:c r="AP51"/>
+      <x:c r="AQ51"/>
+      <x:c r="AR51"/>
+      <x:c r="AS51"/>
+      <x:c r="AT51"/>
+      <x:c r="AU51"/>
+      <x:c r="AV51"/>
+      <x:c r="AW51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" t="str">
@@ -4945,44 +4945,44 @@
       <x:c r="K52" t="str">
         <x:v>Activity Type: IP, How Many: 1, Name Of Organization Planned with: Al Riaz Civil Engineering Services (Pvt.) Ltd., Planned: Yes, Datev Planned on: 2026-02-19 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Al Shabbir Developers, Planned: Yes, Datev Planned on: 2026-02-19 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Al Shabbir Developers, Planned: Yes, Datev Planned on: 2026-02-19 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: CCECC, Planned: Yes, Datev Planned on: 2026-02-19 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Eratech Engineering Company, Planned: Yes, Datev Planned on: 2026-02-19 | Activity Type: IP, How Many: 3, Name Of Organization Planned with: Lahore Engineering Consultant (LEC), Planned: Yes, Datev Planned on: 2026-02-19 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Luxurious Design &amp; Built (Pvt.) Ltd., Planned: Yes, Datev Planned on: 2026-02-19 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: MS Builder and Construction Co., Planned: Yes, Datev Planned on: 2026-02-19 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Nazim &amp; Qasim (Pvt.) Ltd., Planned: Yes, Datev Planned on: 2026-02-19 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Raza Engineers Construction, Planned: Yes, Datev Planned on: 2026-02-19</x:v>
       </x:c>
-      <x:c r="L52" t="str"/>
-      <x:c r="M52" t="str"/>
-      <x:c r="N52" t="str"/>
-      <x:c r="O52" t="str"/>
-      <x:c r="P52" t="str"/>
-      <x:c r="Q52" t="str"/>
-      <x:c r="R52" t="str"/>
-      <x:c r="S52" t="str"/>
-      <x:c r="T52" t="str"/>
-      <x:c r="U52" t="str"/>
-      <x:c r="V52" t="str"/>
-      <x:c r="W52" t="str"/>
-      <x:c r="X52" t="str"/>
-      <x:c r="Y52" t="str"/>
-      <x:c r="Z52" t="str"/>
-      <x:c r="AA52" t="str"/>
-      <x:c r="AB52" t="str"/>
-      <x:c r="AC52" t="str"/>
-      <x:c r="AD52" t="str"/>
-      <x:c r="AE52" t="str"/>
-      <x:c r="AF52" t="str"/>
-      <x:c r="AG52" t="str"/>
-      <x:c r="AH52" t="str"/>
-      <x:c r="AI52" t="str"/>
-      <x:c r="AJ52" t="str"/>
-      <x:c r="AK52" t="str"/>
-      <x:c r="AL52" t="str"/>
-      <x:c r="AM52" t="str"/>
-      <x:c r="AN52" t="str"/>
-      <x:c r="AO52" t="str"/>
-      <x:c r="AP52" t="str"/>
-      <x:c r="AQ52" t="str"/>
-      <x:c r="AR52" t="str"/>
-      <x:c r="AS52" t="str"/>
-      <x:c r="AT52" t="str"/>
-      <x:c r="AU52" t="str"/>
-      <x:c r="AV52" t="str"/>
-      <x:c r="AW52" t="str"/>
+      <x:c r="L52"/>
+      <x:c r="M52"/>
+      <x:c r="N52"/>
+      <x:c r="O52"/>
+      <x:c r="P52"/>
+      <x:c r="Q52"/>
+      <x:c r="R52"/>
+      <x:c r="S52"/>
+      <x:c r="T52"/>
+      <x:c r="U52"/>
+      <x:c r="V52"/>
+      <x:c r="W52"/>
+      <x:c r="X52"/>
+      <x:c r="Y52"/>
+      <x:c r="Z52"/>
+      <x:c r="AA52"/>
+      <x:c r="AB52"/>
+      <x:c r="AC52"/>
+      <x:c r="AD52"/>
+      <x:c r="AE52"/>
+      <x:c r="AF52"/>
+      <x:c r="AG52"/>
+      <x:c r="AH52"/>
+      <x:c r="AI52"/>
+      <x:c r="AJ52"/>
+      <x:c r="AK52"/>
+      <x:c r="AL52"/>
+      <x:c r="AM52"/>
+      <x:c r="AN52"/>
+      <x:c r="AO52"/>
+      <x:c r="AP52"/>
+      <x:c r="AQ52"/>
+      <x:c r="AR52"/>
+      <x:c r="AS52"/>
+      <x:c r="AT52"/>
+      <x:c r="AU52"/>
+      <x:c r="AV52"/>
+      <x:c r="AW52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" t="str">
@@ -5018,44 +5018,44 @@
       <x:c r="K53" t="str">
         <x:v>Activity Type: IP, How Many: 2, Name Of Organization Planned with: Durable Technologies, Planned: Yes, Datev Planned on: 2026-02-18 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Electros Energies, Planned: Yes, Datev Planned on: 2026-02-18 | Activity Type: IP, How Many: 4, Name Of Organization Planned with: Lahore Electric Supply Company (LESCO), Planned: Yes, Datev Planned on: 2026-02-18 | Activity Type: IP, How Many: 1, Name Of Organization Planned with: Technology Links (Pvt.) Ltd., Planned: Yes, Datev Planned on: 2026-02-18 | Activity Type: IP, How Many: 2, Name Of Organization Planned with: Transfopower  Industries, Planned: Yes, Datev Planned on: 2026-02-18</x:v>
       </x:c>
-      <x:c r="L53" t="str"/>
-      <x:c r="M53" t="str"/>
-      <x:c r="N53" t="str"/>
-      <x:c r="O53" t="str"/>
-      <x:c r="P53" t="str"/>
-      <x:c r="Q53" t="str"/>
-      <x:c r="R53" t="str"/>
-      <x:c r="S53" t="str"/>
-      <x:c r="T53" t="str"/>
-      <x:c r="U53" t="str"/>
-      <x:c r="V53" t="str"/>
-      <x:c r="W53" t="str"/>
-      <x:c r="X53" t="str"/>
-      <x:c r="Y53" t="str"/>
-      <x:c r="Z53" t="str"/>
-      <x:c r="AA53" t="str"/>
-      <x:c r="AB53" t="str"/>
-      <x:c r="AC53" t="str"/>
-      <x:c r="AD53" t="str"/>
-      <x:c r="AE53" t="str"/>
-      <x:c r="AF53" t="str"/>
-      <x:c r="AG53" t="str"/>
-      <x:c r="AH53" t="str"/>
-      <x:c r="AI53" t="str"/>
-      <x:c r="AJ53" t="str"/>
-      <x:c r="AK53" t="str"/>
-      <x:c r="AL53" t="str"/>
-      <x:c r="AM53" t="str"/>
-      <x:c r="AN53" t="str"/>
-      <x:c r="AO53" t="str"/>
-      <x:c r="AP53" t="str"/>
-      <x:c r="AQ53" t="str"/>
-      <x:c r="AR53" t="str"/>
-      <x:c r="AS53" t="str"/>
-      <x:c r="AT53" t="str"/>
-      <x:c r="AU53" t="str"/>
-      <x:c r="AV53" t="str"/>
-      <x:c r="AW53" t="str"/>
+      <x:c r="L53"/>
+      <x:c r="M53"/>
+      <x:c r="N53"/>
+      <x:c r="O53"/>
+      <x:c r="P53"/>
+      <x:c r="Q53"/>
+      <x:c r="R53"/>
+      <x:c r="S53"/>
+      <x:c r="T53"/>
+      <x:c r="U53"/>
+      <x:c r="V53"/>
+      <x:c r="W53"/>
+      <x:c r="X53"/>
+      <x:c r="Y53"/>
+      <x:c r="Z53"/>
+      <x:c r="AA53"/>
+      <x:c r="AB53"/>
+      <x:c r="AC53"/>
+      <x:c r="AD53"/>
+      <x:c r="AE53"/>
+      <x:c r="AF53"/>
+      <x:c r="AG53"/>
+      <x:c r="AH53"/>
+      <x:c r="AI53"/>
+      <x:c r="AJ53"/>
+      <x:c r="AK53"/>
+      <x:c r="AL53"/>
+      <x:c r="AM53"/>
+      <x:c r="AN53"/>
+      <x:c r="AO53"/>
+      <x:c r="AP53"/>
+      <x:c r="AQ53"/>
+      <x:c r="AR53"/>
+      <x:c r="AS53"/>
+      <x:c r="AT53"/>
+      <x:c r="AU53"/>
+      <x:c r="AV53"/>
+      <x:c r="AW53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="str">
@@ -5171,21 +5171,21 @@
       <x:c r="AH54" t="str">
         <x:v>Faculty members have been encouraged to develop collaborative research proposals aligned with SDGs, emerging literary trends, and external funding opportunities.</x:v>
       </x:c>
-      <x:c r="AI54" t="str"/>
-      <x:c r="AJ54" t="str"/>
-      <x:c r="AK54" t="str"/>
-      <x:c r="AL54" t="str"/>
-      <x:c r="AM54" t="str"/>
-      <x:c r="AN54" t="str"/>
-      <x:c r="AO54" t="str"/>
-      <x:c r="AP54" t="str"/>
-      <x:c r="AQ54" t="str"/>
-      <x:c r="AR54" t="str"/>
-      <x:c r="AS54" t="str"/>
-      <x:c r="AT54" t="str"/>
-      <x:c r="AU54" t="str"/>
-      <x:c r="AV54" t="str"/>
-      <x:c r="AW54" t="str"/>
+      <x:c r="AI54"/>
+      <x:c r="AJ54"/>
+      <x:c r="AK54"/>
+      <x:c r="AL54"/>
+      <x:c r="AM54"/>
+      <x:c r="AN54"/>
+      <x:c r="AO54"/>
+      <x:c r="AP54"/>
+      <x:c r="AQ54"/>
+      <x:c r="AR54"/>
+      <x:c r="AS54"/>
+      <x:c r="AT54"/>
+      <x:c r="AU54"/>
+      <x:c r="AV54"/>
+      <x:c r="AW54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" t="str">
@@ -5221,21 +5221,21 @@
       <x:c r="K55" t="str">
         <x:v>Activity Type: Internship/Placement, How Many: 1, Name Of Organization Planned with: Govt. Girls High School Bhubtian, Lahore, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-04-16 | Activity Type: Internship/Placement, How Many: 1, Name Of Organization Planned with: Govt. High School Sher Shah Colony, Lahore., Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-04-16 | Activity Type: Internship/Placement, How Many: 1, Name Of Organization Planned with: Govt. Girls Elementary School Sher Shah Colony, Lahore., Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-04-16 | Activity Type: Internship/Placement, How Many: 1, Name Of Organization Planned with: Hamza Foundation, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-04-16 | Activity Type: Internship/Placement, How Many: 1, Name Of Organization Planned with: Child Welfare Center, University of the Punjab, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-04-16 | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: The University of Lahore, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-04-25 | Activity Type: IAB Meeting / Industry Consultation, How Many: 1, Name Of Organization Planned with: Centre for Inclusive Education and Research, Planned: Yes, Scheduled: Yes, Datev Planned on: 2025-11-10 | </x:v>
       </x:c>
-      <x:c r="L55" t="str"/>
+      <x:c r="L55"/>
       <x:c r="M55" t="str">
         <x:v>Company: Govt. Girls High School Bhubtian, Lahore, Sector: Public, Number Of students: 14, Type: Intership, Mode: Physical, Evidence: files::6a58b679d30d1.xlsx, Duration: 30 day | Company: Govt. High School Sher Shah Colony, Lahore., Sector: Public, Number Of students: 9, Type: Intership, Mode: Physical, Evidence: files::6a58b6a816d07.xlsx, Duration: 30 days | Company: Govt. Girls Elementary School Sher Shah Colony, Lahore., Sector: Public, Number Of students: 12, Type: Intership, Mode: Physical, Evidence: files::6a58b6d879616.xlsx, Duration: 30 days | Company: Hamza Foundation, Sector: Welfare NGO, Number Of students: 4, Type: Intership, Mode: Physical, Evidence: files::6a58b77964bb0.xlsx, Duration: 30 days | Company: Child Welfare Center, University of the Punjab, Sector: Public, Number Of students: 2, Type: Intership, Mode: Physical, Evidence: files::6a58b7a77d865.xlsx, Duration: 30 days</x:v>
       </x:c>
-      <x:c r="N55" t="str"/>
-      <x:c r="O55" t="str"/>
-      <x:c r="P55" t="str"/>
-      <x:c r="Q55" t="str"/>
+      <x:c r="N55"/>
+      <x:c r="O55"/>
+      <x:c r="P55"/>
+      <x:c r="Q55"/>
       <x:c r="R55" t="str">
         <x:v>Item: Event Flyers/Reports, Evidence Attached: files::6a59dcdf6e722.docx | Item: Internship Lists (Excel), Evidence Attached: files::6a59dcf037481.xlsx | Item: Guest Visit/Meeting Reports, Evidence Attached: files::6a59dd12c8ef6.pdf</x:v>
       </x:c>
-      <x:c r="S55" t="str"/>
-      <x:c r="T55" t="str"/>
-      <x:c r="U55" t="str"/>
-      <x:c r="V55" t="str"/>
+      <x:c r="S55"/>
+      <x:c r="T55"/>
+      <x:c r="U55"/>
+      <x:c r="V55"/>
       <x:c r="W55" t="str">
         <x:v>2026-07-16</x:v>
       </x:c>
@@ -5251,28 +5251,28 @@
       <x:c r="AA55" t="str">
         <x:v>+923324802789</x:v>
       </x:c>
-      <x:c r="AB55" t="str"/>
-      <x:c r="AC55" t="str"/>
-      <x:c r="AD55" t="str"/>
-      <x:c r="AE55" t="str"/>
-      <x:c r="AF55" t="str"/>
-      <x:c r="AG55" t="str"/>
-      <x:c r="AH55" t="str"/>
-      <x:c r="AI55" t="str"/>
-      <x:c r="AJ55" t="str"/>
-      <x:c r="AK55" t="str"/>
-      <x:c r="AL55" t="str"/>
-      <x:c r="AM55" t="str"/>
-      <x:c r="AN55" t="str"/>
-      <x:c r="AO55" t="str"/>
-      <x:c r="AP55" t="str"/>
-      <x:c r="AQ55" t="str"/>
-      <x:c r="AR55" t="str"/>
-      <x:c r="AS55" t="str"/>
-      <x:c r="AT55" t="str"/>
-      <x:c r="AU55" t="str"/>
-      <x:c r="AV55" t="str"/>
-      <x:c r="AW55" t="str"/>
+      <x:c r="AB55"/>
+      <x:c r="AC55"/>
+      <x:c r="AD55"/>
+      <x:c r="AE55"/>
+      <x:c r="AF55"/>
+      <x:c r="AG55"/>
+      <x:c r="AH55"/>
+      <x:c r="AI55"/>
+      <x:c r="AJ55"/>
+      <x:c r="AK55"/>
+      <x:c r="AL55"/>
+      <x:c r="AM55"/>
+      <x:c r="AN55"/>
+      <x:c r="AO55"/>
+      <x:c r="AP55"/>
+      <x:c r="AQ55"/>
+      <x:c r="AR55"/>
+      <x:c r="AS55"/>
+      <x:c r="AT55"/>
+      <x:c r="AU55"/>
+      <x:c r="AV55"/>
+      <x:c r="AW55"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" t="str">
@@ -5308,7 +5308,7 @@
       <x:c r="K56" t="str">
         <x:v>Activity Type: Seminar / Conference / Workshop, How Many: 41, Name Of Organization Planned with: Department of Mathematics and Statistics, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-01-14, Remarks/Result: Executed: 1/14/2026--6/10/2026</x:v>
       </x:c>
-      <x:c r="L56" t="str"/>
+      <x:c r="L56"/>
       <x:c r="M56" t="str">
         <x:v>Company: University of Lahore (Self), Number Of students: 2, Duration: 4 months as an Teacher Assistant, Type: Intership, Mode: Physical, Evidence: files::6a604dd99e9f0.pdf</x:v>
       </x:c>
@@ -5325,15 +5325,15 @@
       <x:c r="O56" t="str">
         <x:v>New Proposals Initiated: Research Articles, External Collaborators: Yes, Focus Areas / Themes: Research Articles, Evidence: files::6a604aff9ed66.docx</x:v>
       </x:c>
-      <x:c r="P56" t="str"/>
-      <x:c r="Q56" t="str"/>
+      <x:c r="P56"/>
+      <x:c r="Q56"/>
       <x:c r="R56" t="str">
         <x:v>Remarks/Folder Reference/URLs: https://drive.google.com/drive/folders/1Wf2laWl4d-XqLjk05JaWTi-3pl3p0Pdx, Item: Media Coverage/Social Links, Evidence Attached: files::6a604f4787e1c.pdf</x:v>
       </x:c>
-      <x:c r="S56" t="str"/>
-      <x:c r="T56" t="str"/>
-      <x:c r="U56" t="str"/>
-      <x:c r="V56" t="str"/>
+      <x:c r="S56"/>
+      <x:c r="T56"/>
+      <x:c r="U56"/>
+      <x:c r="V56"/>
       <x:c r="W56" t="str">
         <x:v>2026-07-14</x:v>
       </x:c>
@@ -5349,28 +5349,28 @@
       <x:c r="AA56" t="str">
         <x:v>+923366435745</x:v>
       </x:c>
-      <x:c r="AB56" t="str"/>
-      <x:c r="AC56" t="str"/>
-      <x:c r="AD56" t="str"/>
-      <x:c r="AE56" t="str"/>
-      <x:c r="AF56" t="str"/>
-      <x:c r="AG56" t="str"/>
-      <x:c r="AH56" t="str"/>
-      <x:c r="AI56" t="str"/>
-      <x:c r="AJ56" t="str"/>
-      <x:c r="AK56" t="str"/>
-      <x:c r="AL56" t="str"/>
-      <x:c r="AM56" t="str"/>
-      <x:c r="AN56" t="str"/>
-      <x:c r="AO56" t="str"/>
-      <x:c r="AP56" t="str"/>
-      <x:c r="AQ56" t="str"/>
-      <x:c r="AR56" t="str"/>
-      <x:c r="AS56" t="str"/>
-      <x:c r="AT56" t="str"/>
-      <x:c r="AU56" t="str"/>
-      <x:c r="AV56" t="str"/>
-      <x:c r="AW56" t="str"/>
+      <x:c r="AB56"/>
+      <x:c r="AC56"/>
+      <x:c r="AD56"/>
+      <x:c r="AE56"/>
+      <x:c r="AF56"/>
+      <x:c r="AG56"/>
+      <x:c r="AH56"/>
+      <x:c r="AI56"/>
+      <x:c r="AJ56"/>
+      <x:c r="AK56"/>
+      <x:c r="AL56"/>
+      <x:c r="AM56"/>
+      <x:c r="AN56"/>
+      <x:c r="AO56"/>
+      <x:c r="AP56"/>
+      <x:c r="AQ56"/>
+      <x:c r="AR56"/>
+      <x:c r="AS56"/>
+      <x:c r="AT56"/>
+      <x:c r="AU56"/>
+      <x:c r="AV56"/>
+      <x:c r="AW56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" t="str">
@@ -5427,39 +5427,39 @@
       <x:c r="R57" t="str">
         <x:v>Item: Photo Evidence, Evidence Attached: files::6a57183e366b8.jpg, Remarks/Folder Reference/URLs: null | Item: Photo Evidence, Evidence Attached: files::6a5718f26e27b.jpg, Remarks/Folder Reference/URLs: null | Item: Event Flyers/Reports, Evidence Attached: files::6a571988d6f63.jpg, Remarks/Folder Reference/URLs: null | Item: Photo Evidence, Evidence Attached: files::6a5719f0d8dff.jpg, Remarks/Folder Reference/URLs: null</x:v>
       </x:c>
-      <x:c r="S57" t="str"/>
-      <x:c r="T57" t="str"/>
-      <x:c r="U57" t="str"/>
-      <x:c r="V57" t="str"/>
-      <x:c r="W57" t="str"/>
-      <x:c r="X57" t="str"/>
-      <x:c r="Y57" t="str"/>
-      <x:c r="Z57" t="str"/>
-      <x:c r="AA57" t="str"/>
-      <x:c r="AB57" t="str"/>
-      <x:c r="AC57" t="str"/>
-      <x:c r="AD57" t="str"/>
-      <x:c r="AE57" t="str"/>
-      <x:c r="AF57" t="str"/>
-      <x:c r="AG57" t="str"/>
-      <x:c r="AH57" t="str"/>
+      <x:c r="S57"/>
+      <x:c r="T57"/>
+      <x:c r="U57"/>
+      <x:c r="V57"/>
+      <x:c r="W57"/>
+      <x:c r="X57"/>
+      <x:c r="Y57"/>
+      <x:c r="Z57"/>
+      <x:c r="AA57"/>
+      <x:c r="AB57"/>
+      <x:c r="AC57"/>
+      <x:c r="AD57"/>
+      <x:c r="AE57"/>
+      <x:c r="AF57"/>
+      <x:c r="AG57"/>
+      <x:c r="AH57"/>
       <x:c r="AI57" t="str">
         <x:v>select jc44c: IAB Meeting / Industry Consultation, textfield 3ucjgc: Citi pharma, waleed chemicals, printex etc., datetime gxwvjq: 2026-06-30, textfield 2ra7mm: The meeting was chaired by the Dean, Faculty of Sciences, Prof. Dr. Ahmed Bilal Waqar.  The key agenda item was review of seven research projects submitted under the Startup Research Grant Program (SRGP), by the department of Chemistry. The Board evaluated the projects and provided their feedback to the principal investigators (PI) of these projects. The Board assessed the proposals for their research significance, innovation, methodology, and commercialization potential, offering valuable industry-oriented recommendations to strengthen project outcomes and three projects were selected for further submission to ORIC, UOL for final approvals. The meeting reaffirmed the department's commitment to fostering research excellence, academia–industry collaboration, and the translation of faculty research into real-world impact. At the end, Dr Dure Najaf, Secretary IAB and Prof Dr Arif Nazir, HOD Chemistry thanked all the members of the Board for their time, valuable support and recommendations. | select jc44c: MoU Signing (Memorandum of Understanding), textfield 3ucjgc: Waleed Tech (Pvt) Ltd, datetime gxwvjq: 2026-06-19, textfield 2ra7mm: The University of Lahore (UOL) and Waleed Tech (Pvt) Ltd signed a Memorandum of Understanding (MoU) on 19th June 2026, marking a significant step toward strengthening academia–industry collaboration in applied research, innovation, and skill development under UOL’s External Linkages.This partnership aims to foster collaborative research initiatives, industrial training opportunities, and student internship programs, further reinforcing UOL’s commitment to bridging the gap between academia and industry while promoting innovation and professional development.</x:v>
       </x:c>
-      <x:c r="AJ57" t="str"/>
-      <x:c r="AK57" t="str"/>
-      <x:c r="AL57" t="str"/>
-      <x:c r="AM57" t="str"/>
-      <x:c r="AN57" t="str"/>
-      <x:c r="AO57" t="str"/>
-      <x:c r="AP57" t="str"/>
-      <x:c r="AQ57" t="str"/>
-      <x:c r="AR57" t="str"/>
-      <x:c r="AS57" t="str"/>
-      <x:c r="AT57" t="str"/>
-      <x:c r="AU57" t="str"/>
-      <x:c r="AV57" t="str"/>
-      <x:c r="AW57" t="str"/>
+      <x:c r="AJ57"/>
+      <x:c r="AK57"/>
+      <x:c r="AL57"/>
+      <x:c r="AM57"/>
+      <x:c r="AN57"/>
+      <x:c r="AO57"/>
+      <x:c r="AP57"/>
+      <x:c r="AQ57"/>
+      <x:c r="AR57"/>
+      <x:c r="AS57"/>
+      <x:c r="AT57"/>
+      <x:c r="AU57"/>
+      <x:c r="AV57"/>
+      <x:c r="AW57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="str">
@@ -5516,47 +5516,47 @@
       <x:c r="R58" t="str">
         <x:v>Item: null, Evidence Attached: null, Remarks/Folder Reference/URLs: null</x:v>
       </x:c>
-      <x:c r="S58" t="str"/>
-      <x:c r="T58" t="str"/>
-      <x:c r="U58" t="str"/>
-      <x:c r="V58" t="str"/>
+      <x:c r="S58"/>
+      <x:c r="T58"/>
+      <x:c r="U58"/>
+      <x:c r="V58"/>
       <x:c r="W58" t="str">
         <x:v>2026-02-06</x:v>
       </x:c>
       <x:c r="X58" t="str">
-        <x:v>2026</x:v>
+        <x:v>2025</x:v>
       </x:c>
       <x:c r="Y58" t="str">
         <x:v>Lecturer</x:v>
       </x:c>
-      <x:c r="Z58" t="str"/>
+      <x:c r="Z58"/>
       <x:c r="AA58" t="str">
         <x:v>+923360450431</x:v>
       </x:c>
-      <x:c r="AB58" t="str"/>
-      <x:c r="AC58" t="str"/>
-      <x:c r="AD58" t="str"/>
-      <x:c r="AE58" t="str"/>
-      <x:c r="AF58" t="str"/>
-      <x:c r="AG58" t="str"/>
-      <x:c r="AH58" t="str"/>
+      <x:c r="AB58"/>
+      <x:c r="AC58"/>
+      <x:c r="AD58"/>
+      <x:c r="AE58"/>
+      <x:c r="AF58"/>
+      <x:c r="AG58"/>
+      <x:c r="AH58"/>
       <x:c r="AI58" t="str">
         <x:v>select jc44c: null, textfield 3ucjgc: null, datetime gxwvjq: null, textfield 2ra7mm: null</x:v>
       </x:c>
-      <x:c r="AJ58" t="str"/>
-      <x:c r="AK58" t="str"/>
-      <x:c r="AL58" t="str"/>
-      <x:c r="AM58" t="str"/>
-      <x:c r="AN58" t="str"/>
-      <x:c r="AO58" t="str"/>
-      <x:c r="AP58" t="str"/>
-      <x:c r="AQ58" t="str"/>
-      <x:c r="AR58" t="str"/>
-      <x:c r="AS58" t="str"/>
-      <x:c r="AT58" t="str"/>
-      <x:c r="AU58" t="str"/>
-      <x:c r="AV58" t="str"/>
-      <x:c r="AW58" t="str"/>
+      <x:c r="AJ58"/>
+      <x:c r="AK58"/>
+      <x:c r="AL58"/>
+      <x:c r="AM58"/>
+      <x:c r="AN58"/>
+      <x:c r="AO58"/>
+      <x:c r="AP58"/>
+      <x:c r="AQ58"/>
+      <x:c r="AR58"/>
+      <x:c r="AS58"/>
+      <x:c r="AT58"/>
+      <x:c r="AU58"/>
+      <x:c r="AV58"/>
+      <x:c r="AW58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="str">
@@ -5652,28 +5652,28 @@
       <x:c r="AE59" t="str">
         <x:v>N/A</x:v>
       </x:c>
-      <x:c r="AF59" t="str"/>
-      <x:c r="AG59" t="str"/>
+      <x:c r="AF59"/>
+      <x:c r="AG59"/>
       <x:c r="AH59" t="str">
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="AI59" t="str">
         <x:v>select jc44c: Seminar / Conference / Workshop, textfield 3ucjgc: Irrigation Department, datetime gxwvjq: 2026-07-16, textfield 2ra7mm: Students gained industry knowledge | select jc44c: Guest Lecture, textfield 3ucjgc: UET Lahore, datetime gxwvjq: null, textfield 2ra7mm: null</x:v>
       </x:c>
-      <x:c r="AJ59" t="str"/>
-      <x:c r="AK59" t="str"/>
-      <x:c r="AL59" t="str"/>
-      <x:c r="AM59" t="str"/>
-      <x:c r="AN59" t="str"/>
-      <x:c r="AO59" t="str"/>
-      <x:c r="AP59" t="str"/>
-      <x:c r="AQ59" t="str"/>
-      <x:c r="AR59" t="str"/>
-      <x:c r="AS59" t="str"/>
-      <x:c r="AT59" t="str"/>
-      <x:c r="AU59" t="str"/>
-      <x:c r="AV59" t="str"/>
-      <x:c r="AW59" t="str"/>
+      <x:c r="AJ59"/>
+      <x:c r="AK59"/>
+      <x:c r="AL59"/>
+      <x:c r="AM59"/>
+      <x:c r="AN59"/>
+      <x:c r="AO59"/>
+      <x:c r="AP59"/>
+      <x:c r="AQ59"/>
+      <x:c r="AR59"/>
+      <x:c r="AS59"/>
+      <x:c r="AT59"/>
+      <x:c r="AU59"/>
+      <x:c r="AV59"/>
+      <x:c r="AW59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" t="str">
@@ -5691,11 +5691,11 @@
       <x:c r="E60" t="str">
         <x:v>9 July 2026</x:v>
       </x:c>
-      <x:c r="F60" t="str"/>
-      <x:c r="G60" t="str"/>
-      <x:c r="H60" t="str"/>
-      <x:c r="I60" t="str"/>
-      <x:c r="J60" t="str"/>
+      <x:c r="F60"/>
+      <x:c r="G60"/>
+      <x:c r="H60"/>
+      <x:c r="I60"/>
+      <x:c r="J60"/>
       <x:c r="K60" t="str">
         <x:v>Activity Type: null, How Many: null, Name Of Organization Planned with: null, Planned: null, Scheduled: null, Datev Planned on: null, Remarks/Result: null</x:v>
       </x:c>
@@ -5720,22 +5720,22 @@
       <x:c r="R60" t="str">
         <x:v>Item: null, Evidence Attached: null, Remarks/Folder Reference/URLs: null</x:v>
       </x:c>
-      <x:c r="S60" t="str"/>
-      <x:c r="T60" t="str"/>
-      <x:c r="U60" t="str"/>
-      <x:c r="V60" t="str"/>
-      <x:c r="W60" t="str"/>
-      <x:c r="X60" t="str"/>
-      <x:c r="Y60" t="str"/>
-      <x:c r="Z60" t="str"/>
-      <x:c r="AA60" t="str"/>
-      <x:c r="AB60" t="str"/>
-      <x:c r="AC60" t="str"/>
-      <x:c r="AD60" t="str"/>
-      <x:c r="AE60" t="str"/>
-      <x:c r="AF60" t="str"/>
-      <x:c r="AG60" t="str"/>
-      <x:c r="AH60" t="str"/>
+      <x:c r="S60"/>
+      <x:c r="T60"/>
+      <x:c r="U60"/>
+      <x:c r="V60"/>
+      <x:c r="W60"/>
+      <x:c r="X60"/>
+      <x:c r="Y60"/>
+      <x:c r="Z60"/>
+      <x:c r="AA60"/>
+      <x:c r="AB60"/>
+      <x:c r="AC60"/>
+      <x:c r="AD60"/>
+      <x:c r="AE60"/>
+      <x:c r="AF60"/>
+      <x:c r="AG60"/>
+      <x:c r="AH60"/>
       <x:c r="AI60" t="str">
         <x:v>select jc44c: null, textfield 3ucjgc: null, datetime gxwvjq: null, textfield 2ra7mm: null</x:v>
       </x:c>
@@ -5766,11 +5766,11 @@
       <x:c r="AR60" t="str">
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="AS60" t="str"/>
-      <x:c r="AT60" t="str"/>
-      <x:c r="AU60" t="str"/>
-      <x:c r="AV60" t="str"/>
-      <x:c r="AW60" t="str"/>
+      <x:c r="AS60"/>
+      <x:c r="AT60"/>
+      <x:c r="AU60"/>
+      <x:c r="AV60"/>
+      <x:c r="AW60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="str">
@@ -5827,39 +5827,39 @@
       <x:c r="R61" t="str">
         <x:v>Item: null, Evidence Attached: null, Remarks/Folder Reference/URLs: null</x:v>
       </x:c>
-      <x:c r="S61" t="str"/>
-      <x:c r="T61" t="str"/>
-      <x:c r="U61" t="str"/>
-      <x:c r="V61" t="str"/>
-      <x:c r="W61" t="str"/>
-      <x:c r="X61" t="str"/>
-      <x:c r="Y61" t="str"/>
-      <x:c r="Z61" t="str"/>
-      <x:c r="AA61" t="str"/>
-      <x:c r="AB61" t="str"/>
-      <x:c r="AC61" t="str"/>
-      <x:c r="AD61" t="str"/>
-      <x:c r="AE61" t="str"/>
-      <x:c r="AF61" t="str"/>
-      <x:c r="AG61" t="str"/>
-      <x:c r="AH61" t="str"/>
+      <x:c r="S61"/>
+      <x:c r="T61"/>
+      <x:c r="U61"/>
+      <x:c r="V61"/>
+      <x:c r="W61"/>
+      <x:c r="X61"/>
+      <x:c r="Y61"/>
+      <x:c r="Z61"/>
+      <x:c r="AA61"/>
+      <x:c r="AB61"/>
+      <x:c r="AC61"/>
+      <x:c r="AD61"/>
+      <x:c r="AE61"/>
+      <x:c r="AF61"/>
+      <x:c r="AG61"/>
+      <x:c r="AH61"/>
       <x:c r="AI61" t="str">
         <x:v>select jc44c: null, textfield 3ucjgc: null, datetime gxwvjq: null, textfield 2ra7mm: null</x:v>
       </x:c>
-      <x:c r="AJ61" t="str"/>
-      <x:c r="AK61" t="str"/>
-      <x:c r="AL61" t="str"/>
-      <x:c r="AM61" t="str"/>
-      <x:c r="AN61" t="str"/>
-      <x:c r="AO61" t="str"/>
-      <x:c r="AP61" t="str"/>
-      <x:c r="AQ61" t="str"/>
-      <x:c r="AR61" t="str"/>
-      <x:c r="AS61" t="str"/>
-      <x:c r="AT61" t="str"/>
-      <x:c r="AU61" t="str"/>
-      <x:c r="AV61" t="str"/>
-      <x:c r="AW61" t="str"/>
+      <x:c r="AJ61"/>
+      <x:c r="AK61"/>
+      <x:c r="AL61"/>
+      <x:c r="AM61"/>
+      <x:c r="AN61"/>
+      <x:c r="AO61"/>
+      <x:c r="AP61"/>
+      <x:c r="AQ61"/>
+      <x:c r="AR61"/>
+      <x:c r="AS61"/>
+      <x:c r="AT61"/>
+      <x:c r="AU61"/>
+      <x:c r="AV61"/>
+      <x:c r="AW61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="str">
@@ -5916,10 +5916,10 @@
       <x:c r="R62" t="str">
         <x:v>Item: Guest Visit/Meeting Reports, Evidence Attached: files::6a59d5a103d62.docx, Remarks/Folder Reference/URLs: reports of major events compiled in one file | Item: Media Coverage/Social Links, Remarks/Folder Reference/URLs: ms bushra event   https://drive.google.com/drive/folders/1w9tEVOy3_MLJ_bYxbxTv90JoPYAzB8Xg?usp=drive_link | Item: Media Coverage/Social Links, Remarks/Folder Reference/URLs: Income Tax Certificate Distribution Ceremony   https://drive.google.com/drive/folders/15z2VFcn7_7FrOQBx7uB-mC_N2STAE-oF?usp=sharing | Item: Media Coverage/Social Links, Remarks/Folder Reference/URLs: Please find pictures of the 6th National Moot Competition in the attached link. https://drive.google.com/drive/folders/1bp4P7mPJfcy2AAzPi3RCuaEKHlhJMGKz?usp=sharing | Item: Photo Evidence, Evidence Attached: files::6a59d8aed1dca.jpg, Remarks/Folder Reference/URLs: Federal Tax Ombudsman Campus Ambassador (CAP) 2026–27.-Rubab Anjum | Item: Photo Evidence, Evidence Attached: files::6a59d9e799a63.jpg, Remarks/Folder Reference/URLs: Rubab Anjum | Item: Photo Evidence, Evidence Attached: files::6a59d9fe0b47b.jpg, Remarks/Folder Reference/URLs: Arshmah Awan, Digital Ambassador for the Human Rights Committee, Punjab Bar Council, | Item: Photo Evidence, Evidence Attached: files::6a59da0918a46.jpg, Remarks/Folder Reference/URLs: Ayesha Aslam and Qandeel Imran</x:v>
       </x:c>
-      <x:c r="S62" t="str"/>
-      <x:c r="T62" t="str"/>
-      <x:c r="U62" t="str"/>
-      <x:c r="V62" t="str"/>
+      <x:c r="S62"/>
+      <x:c r="T62"/>
+      <x:c r="U62"/>
+      <x:c r="V62"/>
       <x:c r="W62" t="str">
         <x:v>2026-07-09</x:v>
       </x:c>
@@ -5935,30 +5935,30 @@
       <x:c r="AA62" t="str">
         <x:v>+923238476688</x:v>
       </x:c>
-      <x:c r="AB62" t="str"/>
-      <x:c r="AC62" t="str"/>
-      <x:c r="AD62" t="str"/>
-      <x:c r="AE62" t="str"/>
-      <x:c r="AF62" t="str"/>
-      <x:c r="AG62" t="str"/>
-      <x:c r="AH62" t="str"/>
+      <x:c r="AB62"/>
+      <x:c r="AC62"/>
+      <x:c r="AD62"/>
+      <x:c r="AE62"/>
+      <x:c r="AF62"/>
+      <x:c r="AG62"/>
+      <x:c r="AH62"/>
       <x:c r="AI62" t="str">
         <x:v>select jc44c: null, textfield 3ucjgc: null, datetime gxwvjq: null, textfield 2ra7mm: null</x:v>
       </x:c>
-      <x:c r="AJ62" t="str"/>
-      <x:c r="AK62" t="str"/>
-      <x:c r="AL62" t="str"/>
-      <x:c r="AM62" t="str"/>
-      <x:c r="AN62" t="str"/>
-      <x:c r="AO62" t="str"/>
-      <x:c r="AP62" t="str"/>
-      <x:c r="AQ62" t="str"/>
-      <x:c r="AR62" t="str"/>
-      <x:c r="AS62" t="str"/>
-      <x:c r="AT62" t="str"/>
-      <x:c r="AU62" t="str"/>
-      <x:c r="AV62" t="str"/>
-      <x:c r="AW62" t="str"/>
+      <x:c r="AJ62"/>
+      <x:c r="AK62"/>
+      <x:c r="AL62"/>
+      <x:c r="AM62"/>
+      <x:c r="AN62"/>
+      <x:c r="AO62"/>
+      <x:c r="AP62"/>
+      <x:c r="AQ62"/>
+      <x:c r="AR62"/>
+      <x:c r="AS62"/>
+      <x:c r="AT62"/>
+      <x:c r="AU62"/>
+      <x:c r="AV62"/>
+      <x:c r="AW62"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="str">
@@ -6015,39 +6015,39 @@
       <x:c r="R63" t="str">
         <x:v>Item: null, Evidence Attached: null, Remarks/Folder Reference/URLs: null</x:v>
       </x:c>
-      <x:c r="S63" t="str"/>
-      <x:c r="T63" t="str"/>
-      <x:c r="U63" t="str"/>
-      <x:c r="V63" t="str"/>
-      <x:c r="W63" t="str"/>
-      <x:c r="X63" t="str"/>
-      <x:c r="Y63" t="str"/>
-      <x:c r="Z63" t="str"/>
-      <x:c r="AA63" t="str"/>
-      <x:c r="AB63" t="str"/>
-      <x:c r="AC63" t="str"/>
-      <x:c r="AD63" t="str"/>
-      <x:c r="AE63" t="str"/>
-      <x:c r="AF63" t="str"/>
-      <x:c r="AG63" t="str"/>
-      <x:c r="AH63" t="str"/>
+      <x:c r="S63"/>
+      <x:c r="T63"/>
+      <x:c r="U63"/>
+      <x:c r="V63"/>
+      <x:c r="W63"/>
+      <x:c r="X63"/>
+      <x:c r="Y63"/>
+      <x:c r="Z63"/>
+      <x:c r="AA63"/>
+      <x:c r="AB63"/>
+      <x:c r="AC63"/>
+      <x:c r="AD63"/>
+      <x:c r="AE63"/>
+      <x:c r="AF63"/>
+      <x:c r="AG63"/>
+      <x:c r="AH63"/>
       <x:c r="AI63" t="str">
         <x:v>select jc44c: null, textfield 3ucjgc: null, datetime gxwvjq: null, textfield 2ra7mm: null</x:v>
       </x:c>
-      <x:c r="AJ63" t="str"/>
-      <x:c r="AK63" t="str"/>
-      <x:c r="AL63" t="str"/>
-      <x:c r="AM63" t="str"/>
-      <x:c r="AN63" t="str"/>
-      <x:c r="AO63" t="str"/>
-      <x:c r="AP63" t="str"/>
-      <x:c r="AQ63" t="str"/>
-      <x:c r="AR63" t="str"/>
-      <x:c r="AS63" t="str"/>
-      <x:c r="AT63" t="str"/>
-      <x:c r="AU63" t="str"/>
-      <x:c r="AV63" t="str"/>
-      <x:c r="AW63" t="str"/>
+      <x:c r="AJ63"/>
+      <x:c r="AK63"/>
+      <x:c r="AL63"/>
+      <x:c r="AM63"/>
+      <x:c r="AN63"/>
+      <x:c r="AO63"/>
+      <x:c r="AP63"/>
+      <x:c r="AQ63"/>
+      <x:c r="AR63"/>
+      <x:c r="AS63"/>
+      <x:c r="AT63"/>
+      <x:c r="AU63"/>
+      <x:c r="AV63"/>
+      <x:c r="AW63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="str">
@@ -6065,11 +6065,11 @@
       <x:c r="E64" t="str">
         <x:v>15 June 2026</x:v>
       </x:c>
-      <x:c r="F64" t="str"/>
-      <x:c r="G64" t="str"/>
-      <x:c r="H64" t="str"/>
-      <x:c r="I64" t="str"/>
-      <x:c r="J64" t="str"/>
+      <x:c r="F64"/>
+      <x:c r="G64"/>
+      <x:c r="H64"/>
+      <x:c r="I64"/>
+      <x:c r="J64"/>
       <x:c r="K64" t="str">
         <x:v>checklist vqmy3r: , How Many: null, textarea c28h0g: null</x:v>
       </x:c>
@@ -6079,7 +6079,7 @@
       <x:c r="M64" t="str">
         <x:v>Company: null, Sector: null, Number Of students: null, textfield 7f2kh: null, Duration: null, textfield 99poj: null</x:v>
       </x:c>
-      <x:c r="N64" t="str"/>
+      <x:c r="N64"/>
       <x:c r="O64" t="str">
         <x:v>New Proposals Initiated: null, External Collaborators: null, Focus Areas / Themes: null, Current Status: </x:v>
       </x:c>
@@ -6092,39 +6092,39 @@
       <x:c r="R64" t="str">
         <x:v>checklist xtq45c: , checkbox 9sd7e: false, textarea qhmbl9: null</x:v>
       </x:c>
-      <x:c r="S64" t="str"/>
-      <x:c r="T64" t="str"/>
-      <x:c r="U64" t="str"/>
-      <x:c r="V64" t="str"/>
-      <x:c r="W64" t="str"/>
-      <x:c r="X64" t="str"/>
-      <x:c r="Y64" t="str"/>
-      <x:c r="Z64" t="str"/>
-      <x:c r="AA64" t="str"/>
-      <x:c r="AB64" t="str"/>
-      <x:c r="AC64" t="str"/>
-      <x:c r="AD64" t="str"/>
-      <x:c r="AE64" t="str"/>
-      <x:c r="AF64" t="str"/>
-      <x:c r="AG64" t="str"/>
-      <x:c r="AH64" t="str"/>
+      <x:c r="S64"/>
+      <x:c r="T64"/>
+      <x:c r="U64"/>
+      <x:c r="V64"/>
+      <x:c r="W64"/>
+      <x:c r="X64"/>
+      <x:c r="Y64"/>
+      <x:c r="Z64"/>
+      <x:c r="AA64"/>
+      <x:c r="AB64"/>
+      <x:c r="AC64"/>
+      <x:c r="AD64"/>
+      <x:c r="AE64"/>
+      <x:c r="AF64"/>
+      <x:c r="AG64"/>
+      <x:c r="AH64"/>
       <x:c r="AI64" t="str">
         <x:v>textfield cmat3d: null, textfield 3ucjgc: null, datetime gxwvjq: null, textfield 2ra7mm: null</x:v>
       </x:c>
-      <x:c r="AJ64" t="str"/>
-      <x:c r="AK64" t="str"/>
-      <x:c r="AL64" t="str"/>
-      <x:c r="AM64" t="str"/>
-      <x:c r="AN64" t="str"/>
-      <x:c r="AO64" t="str"/>
-      <x:c r="AP64" t="str"/>
-      <x:c r="AQ64" t="str"/>
-      <x:c r="AR64" t="str"/>
-      <x:c r="AS64" t="str"/>
-      <x:c r="AT64" t="str"/>
-      <x:c r="AU64" t="str"/>
-      <x:c r="AV64" t="str"/>
-      <x:c r="AW64" t="str"/>
+      <x:c r="AJ64"/>
+      <x:c r="AK64"/>
+      <x:c r="AL64"/>
+      <x:c r="AM64"/>
+      <x:c r="AN64"/>
+      <x:c r="AO64"/>
+      <x:c r="AP64"/>
+      <x:c r="AQ64"/>
+      <x:c r="AR64"/>
+      <x:c r="AS64"/>
+      <x:c r="AT64"/>
+      <x:c r="AU64"/>
+      <x:c r="AV64"/>
+      <x:c r="AW64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="str">
@@ -6148,7 +6148,7 @@
       <x:c r="G65" t="str">
         <x:v>foc_lbs_lhr@uol.edu.pk</x:v>
       </x:c>
-      <x:c r="H65" t="str"/>
+      <x:c r="H65"/>
       <x:c r="I65" t="str">
         <x:v>Faculty of Management Sciences</x:v>
       </x:c>
@@ -6164,7 +6164,7 @@
       <x:c r="M65" t="str">
         <x:v>Company: Fountain House-Pakistan, Sector: Mental Health, Number Of students: 28, textfield 7f2kh: Placement, Duration: 13 to 15 weeks, textfield 99poj: Physical | Company: null, Sector: null, Number Of students: null, textfield 7f2kh: null, Duration: null, textfield 99poj: null</x:v>
       </x:c>
-      <x:c r="N65" t="str"/>
+      <x:c r="N65"/>
       <x:c r="O65" t="str">
         <x:v>New Proposals Initiated: Pathological Traits, Creative Motivation, and Deviance in Individuals with Substance Use Disorder, External Collaborators: Dr. Saima Majeed, Forman Christian College, University, Lahore, Focus Areas / Themes: Substance Use Disorder, Current Status: Submitted</x:v>
       </x:c>
@@ -6221,23 +6221,23 @@
       <x:c r="AD65" t="str">
         <x:v>Exchange, Joint Forum, MoU Drafting</x:v>
       </x:c>
-      <x:c r="AE65" t="str"/>
-      <x:c r="AF65" t="str"/>
-      <x:c r="AG65" t="str"/>
-      <x:c r="AH65" t="str"/>
+      <x:c r="AE65"/>
+      <x:c r="AF65"/>
+      <x:c r="AG65"/>
+      <x:c r="AH65"/>
       <x:c r="AI65" t="str">
         <x:v>textfield cmat3d: MOU, textfield 3ucjgc: SKY HIGHER, datetime gxwvjq: 2025-09-01, textfield 2ra7mm: SEEKS TO ESTABLISH MUTUAL BENIFIT | textfield cmat3d: MOU, textfield 3ucjgc: INNOVATIVE ZONE, datetime gxwvjq: 2025-09-04, textfield 2ra7mm: CLINICAL TRAINING | textfield cmat3d: INTERNSHIP, textfield 3ucjgc: FOUNTAIN HOUSE, datetime gxwvjq: 2025-06-09, textfield 2ra7mm: HANDS ON EXPIERENCE</x:v>
       </x:c>
-      <x:c r="AJ65" t="str"/>
-      <x:c r="AK65" t="str"/>
-      <x:c r="AL65" t="str"/>
-      <x:c r="AM65" t="str"/>
-      <x:c r="AN65" t="str"/>
-      <x:c r="AO65" t="str"/>
-      <x:c r="AP65" t="str"/>
-      <x:c r="AQ65" t="str"/>
-      <x:c r="AR65" t="str"/>
-      <x:c r="AS65" t="str"/>
+      <x:c r="AJ65"/>
+      <x:c r="AK65"/>
+      <x:c r="AL65"/>
+      <x:c r="AM65"/>
+      <x:c r="AN65"/>
+      <x:c r="AO65"/>
+      <x:c r="AP65"/>
+      <x:c r="AQ65"/>
+      <x:c r="AR65"/>
+      <x:c r="AS65"/>
       <x:c r="AT65" t="str">
         <x:v>(e.g., Alumni Talks, Mentorship, Panels): 
 During the current reporting period, no formal alumni engagement activities (such as alumni talks, mentorship sessions, or panel discussions) were conducted. However, the department recognizes the importance of alumni involvement in academic enrichment and professional development of students</x:v>
@@ -6259,6 +6259,89 @@
 •	Schedule at least one alumni interaction session in the next term</x:v>
       </x:c>
     </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str">
+        <x:v>PRPSTFPT105</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>Foc Pharm Lhr</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>foc_pharm_lhr@uol.edu.pk</x:v>
+      </x:c>
+      <x:c r="D66" t="str">
+        <x:v>Pending From Linkage Officer</x:v>
+      </x:c>
+      <x:c r="E66" t="str">
+        <x:v>12 October 2026</x:v>
+      </x:c>
+      <x:c r="F66" t="str">
+        <x:v>Foc Pharm Lhr</x:v>
+      </x:c>
+      <x:c r="G66" t="str">
+        <x:v>foc_pharm_lhr@uol.edu.pk</x:v>
+      </x:c>
+      <x:c r="H66" t="str">
+        <x:v>Lahore Campus</x:v>
+      </x:c>
+      <x:c r="I66" t="str">
+        <x:v>Faculty of Pharmacy</x:v>
+      </x:c>
+      <x:c r="J66" t="str">
+        <x:v>Department of Pharmacy</x:v>
+      </x:c>
+      <x:c r="K66" t="str">
+        <x:v>Activity Type: Seminar / Conference / Workshop, How Many: 1, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-09-16, Remarks/Result: Done, Name Of Organization Planned with: CHughtai LAb | Activity Type: Seminar / Conference / Workshop, How Many: 1, Name Of Organization Planned with: SKMHRC, Planned: Yes, Scheduled: Yes, Datev Planned on: 2026-10-12 | Activity Type: Guest Lecture, How Many: 5, Name Of Organization Planned with: Dr Kamala Dr Osman Mirza Dr Khalid Dr Mohsen Dr Hafiz Hassan, Planned: Yes, Scheduled: No</x:v>
+      </x:c>
+      <x:c r="L66"/>
+      <x:c r="M66"/>
+      <x:c r="N66"/>
+      <x:c r="O66"/>
+      <x:c r="P66"/>
+      <x:c r="Q66"/>
+      <x:c r="R66"/>
+      <x:c r="S66"/>
+      <x:c r="T66"/>
+      <x:c r="U66"/>
+      <x:c r="V66"/>
+      <x:c r="W66" t="str">
+        <x:v>2026-10-01</x:v>
+      </x:c>
+      <x:c r="X66" t="str">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="Y66" t="str">
+        <x:v>Assistanat Professor</x:v>
+      </x:c>
+      <x:c r="Z66" t="str">
+        <x:v>2026-10-12</x:v>
+      </x:c>
+      <x:c r="AA66" t="str">
+        <x:v>+923317072711</x:v>
+      </x:c>
+      <x:c r="AB66"/>
+      <x:c r="AC66"/>
+      <x:c r="AD66"/>
+      <x:c r="AE66"/>
+      <x:c r="AF66"/>
+      <x:c r="AG66"/>
+      <x:c r="AH66"/>
+      <x:c r="AI66"/>
+      <x:c r="AJ66"/>
+      <x:c r="AK66"/>
+      <x:c r="AL66"/>
+      <x:c r="AM66"/>
+      <x:c r="AN66"/>
+      <x:c r="AO66"/>
+      <x:c r="AP66"/>
+      <x:c r="AQ66"/>
+      <x:c r="AR66"/>
+      <x:c r="AS66"/>
+      <x:c r="AT66"/>
+      <x:c r="AU66"/>
+      <x:c r="AV66"/>
+      <x:c r="AW66"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
